--- a/AAII_Financials/Quarterly/DLTH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DLTH_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="92">
   <si>
     <t>DLTH</t>
   </si>
@@ -656,405 +656,418 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45228</v>
+      </c>
+      <c r="E7" s="2">
         <v>45137</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45046</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44955</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44864</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44773</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44682</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44591</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44500</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44409</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44318</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44227</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44136</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44045</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43954</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43863</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43772</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43681</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43590</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43499</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43401</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43310</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43219</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43128</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43037</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>42946</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42855</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42764</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42673</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>138200</v>
+      </c>
+      <c r="E8" s="3">
         <v>139100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>123800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>241800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>147100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>141500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>122900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>270800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>145300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>149100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>133400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>256000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>135500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>137400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>109900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>259600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>119800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>122000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>114200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>250500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>106700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>110700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>100200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>217800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>83700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>86200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>83700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>174700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>67000</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>68800</v>
+      </c>
+      <c r="E9" s="3">
         <v>67600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>58100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>117900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>70200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>65900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>55800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>125100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>61600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>67700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>66900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>120300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>64500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>64900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>57600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>122600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>54400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>57200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>53300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>119300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>45700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>48400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>44300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>101800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>36300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>37300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>35000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>77900</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>28300</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>69400</v>
+      </c>
+      <c r="E10" s="3">
         <v>71500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>65700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>123900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>76900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>75600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>67100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>145700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>83700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>81400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>66500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>135700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>71000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>72500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>52300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>137000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>65400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>64800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>60900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>131200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>61000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>62300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>55900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>116000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>47400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>48900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>48700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>96800</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>38700</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1086,8 +1099,9 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1175,8 +1189,11 @@
       <c r="AE12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1264,8 +1281,11 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1290,8 +1310,8 @@
       <c r="J14" s="3">
         <v>0</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>8</v>
+      <c r="K14" s="3">
+        <v>0</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>8</v>
@@ -1308,11 +1328,11 @@
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R14" s="3">
         <v>1600</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>8</v>
@@ -1329,8 +1349,8 @@
       <c r="W14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y14" s="3">
         <v>0</v>
@@ -1353,8 +1373,11 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1395,25 +1418,25 @@
         <v>800</v>
       </c>
       <c r="P15" s="3">
+        <v>800</v>
+      </c>
+      <c r="Q15" s="3">
         <v>900</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>700</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>200</v>
-      </c>
-      <c r="S15" s="3">
-        <v>500</v>
       </c>
       <c r="T15" s="3">
         <v>500</v>
       </c>
       <c r="U15" s="3">
+        <v>500</v>
+      </c>
+      <c r="V15" s="3">
         <v>100</v>
-      </c>
-      <c r="V15" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="W15" s="3" t="s">
         <v>8</v>
@@ -1424,8 +1447,8 @@
       <c r="Y15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z15" s="3">
-        <v>0</v>
+      <c r="Z15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA15" s="3">
         <v>0</v>
@@ -1442,8 +1465,11 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1472,186 +1498,193 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>150600</v>
+      </c>
+      <c r="E17" s="3">
         <v>140500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>128300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>231100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>154500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>137600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>123800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>246500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>140400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>136000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>131500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>225400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>132700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>127600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>128900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>226500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>118400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>118200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>123900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>220400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>109300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>100800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>100500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>188300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>84300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>78800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>82900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>151800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>66200</v>
       </c>
     </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-12400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-1400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-4500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>10700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-7400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>3900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>24300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>4900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>13100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>30600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>9800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-19000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>33100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>3800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-9700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>30100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-2600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>9900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>29500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>7400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>22900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1683,8 +1716,9 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1695,76 +1729,76 @@
         <v>100</v>
       </c>
       <c r="F20" s="3">
+        <v>100</v>
+      </c>
+      <c r="G20" s="3">
         <v>200</v>
-      </c>
-      <c r="G20" s="3">
-        <v>100</v>
       </c>
       <c r="H20" s="3">
         <v>100</v>
       </c>
       <c r="I20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>100</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O20" s="3">
         <v>100</v>
       </c>
       <c r="P20" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-300</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>100</v>
       </c>
       <c r="R20" s="3">
         <v>100</v>
       </c>
       <c r="S20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T20" s="3">
         <v>0</v>
       </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>300</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
       <c r="X20" s="3">
         <v>0</v>
       </c>
       <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
         <v>200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>300</v>
-      </c>
-      <c r="AA20" s="3">
-        <v>100</v>
       </c>
       <c r="AB20" s="3">
         <v>100</v>
       </c>
       <c r="AC20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD20" s="3">
         <v>0</v>
@@ -1772,102 +1806,108 @@
       <c r="AE20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="E21" s="3">
         <v>6100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>3000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>18700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>11800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>6600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>31900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>11900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>20400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>9200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>38000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>10900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>16100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-12200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>39300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>7900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>8700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-5100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>34700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>12700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>2200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>32000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>9200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>2400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>24400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>900</v>
+        <v>1200</v>
       </c>
       <c r="E22" s="3">
         <v>900</v>
@@ -1876,260 +1916,269 @@
         <v>900</v>
       </c>
       <c r="G22" s="3">
+        <v>900</v>
+      </c>
+      <c r="H22" s="3">
         <v>1000</v>
-      </c>
-      <c r="H22" s="3">
-        <v>900</v>
       </c>
       <c r="I22" s="3">
         <v>900</v>
       </c>
       <c r="J22" s="3">
+        <v>900</v>
+      </c>
+      <c r="K22" s="3">
         <v>1300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>1600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>1800</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>1400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>1300</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>1500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>1200</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>800</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>2300</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>1600</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>1200</v>
-      </c>
-      <c r="Y22" s="3">
-        <v>800</v>
       </c>
       <c r="Z22" s="3">
         <v>800</v>
       </c>
       <c r="AA22" s="3">
+        <v>800</v>
+      </c>
+      <c r="AB22" s="3">
         <v>700</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>400</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>200</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>100</v>
       </c>
-      <c r="AE22" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-13600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-2200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-5300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>9900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-8300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>3100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>23200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>3700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>12000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>29200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>7800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-20300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>31800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-10300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>28000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-4100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>8700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>29000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-1200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>7100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>22900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E24" s="3">
         <v>-200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-1500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>2500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-2100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>5800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>3000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>7500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-5100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>7600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-2700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>7500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-1100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>2200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>10900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>2700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>8800</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2217,186 +2266,195 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-10500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-2000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-3900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>7500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-6200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>2300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>17300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>8900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>21800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>5900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-15200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>24200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-7600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>20500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-3100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>6500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>18100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>4400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>14000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-10500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-2000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-3900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>7400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-6200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>2400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>17400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>9000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>21800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>5900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-15100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>24400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-7600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>20600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-3200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>6400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>18000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>4300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>14000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2484,8 +2542,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2537,8 +2598,8 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>8</v>
+      <c r="T29" s="3">
+        <v>0</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>8</v>
@@ -2555,11 +2616,11 @@
       <c r="Y29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="Z29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA29" s="3">
         <v>1500</v>
-      </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
@@ -2573,8 +2634,11 @@
       <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2662,8 +2726,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2751,8 +2818,11 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2763,76 +2833,76 @@
         <v>-100</v>
       </c>
       <c r="F32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G32" s="3">
         <v>-200</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-100</v>
       </c>
       <c r="H32" s="3">
         <v>-100</v>
       </c>
       <c r="I32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>-200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="O32" s="3">
         <v>-100</v>
       </c>
       <c r="P32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Q32" s="3">
         <v>300</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>-100</v>
       </c>
       <c r="R32" s="3">
         <v>-100</v>
       </c>
       <c r="S32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="T32" s="3">
         <v>0</v>
       </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>-200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-300</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
       <c r="X32" s="3">
         <v>0</v>
       </c>
       <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
         <v>-200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-300</v>
-      </c>
-      <c r="AA32" s="3">
-        <v>-100</v>
       </c>
       <c r="AB32" s="3">
         <v>-100</v>
       </c>
       <c r="AC32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AD32" s="3">
         <v>0</v>
@@ -2840,97 +2910,103 @@
       <c r="AE32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-10500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-2000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-3900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>7400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-6200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>2400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>17400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>9000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>21800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>5900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-15100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>24400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-7600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>20600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-3200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>6400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>19500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>4300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>14000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3018,191 +3094,200 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-10500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-2000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-3900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>7400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-6200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>2400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>17400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>9000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>21800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>5900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-15100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>24400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-7600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>20600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-3200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>6400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>19500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>4300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>14000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45228</v>
+      </c>
+      <c r="E38" s="2">
         <v>45137</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45046</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44955</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44864</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44773</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44682</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44591</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44500</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44409</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44318</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44227</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44136</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44045</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43954</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43863</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43772</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43681</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43590</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43499</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43401</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43310</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43219</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43128</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43037</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>42946</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42855</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42764</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42673</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3234,8 +3319,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3267,97 +3353,101 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E41" s="3">
         <v>11100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>9200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>45500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>9400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>15400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>40400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>77100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>20400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>18900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>26100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>46600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>12800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>19000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>8900</v>
-      </c>
-      <c r="R41" s="3">
-        <v>2200</v>
       </c>
       <c r="S41" s="3">
         <v>2200</v>
       </c>
       <c r="T41" s="3">
+        <v>2200</v>
+      </c>
+      <c r="U41" s="3">
         <v>3500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>13600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>24000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3445,420 +3535,435 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>7900</v>
+      </c>
+      <c r="E43" s="3">
         <v>7800</v>
-      </c>
-      <c r="E43" s="3">
-        <v>8400</v>
       </c>
       <c r="F43" s="3">
         <v>8400</v>
       </c>
       <c r="G43" s="3">
+        <v>8400</v>
+      </c>
+      <c r="H43" s="3">
         <v>10200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>7600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>6900</v>
-      </c>
-      <c r="J43" s="3">
-        <v>7700</v>
       </c>
       <c r="K43" s="3">
         <v>7700</v>
       </c>
       <c r="L43" s="3">
+        <v>7700</v>
+      </c>
+      <c r="M43" s="3">
         <v>4900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>4600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>5300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>7000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>7600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>5400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>3400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>8200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>7100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>8700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>4600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>3200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1700</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1100</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>174000</v>
+      </c>
+      <c r="E44" s="3">
         <v>157100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>145000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>154900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>204700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>164500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>152200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>122700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>165100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>134900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>144200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>149100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>213400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>167600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>175000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>147800</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>183100</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>114800</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>104300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>97700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>131400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>102400</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>98000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>89500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>129500</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>84700</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>75700</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>70400</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>96700</v>
       </c>
     </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>13500</v>
+      </c>
+      <c r="E45" s="3">
         <v>15800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>13900</v>
       </c>
-      <c r="F45" s="3">
-        <v>17000</v>
-      </c>
       <c r="G45" s="3">
+        <v>12800</v>
+      </c>
+      <c r="H45" s="3">
         <v>15700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>15100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>14600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>15100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>13400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>11200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>9700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>8700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>9700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>7600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>7700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>8800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>10700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>12000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>12200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>15100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>13100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>11500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>9800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>9100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>13300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>9500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>5400</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>6400</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>8300</v>
       </c>
     </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>203500</v>
+      </c>
+      <c r="E46" s="3">
         <v>191800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>176500</v>
       </c>
-      <c r="F46" s="3">
-        <v>225900</v>
-      </c>
       <c r="G46" s="3">
+        <v>221700</v>
+      </c>
+      <c r="H46" s="3">
         <v>240000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>202500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>214100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>222500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>206600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>169800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>184600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>209700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>242900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>201800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>197000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>162200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>204300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>137500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>126100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>118200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>150200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>116600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>109600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>101800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>145400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>96100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>95900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>101200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>108200</v>
       </c>
     </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E47" s="3">
         <v>5300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>5400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>5500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>5300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>5800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>6100</v>
-      </c>
-      <c r="J47" s="3">
-        <v>6600</v>
       </c>
       <c r="K47" s="3">
         <v>6600</v>
       </c>
       <c r="L47" s="3">
+        <v>6600</v>
+      </c>
+      <c r="M47" s="3">
         <v>6700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>6300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>6100</v>
-      </c>
-      <c r="O47" s="3">
-        <v>6000</v>
       </c>
       <c r="P47" s="3">
         <v>6000</v>
       </c>
       <c r="Q47" s="3">
+        <v>6000</v>
+      </c>
+      <c r="R47" s="3">
         <v>5700</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>6400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>6500</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>6200</v>
-      </c>
-      <c r="U47" s="3">
-        <v>6300</v>
       </c>
       <c r="V47" s="3">
         <v>6300</v>
@@ -3878,8 +3983,8 @@
       <c r="AA47" s="3">
         <v>6300</v>
       </c>
-      <c r="AB47" s="3" t="s">
-        <v>8</v>
+      <c r="AB47" s="3">
+        <v>6300</v>
       </c>
       <c r="AC47" s="3" t="s">
         <v>8</v>
@@ -3890,97 +3995,103 @@
       <c r="AE47" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>304100</v>
+      </c>
+      <c r="E48" s="3">
         <v>297800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>297700</v>
       </c>
-      <c r="F48" s="3">
-        <v>287300</v>
-      </c>
       <c r="G48" s="3">
+        <v>291500</v>
+      </c>
+      <c r="H48" s="3">
         <v>295900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>278300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>276100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>281100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>289600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>281300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>287200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>295200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>304600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>296600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>301100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>304200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>303800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>284400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>282200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>334200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>165900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>144800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>129200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>109700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>98200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>75700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>62500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>52400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>45300</v>
       </c>
     </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3991,7 +4102,7 @@
         <v>800</v>
       </c>
       <c r="F49" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="G49" s="3">
         <v>900</v>
@@ -4000,13 +4111,13 @@
         <v>900</v>
       </c>
       <c r="I49" s="3">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="J49" s="3">
         <v>600</v>
       </c>
       <c r="K49" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="L49" s="3">
         <v>700</v>
@@ -4027,22 +4138,22 @@
         <v>700</v>
       </c>
       <c r="R49" s="3">
+        <v>700</v>
+      </c>
+      <c r="S49" s="3">
         <v>1700</v>
-      </c>
-      <c r="S49" s="3">
-        <v>700</v>
       </c>
       <c r="T49" s="3">
         <v>700</v>
       </c>
       <c r="U49" s="3">
+        <v>700</v>
+      </c>
+      <c r="V49" s="3">
         <v>400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>700</v>
-      </c>
-      <c r="W49" s="3">
-        <v>400</v>
       </c>
       <c r="X49" s="3">
         <v>400</v>
@@ -4068,8 +4179,11 @@
       <c r="AE49" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4157,8 +4271,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4246,97 +4363,103 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>12700</v>
+      </c>
+      <c r="E52" s="3">
         <v>7400</v>
-      </c>
-      <c r="E52" s="3">
-        <v>7900</v>
       </c>
       <c r="F52" s="3">
         <v>7900</v>
       </c>
       <c r="G52" s="3">
+        <v>7900</v>
+      </c>
+      <c r="H52" s="3">
         <v>5600</v>
-      </c>
-      <c r="H52" s="3">
-        <v>5900</v>
       </c>
       <c r="I52" s="3">
         <v>5900</v>
       </c>
       <c r="J52" s="3">
-        <v>4700</v>
+        <v>5900</v>
       </c>
       <c r="K52" s="3">
         <v>4700</v>
       </c>
       <c r="L52" s="3">
+        <v>4700</v>
+      </c>
+      <c r="M52" s="3">
         <v>4600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>5300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>3900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>3000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>2300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>3500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>4800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>2700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>9400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1200</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1900</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4424,97 +4547,103 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>526000</v>
+      </c>
+      <c r="E54" s="3">
         <v>503100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>488400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>527500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>547700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>493300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>502800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>515600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>508200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>463200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>482200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>514900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>554700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>506200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>505600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>474100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>518100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>434100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>418900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>295300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>324500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>270400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>249000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>223100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>252900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>181700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>160000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>156000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>155600</v>
       </c>
     </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4546,8 +4675,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4579,117 +4709,121 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>53500</v>
+      </c>
+      <c r="E57" s="3">
         <v>59300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>36100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>56500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>77800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>53600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>54500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>45400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>59200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>37700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>40100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>33600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>57100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>40100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>34400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>33100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>55400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>36300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>26700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>25400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>34200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>19500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>14600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>17300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>30100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>17800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>10700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>9300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>19300</v>
       </c>
     </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>39900</v>
+      </c>
+      <c r="E58" s="3">
         <v>3800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>13600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3500</v>
-      </c>
-      <c r="I58" s="3">
-        <v>3400</v>
       </c>
       <c r="J58" s="3">
         <v>3400</v>
@@ -4698,411 +4832,423 @@
         <v>3400</v>
       </c>
       <c r="L58" s="3">
+        <v>3400</v>
+      </c>
+      <c r="M58" s="3">
         <v>3300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>20800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>5800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>5700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>4800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>2200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>3200</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>2100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1600</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>800</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>200</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>600</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>21800</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>100</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>3000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>2400</v>
-      </c>
-      <c r="AC58" s="3">
-        <v>700</v>
       </c>
       <c r="AD58" s="3">
         <v>700</v>
       </c>
       <c r="AE58" s="3">
+        <v>700</v>
+      </c>
+      <c r="AF58" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>47800</v>
+      </c>
+      <c r="E59" s="3">
         <v>44200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>48100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>58100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>49900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>43000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>50200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>67200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>54200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>44700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>49800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>56300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>43500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>39200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>46000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>54500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>38000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>33500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>35200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>26700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>30700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>22800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>33200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>32900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>25700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>17500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>25300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>25000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>17400</v>
       </c>
     </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>141200</v>
+      </c>
+      <c r="E60" s="3">
         <v>107200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>87900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>118300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>141300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>100100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>108200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>116000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>116700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>85700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>110700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>95700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>106300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>84100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>82600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>79800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>95500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>71400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>62700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>52600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>65200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>42800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>69600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>50300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>58800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>37800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>36700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>35100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>38800</v>
       </c>
     </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>60500</v>
+      </c>
+      <c r="E61" s="3">
         <v>61400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>62400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>63300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>64300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>65100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>66000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>66900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>67700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>68600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>69400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>116300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>160700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>141400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>149800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>103500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>156500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>99200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>77500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>67900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>111200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>76900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>35600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>28000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>70000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>20200</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>4800</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>3400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>110500</v>
+      </c>
+      <c r="E62" s="3">
         <v>111000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>114000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>118600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>123500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>103700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>107200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>110000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>118500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>107000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>110100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>112500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>119000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>113200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>112400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>123100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>113100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>110200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>127900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>14700</v>
-      </c>
-      <c r="W62" s="3">
-        <v>5500</v>
       </c>
       <c r="X62" s="3">
         <v>5500</v>
       </c>
       <c r="Y62" s="3">
+        <v>5500</v>
+      </c>
+      <c r="Z62" s="3">
         <v>5400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>5500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>4800</v>
-      </c>
-      <c r="AB62" s="3">
-        <v>3700</v>
       </c>
       <c r="AC62" s="3">
         <v>3700</v>
@@ -5111,10 +5257,13 @@
         <v>3700</v>
       </c>
       <c r="AE62" s="3">
+        <v>3700</v>
+      </c>
+      <c r="AF62" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5202,8 +5351,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5291,8 +5443,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5380,97 +5535,103 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>308900</v>
+      </c>
+      <c r="E66" s="3">
         <v>276500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>261100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>297000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>325800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>265700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>278200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>289700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>300400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>258800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>287800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>321500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>383700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>336500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>342600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>295800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>364600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>280400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>267800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>135000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>185300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>128500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>113900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>87000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>136800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>65300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>48100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>44800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>58700</v>
       </c>
     </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5502,8 +5663,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5591,8 +5753,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5680,8 +5845,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5769,8 +5937,11 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5858,97 +6029,103 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>116800</v>
+      </c>
+      <c r="E72" s="3">
         <v>127300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>129300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>133200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>125700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>131900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>129600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>130900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>113500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>110700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>101700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>101200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>79300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>78400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>72500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>87600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>63200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>63000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>61100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>70600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>50000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>53100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>46700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>48100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>28600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>29400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>25100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>24700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>10700</v>
       </c>
     </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6036,8 +6213,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6125,8 +6305,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6214,97 +6397,103 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>217100</v>
+      </c>
+      <c r="E76" s="3">
         <v>226700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>227300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>230400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>221900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>227600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>224600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>225900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>207800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>204400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>194400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>193500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>171100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>169700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>163100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>178300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>153500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>153700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>151100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>160300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>139200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>141900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>135100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>136100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>116100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>116400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>111900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>111200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>96900</v>
       </c>
     </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6392,191 +6581,200 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45228</v>
+      </c>
+      <c r="E80" s="2">
         <v>45137</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45046</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44955</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44864</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44773</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44682</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44591</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44500</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44409</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44318</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44227</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44136</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44045</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43954</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43863</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43772</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43681</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43590</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43499</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43401</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43310</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43219</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43128</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43037</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>42946</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42855</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42764</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42673</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-10500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-2000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-3900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>7400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-6200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>2400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>17400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>9000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>21800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>5900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-15100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>24400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-7600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>20600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-3200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>6400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>19500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>4300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>14000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6608,97 +6806,101 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E83" s="3">
         <v>7500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>7400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>7900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>7600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>7900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>7500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>7400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>7300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>7200</v>
-      </c>
-      <c r="M83" s="3">
-        <v>7300</v>
       </c>
       <c r="N83" s="3">
         <v>7300</v>
       </c>
       <c r="O83" s="3">
+        <v>7300</v>
+      </c>
+      <c r="P83" s="3">
         <v>7900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>6600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>6700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>6100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>6500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>5000</v>
-      </c>
-      <c r="U83" s="3">
-        <v>4400</v>
       </c>
       <c r="V83" s="3">
         <v>4400</v>
       </c>
       <c r="W83" s="3">
+        <v>4400</v>
+      </c>
+      <c r="X83" s="3">
         <v>3100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>2800</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>2300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>2200</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>1800</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>1700</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>1600</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>1500</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6786,8 +6988,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6875,8 +7080,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6964,8 +7172,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7053,8 +7264,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7142,97 +7356,103 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-29800</v>
+      </c>
+      <c r="E89" s="3">
         <v>12700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-14000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>45400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-9900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-9400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-31700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>59200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>6200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>14100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>12400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>79400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-15800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>20700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-33500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>56000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-39600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>5100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-13100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>54600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-10900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-1600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-11000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>64800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-22800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-8600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-3500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>47000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-27900</v>
       </c>
     </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7264,97 +7484,101 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-10100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-21400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-5400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-14900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-4100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-4800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-3500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-7100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-5800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-8000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-7200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-19100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-12800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-14000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-9000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-17400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-11700</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-8300</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-7600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-6500</v>
       </c>
     </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7442,8 +7666,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7531,97 +7758,103 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-10000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-21300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>1500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-5400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-14900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-4100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-5000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-4100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-6100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-7800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-7000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-9800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-7400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-19000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-13400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-14000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-11900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-17300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-18900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-7700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-7900</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-7200</v>
       </c>
     </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7653,8 +7886,9 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7742,8 +7976,11 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7831,8 +8068,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7920,8 +8160,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8009,97 +8252,103 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>35200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-10700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>9300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1100</v>
-      </c>
-      <c r="J100" s="3">
-        <v>-700</v>
       </c>
       <c r="K100" s="3">
         <v>-700</v>
       </c>
       <c r="L100" s="3">
+        <v>-700</v>
+      </c>
+      <c r="M100" s="3">
         <v>-18300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-31600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-44300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>11800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-5800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>44700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-51500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>45200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>5500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>22400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-47300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>29500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>14400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>22000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-51800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>39300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>16400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-15300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>11900</v>
       </c>
     </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8187,93 +8436,99 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E102" s="3">
         <v>1900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-36300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>36100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-6000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-25000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-36700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>57300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-7100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-21200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>34400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-6400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>9900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>7100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-2200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>3600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-3000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>1200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-11100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-10500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>23900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-23100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DLTH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DLTH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="92">
   <si>
     <t>DLTH</t>
   </si>
@@ -656,418 +656,443 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45410</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45319</v>
+      </c>
+      <c r="F7" s="2">
         <v>45228</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45137</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45046</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44955</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44864</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44773</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44682</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44591</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44500</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44409</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44318</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44227</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44136</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44045</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43954</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43863</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43772</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43681</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43590</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43499</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43401</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43310</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43219</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43128</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43037</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42946</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42855</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42764</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42673</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>116700</v>
+      </c>
+      <c r="E8" s="3">
+        <v>245600</v>
+      </c>
+      <c r="F8" s="3">
         <v>138200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>139100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>123800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>241800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>147100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>141500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>122900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>270800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>145300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>149100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>133400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>256000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>135500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>137400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>109900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>259600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>119800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>122000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>114200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>250500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>106700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>110700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>100200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>217800</v>
-      </c>
-      <c r="AB8" s="3">
-        <v>83700</v>
-      </c>
-      <c r="AC8" s="3">
-        <v>86200</v>
       </c>
       <c r="AD8" s="3">
         <v>83700</v>
       </c>
       <c r="AE8" s="3">
+        <v>86200</v>
+      </c>
+      <c r="AF8" s="3">
+        <v>83700</v>
+      </c>
+      <c r="AG8" s="3">
         <v>174700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>67000</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>55100</v>
+      </c>
+      <c r="E9" s="3">
+        <v>127200</v>
+      </c>
+      <c r="F9" s="3">
         <v>68800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>67600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>58100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>117900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>70200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>65900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>55800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>125100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>61600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>67700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>66900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>120300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>64500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>64900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>57600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>122600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>54400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>57200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>53300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>119300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>45700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>48400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>44300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>101800</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>36300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>37300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>35000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>77900</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>28300</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>61600</v>
+      </c>
+      <c r="E10" s="3">
+        <v>118400</v>
+      </c>
+      <c r="F10" s="3">
         <v>69400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>71500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>65700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>123900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>76900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>75600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>67100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>145700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>83700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>81400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>66500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>135700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>71000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>72500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>52300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>137000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>65400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>64800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>60900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>131200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>61000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>62300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>55900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>116000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>47400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>48900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>48700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>96800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>38700</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1100,8 +1125,10 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1192,8 +1219,14 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1284,8 +1317,14 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1313,11 +1352,11 @@
       <c r="K14" s="3">
         <v>0</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>8</v>
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>8</v>
@@ -1331,14 +1370,14 @@
       <c r="Q14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R14" s="3">
-        <v>1600</v>
+      <c r="R14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>8</v>
+      <c r="T14" s="3">
+        <v>1600</v>
       </c>
       <c r="U14" s="3" t="s">
         <v>8</v>
@@ -1352,11 +1391,11 @@
       <c r="X14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="3">
-        <v>0</v>
+      <c r="Y14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA14" s="3">
         <v>0</v>
@@ -1376,8 +1415,14 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1421,28 +1466,28 @@
         <v>800</v>
       </c>
       <c r="Q15" s="3">
+        <v>800</v>
+      </c>
+      <c r="R15" s="3">
+        <v>800</v>
+      </c>
+      <c r="S15" s="3">
         <v>900</v>
       </c>
-      <c r="R15" s="3">
+      <c r="T15" s="3">
         <v>700</v>
       </c>
-      <c r="S15" s="3">
+      <c r="U15" s="3">
         <v>200</v>
       </c>
-      <c r="T15" s="3">
+      <c r="V15" s="3">
         <v>500</v>
       </c>
-      <c r="U15" s="3">
+      <c r="W15" s="3">
         <v>500</v>
       </c>
-      <c r="V15" s="3">
+      <c r="X15" s="3">
         <v>100</v>
-      </c>
-      <c r="W15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X15" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Y15" s="3" t="s">
         <v>8</v>
@@ -1450,11 +1495,11 @@
       <c r="Z15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA15" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB15" s="3">
-        <v>0</v>
+      <c r="AA15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC15" s="3">
         <v>0</v>
@@ -1468,8 +1513,14 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1499,192 +1550,206 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>125700</v>
+      </c>
+      <c r="E17" s="3">
+        <v>236000</v>
+      </c>
+      <c r="F17" s="3">
         <v>150600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>140500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>128300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>231100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>154500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>137600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>123800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>246500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>140400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>136000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>131500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>225400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>132700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>127600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>128900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>226500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>118400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>118200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>123900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>220400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>109300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>100800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>100500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>188300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>84300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>78800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>82900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>151800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>66200</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="E18" s="3">
+        <v>9600</v>
+      </c>
+      <c r="F18" s="3">
         <v>-12400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-1400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-4500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>10700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-7400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>3900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>24300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>4900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>13100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>1900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>30600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>2800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>9800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-19000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>33100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>1400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>3800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-9700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>30100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-2600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>9900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>29500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>-600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>7400</v>
-      </c>
-      <c r="AD18" s="3">
-        <v>800</v>
-      </c>
-      <c r="AE18" s="3">
-        <v>22900</v>
       </c>
       <c r="AF18" s="3">
         <v>800</v>
       </c>
-    </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG18" s="3">
+        <v>22900</v>
+      </c>
+      <c r="AH18" s="3">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1717,468 +1782,500 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E20" s="3">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="F20" s="3">
         <v>100</v>
       </c>
       <c r="G20" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H20" s="3">
         <v>100</v>
       </c>
       <c r="I20" s="3">
+        <v>200</v>
+      </c>
+      <c r="J20" s="3">
         <v>100</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
+        <v>100</v>
+      </c>
+      <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-300</v>
-      </c>
-      <c r="M20" s="3">
-        <v>100</v>
-      </c>
-      <c r="N20" s="3">
-        <v>0</v>
       </c>
       <c r="O20" s="3">
         <v>100</v>
       </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>100</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>-300</v>
       </c>
       <c r="R20" s="3">
         <v>100</v>
       </c>
       <c r="S20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="T20" s="3">
         <v>100</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
         <v>200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>300</v>
       </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
       <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="3">
         <v>200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>100</v>
       </c>
-      <c r="AD20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE20" s="3">
-        <v>0</v>
-      </c>
       <c r="AF20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E21" s="3">
+        <v>18900</v>
+      </c>
+      <c r="F21" s="3">
         <v>-3800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>6100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>3000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>18700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>11800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>6600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>31900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>11900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>20400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>9200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>38000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>10900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>16100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-12200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>39300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>7900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>8700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>-5100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>34700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>12700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>2200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>32000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>1300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>9200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>2400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>24400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E22" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F22" s="3">
         <v>1200</v>
-      </c>
-      <c r="E22" s="3">
-        <v>900</v>
-      </c>
-      <c r="F22" s="3">
-        <v>900</v>
       </c>
       <c r="G22" s="3">
         <v>900</v>
       </c>
       <c r="H22" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="I22" s="3">
         <v>900</v>
       </c>
       <c r="J22" s="3">
+        <v>1000</v>
+      </c>
+      <c r="K22" s="3">
         <v>900</v>
-      </c>
-      <c r="K22" s="3">
-        <v>1300</v>
       </c>
       <c r="L22" s="3">
         <v>900</v>
       </c>
       <c r="M22" s="3">
+        <v>1300</v>
+      </c>
+      <c r="N22" s="3">
+        <v>900</v>
+      </c>
+      <c r="O22" s="3">
         <v>1200</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>1300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>1500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>1600</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>1800</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>1400</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>1300</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>1500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>1200</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>800</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>2300</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>1600</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>1200</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>800</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>800</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>700</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>400</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AF22" s="3">
         <v>200</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AG22" s="3">
         <v>100</v>
       </c>
-      <c r="AF22" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-9900</v>
+      </c>
+      <c r="E23" s="3">
+        <v>9100</v>
+      </c>
+      <c r="F23" s="3">
         <v>-13600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-2200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-5300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>9900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-8300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>3100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-1800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>23200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>3700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>12000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>29200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>1300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>7800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-20300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>31800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>2500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-10300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>28000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-4100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>8700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>29000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-1200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>7100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>22900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E24" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F24" s="3">
         <v>-3100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>-200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>-1500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>2500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>-2100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>-400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>5800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>3000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>7500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>1900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>-5100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>7600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>-200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>-2700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>7500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>-1100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>2200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>-200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>10900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>-500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>2700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>8800</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2269,192 +2366,210 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="E26" s="3">
+        <v>7000</v>
+      </c>
+      <c r="F26" s="3">
         <v>-10500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-2000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-3900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>7500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-6200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>2300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-1300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>17300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>2800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>8900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>21800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>5900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-15200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>24200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>1800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-7600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>20500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-3100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>6500</v>
-      </c>
-      <c r="Z26" s="3">
-        <v>-700</v>
-      </c>
-      <c r="AA26" s="3">
-        <v>18100</v>
       </c>
       <c r="AB26" s="3">
         <v>-700</v>
       </c>
       <c r="AC26" s="3">
+        <v>18100</v>
+      </c>
+      <c r="AD26" s="3">
+        <v>-700</v>
+      </c>
+      <c r="AE26" s="3">
         <v>4400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>14000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="E27" s="3">
+        <v>7000</v>
+      </c>
+      <c r="F27" s="3">
         <v>-10500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-2000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-3900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>7400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-6200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>2400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-1300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>17400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>2800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>9000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>21800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>5900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-15100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>24400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>1900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-7600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>20600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-3200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>6400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>18000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>4300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>14000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2545,8 +2660,14 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2601,11 +2722,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V29" s="3" t="s">
-        <v>8</v>
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>8</v>
@@ -2619,14 +2740,14 @@
       <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA29" s="3">
-        <v>1500</v>
+      <c r="AA29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
+      <c r="AC29" s="3">
+        <v>1500</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
@@ -2637,8 +2758,14 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2729,8 +2856,14 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2821,192 +2954,210 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="E32" s="3">
-        <v>-100</v>
+        <v>-600</v>
       </c>
       <c r="F32" s="3">
         <v>-100</v>
       </c>
       <c r="G32" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="H32" s="3">
         <v>-100</v>
       </c>
       <c r="I32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J32" s="3">
         <v>-100</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>300</v>
-      </c>
-      <c r="M32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="N32" s="3">
-        <v>0</v>
       </c>
       <c r="O32" s="3">
         <v>-100</v>
       </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-100</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>300</v>
       </c>
       <c r="R32" s="3">
         <v>-100</v>
       </c>
       <c r="S32" s="3">
+        <v>300</v>
+      </c>
+      <c r="T32" s="3">
         <v>-100</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
         <v>-200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-300</v>
       </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
       <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="3">
         <v>-200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>-100</v>
       </c>
-      <c r="AD32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE32" s="3">
-        <v>0</v>
-      </c>
       <c r="AF32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="E33" s="3">
+        <v>7000</v>
+      </c>
+      <c r="F33" s="3">
         <v>-10500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-2000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-3900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>7400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-6200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>2400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-1300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>17400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>2800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>9000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>21800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>5900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-15100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>24400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>1900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-7600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>20600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-3200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>6400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>19500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>4300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>14000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3097,197 +3248,215 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="E35" s="3">
+        <v>7000</v>
+      </c>
+      <c r="F35" s="3">
         <v>-10500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-2000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-3900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>7400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-6200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>2400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-1300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>17400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>2800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>9000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>21800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>5900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-15100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>24400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>1900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-7600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>20600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-3200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>6400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>19500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>4300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>14000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45410</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45319</v>
+      </c>
+      <c r="F38" s="2">
         <v>45228</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45137</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45046</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44955</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44864</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44773</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44682</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44591</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44500</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44409</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44318</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44227</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44136</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44045</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43954</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43863</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43772</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43681</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43590</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43499</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43401</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43310</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43219</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43128</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43037</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42946</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42855</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42764</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42673</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3320,8 +3489,10 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3354,100 +3525,108 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E41" s="3">
+        <v>32200</v>
+      </c>
+      <c r="F41" s="3">
         <v>8200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>11100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>9200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>45500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>9400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>15400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>40400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>77100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>20400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>18900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>26100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>46600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>12800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>19000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>8900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>2200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>2200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>3500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>1000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>2500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>2400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>1200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>2900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>1000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>1400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>13600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>24000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3538,438 +3717,468 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>12800</v>
+      </c>
+      <c r="E43" s="3">
+        <v>9400</v>
+      </c>
+      <c r="F43" s="3">
         <v>7900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>7800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>8400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>8400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>10200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>7600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>6900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>7700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>7700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>4900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>4600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>5300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>7000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>7600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>5400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>3400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>8200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>7100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>8700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>4600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>3200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>1700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>1100</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>400</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>136400</v>
+      </c>
+      <c r="E44" s="3">
+        <v>125800</v>
+      </c>
+      <c r="F44" s="3">
         <v>174000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>157100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>145000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>154900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>204700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>164500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>152200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>122700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>165100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>134900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>144200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>149100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>213400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>167600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>175000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>147800</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>183100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>114800</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>104300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>97700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>131400</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>102400</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>98000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>89500</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>129500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>84700</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>75700</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>70400</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>96700</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>15400</v>
+      </c>
+      <c r="E45" s="3">
+        <v>13700</v>
+      </c>
+      <c r="F45" s="3">
         <v>13500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>15800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>13900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>12800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>15700</v>
-      </c>
-      <c r="I45" s="3">
-        <v>15100</v>
-      </c>
-      <c r="J45" s="3">
-        <v>14600</v>
       </c>
       <c r="K45" s="3">
         <v>15100</v>
       </c>
       <c r="L45" s="3">
+        <v>14600</v>
+      </c>
+      <c r="M45" s="3">
+        <v>15100</v>
+      </c>
+      <c r="N45" s="3">
         <v>13400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>11200</v>
-      </c>
-      <c r="N45" s="3">
-        <v>9700</v>
-      </c>
-      <c r="O45" s="3">
-        <v>8700</v>
       </c>
       <c r="P45" s="3">
         <v>9700</v>
       </c>
       <c r="Q45" s="3">
+        <v>8700</v>
+      </c>
+      <c r="R45" s="3">
+        <v>9700</v>
+      </c>
+      <c r="S45" s="3">
         <v>7600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>7700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>8800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>10700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>12000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>12200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>15100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>13100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>11500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>9800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>9100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>13300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>9500</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>5400</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>6400</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>8300</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>171400</v>
+      </c>
+      <c r="E46" s="3">
+        <v>181000</v>
+      </c>
+      <c r="F46" s="3">
         <v>203500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>191800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>176500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>221700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>240000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>202500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>214100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>222500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>206600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>169800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>184600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>209700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>242900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>201800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>197000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>162200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>204300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>137500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>126100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>118200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>150200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>116600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>109600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>101800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>145400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>96100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>95900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>101200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>108200</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E47" s="3">
+        <v>5000</v>
+      </c>
+      <c r="F47" s="3">
         <v>4900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>5300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>5400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>5500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>5300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>5800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>6100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>6600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>6600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>6700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>6300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>6100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>6000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>6000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>5700</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>6400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>6500</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>6200</v>
-      </c>
-      <c r="V47" s="3">
-        <v>6300</v>
-      </c>
-      <c r="W47" s="3">
-        <v>6300</v>
       </c>
       <c r="X47" s="3">
         <v>6300</v>
@@ -3986,11 +4195,11 @@
       <c r="AB47" s="3">
         <v>6300</v>
       </c>
-      <c r="AC47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD47" s="3" t="s">
-        <v>8</v>
+      <c r="AC47" s="3">
+        <v>6300</v>
+      </c>
+      <c r="AD47" s="3">
+        <v>6300</v>
       </c>
       <c r="AE47" s="3" t="s">
         <v>8</v>
@@ -3998,100 +4207,112 @@
       <c r="AF47" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH47" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>282400</v>
+      </c>
+      <c r="E48" s="3">
+        <v>294500</v>
+      </c>
+      <c r="F48" s="3">
         <v>304100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>297800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>297700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>291500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>295900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>278300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>276100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>281100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>289600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>281300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>287200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>295200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>304600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>296600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>301100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>304200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>303800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>284400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>282200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>334200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>165900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>144800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>129200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>109700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>98200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>75700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>62500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>52400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>45300</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4105,25 +4326,25 @@
         <v>800</v>
       </c>
       <c r="G49" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="H49" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="I49" s="3">
         <v>900</v>
       </c>
       <c r="J49" s="3">
+        <v>900</v>
+      </c>
+      <c r="K49" s="3">
+        <v>900</v>
+      </c>
+      <c r="L49" s="3">
         <v>600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>600</v>
-      </c>
-      <c r="L49" s="3">
-        <v>700</v>
-      </c>
-      <c r="M49" s="3">
-        <v>700</v>
       </c>
       <c r="N49" s="3">
         <v>700</v>
@@ -4141,16 +4362,16 @@
         <v>700</v>
       </c>
       <c r="S49" s="3">
-        <v>1700</v>
+        <v>700</v>
       </c>
       <c r="T49" s="3">
         <v>700</v>
       </c>
       <c r="U49" s="3">
+        <v>1700</v>
+      </c>
+      <c r="V49" s="3">
         <v>700</v>
-      </c>
-      <c r="V49" s="3">
-        <v>400</v>
       </c>
       <c r="W49" s="3">
         <v>700</v>
@@ -4159,7 +4380,7 @@
         <v>400</v>
       </c>
       <c r="Y49" s="3">
-        <v>400</v>
+        <v>700</v>
       </c>
       <c r="Z49" s="3">
         <v>400</v>
@@ -4182,8 +4403,14 @@
       <c r="AF49" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3">
+        <v>400</v>
+      </c>
+      <c r="AH49" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4274,8 +4501,14 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4366,100 +4599,112 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>9200</v>
+      </c>
+      <c r="F52" s="3">
         <v>12700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>7400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>7900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>7900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>5600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>5900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>5900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>4700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>4700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>4600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>3400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>3300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>1100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>1200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>2900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>5300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>3900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>3000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>1700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>2300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>3500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>4800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>2700</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>9400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>1200</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>1900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4550,100 +4795,112 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>471400</v>
+      </c>
+      <c r="E54" s="3">
+        <v>490500</v>
+      </c>
+      <c r="F54" s="3">
         <v>526000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>503100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>488400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>527500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>547700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>493300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>502800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>515600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>508200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>463200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>482200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>514900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>554700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>506200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>505600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>474100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>518100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>434100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>418900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>295300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>324500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>270400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>249000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>223100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>252900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>181700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>160000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>156000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>155600</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4676,8 +4933,10 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4710,560 +4969,598 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>37400</v>
+      </c>
+      <c r="E57" s="3">
+        <v>51100</v>
+      </c>
+      <c r="F57" s="3">
         <v>53500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>59300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>36100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>56500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>77800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>53600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>54500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>45400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>59200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>37700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>40100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>33600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>57100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>40100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>34400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>33100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>55400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>36300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>26700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>25400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>34200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>19500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>14600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>17300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>30100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>17800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>10700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>9300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>19300</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E58" s="3">
+        <v>4000</v>
+      </c>
+      <c r="F58" s="3">
         <v>39900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>3800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>3700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>3600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>13600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>3500</v>
-      </c>
-      <c r="J58" s="3">
-        <v>3400</v>
-      </c>
-      <c r="K58" s="3">
-        <v>3400</v>
       </c>
       <c r="L58" s="3">
         <v>3400</v>
       </c>
       <c r="M58" s="3">
+        <v>3400</v>
+      </c>
+      <c r="N58" s="3">
+        <v>3400</v>
+      </c>
+      <c r="O58" s="3">
         <v>3300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>20800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>5800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>5700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>4800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>2200</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>3200</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>2100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>1600</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>800</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>1000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>200</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>600</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>21800</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>100</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>3000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>2400</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>700</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>700</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AH58" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>43000</v>
+      </c>
+      <c r="E59" s="3">
+        <v>47300</v>
+      </c>
+      <c r="F59" s="3">
         <v>47800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>44200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>48100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>58100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>49900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>43000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>50200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>67200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>54200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>44700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>49800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>56300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>43500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>39200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>46000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>54500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>38000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>33500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>35200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>26700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>30700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>22800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>33200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>32900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>25700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>17500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>25300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>25000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>17400</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>95500</v>
+      </c>
+      <c r="E60" s="3">
+        <v>102400</v>
+      </c>
+      <c r="F60" s="3">
         <v>141200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>107200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>87900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>118300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>141300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>100100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>108200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>116000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>116700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>85700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>110700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>95700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>106300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>84100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>82600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>79800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>95500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>71400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>62700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>52600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>65200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>42800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>69600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>50300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>58800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>37800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>36700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>35100</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>38800</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>58400</v>
+      </c>
+      <c r="E61" s="3">
+        <v>59400</v>
+      </c>
+      <c r="F61" s="3">
         <v>60500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>61400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>62400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>63300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>64300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>65100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>66000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>66900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>67700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>68600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>69400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>116300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>160700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>141400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>149800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>103500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>156500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>99200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>77500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>67900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>111200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>76900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>35600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>28000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>70000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>20200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>4800</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>3400</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>102200</v>
+      </c>
+      <c r="E62" s="3">
+        <v>106400</v>
+      </c>
+      <c r="F62" s="3">
         <v>110500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>111000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>114000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>118600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>123500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>103700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>107200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>110000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>118500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>107000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>110100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>112500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>119000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>113200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>112400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>123100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>113100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>110200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>127900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>14700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>5500</v>
-      </c>
-      <c r="Y62" s="3">
-        <v>5500</v>
-      </c>
-      <c r="Z62" s="3">
-        <v>5400</v>
       </c>
       <c r="AA62" s="3">
         <v>5500</v>
       </c>
       <c r="AB62" s="3">
+        <v>5400</v>
+      </c>
+      <c r="AC62" s="3">
+        <v>5500</v>
+      </c>
+      <c r="AD62" s="3">
         <v>4800</v>
-      </c>
-      <c r="AC62" s="3">
-        <v>3700</v>
-      </c>
-      <c r="AD62" s="3">
-        <v>3700</v>
       </c>
       <c r="AE62" s="3">
         <v>3700</v>
       </c>
       <c r="AF62" s="3">
+        <v>3700</v>
+      </c>
+      <c r="AG62" s="3">
+        <v>3700</v>
+      </c>
+      <c r="AH62" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5354,8 +5651,14 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5446,8 +5749,14 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5538,100 +5847,112 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>253000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>265200</v>
+      </c>
+      <c r="F66" s="3">
         <v>308900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>276500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>261100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>297000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>325800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>265700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>278200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>289700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>300400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>258800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>287800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>321500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>383700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>336500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>342600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>295800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>364600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>280400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>267800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>135000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>185300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>128500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>113900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>87000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>136800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>65300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>48100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>44800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>58700</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5664,8 +5985,10 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5756,8 +6079,14 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5848,8 +6177,14 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5940,8 +6275,14 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6032,100 +6373,112 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>115900</v>
+      </c>
+      <c r="E72" s="3">
+        <v>123800</v>
+      </c>
+      <c r="F72" s="3">
         <v>116800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>127300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>129300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>133200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>125700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>131900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>129600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>130900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>113500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>110700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>101700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>101200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>79300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>78400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>72500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>87600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>63200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>63000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>61100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>70600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>50000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>53100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>46700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>48100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>28600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>29400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>25100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>24700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>10700</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6216,8 +6569,14 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6308,8 +6667,14 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6400,100 +6765,112 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>218400</v>
+      </c>
+      <c r="E76" s="3">
+        <v>225200</v>
+      </c>
+      <c r="F76" s="3">
         <v>217100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>226700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>227300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>230400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>221900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>227600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>224600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>225900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>207800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>204400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>194400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>193500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>171100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>169700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>163100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>178300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>153500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>153700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>151100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>160300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>139200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>141900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>135100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>136100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>116100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>116400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>111900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>111200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>96900</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6584,197 +6961,215 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45410</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45319</v>
+      </c>
+      <c r="F80" s="2">
         <v>45228</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45137</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45046</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44955</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44864</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44773</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44682</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44591</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44500</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44409</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44318</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44227</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44136</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44045</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43954</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43863</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43772</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43681</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43590</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43499</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43401</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43310</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43219</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43128</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43037</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42946</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42855</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42764</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42673</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="E81" s="3">
+        <v>7000</v>
+      </c>
+      <c r="F81" s="3">
         <v>-10500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-2000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-3900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>7400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-6200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>2400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-1300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>17400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>2800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>9000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>21800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>5900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-15100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>24400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>1900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-7600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>20600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-3200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>6400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>19500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>4300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>14000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6807,100 +7202,108 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E83" s="3">
+        <v>8700</v>
+      </c>
+      <c r="F83" s="3">
         <v>8600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>7500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>7400</v>
-      </c>
-      <c r="G83" s="3">
-        <v>7900</v>
-      </c>
-      <c r="H83" s="3">
-        <v>7600</v>
       </c>
       <c r="I83" s="3">
         <v>7900</v>
       </c>
       <c r="J83" s="3">
+        <v>7600</v>
+      </c>
+      <c r="K83" s="3">
+        <v>7900</v>
+      </c>
+      <c r="L83" s="3">
         <v>7500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>7400</v>
-      </c>
-      <c r="L83" s="3">
-        <v>7300</v>
-      </c>
-      <c r="M83" s="3">
-        <v>7200</v>
       </c>
       <c r="N83" s="3">
         <v>7300</v>
       </c>
       <c r="O83" s="3">
+        <v>7200</v>
+      </c>
+      <c r="P83" s="3">
         <v>7300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
+        <v>7300</v>
+      </c>
+      <c r="R83" s="3">
         <v>7900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>6600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>6700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>6100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>6500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>5000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>4400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>4400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>3100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>2800</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>2300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>2200</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>1800</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>1700</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>1600</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>1500</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6991,8 +7394,14 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7083,8 +7492,14 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7175,8 +7590,14 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7267,8 +7688,14 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7359,100 +7786,112 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-33700</v>
+      </c>
+      <c r="E89" s="3">
+        <v>69700</v>
+      </c>
+      <c r="F89" s="3">
         <v>-29800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>12700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-14000</v>
       </c>
-      <c r="G89" s="3">
-        <v>45400</v>
-      </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
+        <v>49600</v>
+      </c>
+      <c r="J89" s="3">
         <v>-9900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-9400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-31700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>59200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>6200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>14100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>12400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>79400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-15800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>20700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-33500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>56000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-39600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>5100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-13100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>54600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-10900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-11000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>64800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>-22800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>-8600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>-3500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>47000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>-27900</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7485,100 +7924,108 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="F91" s="3">
         <v>-8500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-10100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-21400</v>
       </c>
-      <c r="G91" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="J91" s="3">
         <v>-5400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-14900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-3900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-1200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-4100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-3000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-2000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-4800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-4100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-3500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-7100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-5800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-8000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-7200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-19100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-12800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-14000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-9000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-17400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-11700</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-8300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-7600</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-6500</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7669,8 +8116,14 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7761,100 +8214,112 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="F94" s="3">
         <v>-8400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-10000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-21300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>1500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-5400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-14900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-3800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-1200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-4100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-2900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-2000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-5000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-4100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-6100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-7800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-7000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-9800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-7400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-19000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-13400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-14000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-11900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-17300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-18900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-7700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-7900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-7200</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7887,8 +8352,10 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7979,8 +8446,14 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8071,8 +8544,14 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8163,8 +8642,14 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8255,100 +8740,112 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>9800</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-36800</v>
+      </c>
+      <c r="F100" s="3">
         <v>35200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-1000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-10700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>9300</v>
-      </c>
-      <c r="I100" s="3">
-        <v>-700</v>
-      </c>
-      <c r="J100" s="3">
-        <v>-1100</v>
       </c>
       <c r="K100" s="3">
         <v>-700</v>
       </c>
       <c r="L100" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="M100" s="3">
         <v>-700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
+        <v>-700</v>
+      </c>
+      <c r="O100" s="3">
         <v>-18300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-31600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-44300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>11800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-5800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>44700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-51500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>45200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>5500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>22400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-47300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>29500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>14400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>22000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-51800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>39300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>16400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>-15300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>11900</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8439,96 +8936,108 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-25400</v>
+      </c>
+      <c r="E102" s="3">
+        <v>24000</v>
+      </c>
+      <c r="F102" s="3">
         <v>-3000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>1900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-36300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>36100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-6000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-25000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-36700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>57300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>1500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-7100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-21200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>34400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-6400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>9900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>7100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-1700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-2200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>3600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-3000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>1200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-11100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>-10500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>23900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>-23100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DLTH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DLTH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="92">
   <si>
     <t>DLTH</t>
   </si>
@@ -656,443 +656,456 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45501</v>
+      </c>
+      <c r="E7" s="2">
         <v>45410</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45319</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45228</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45137</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45046</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44955</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44864</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44773</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44682</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44591</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44500</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44409</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44318</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44227</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44136</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44045</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43954</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43863</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43772</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43681</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43590</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43499</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43401</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43310</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43219</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43128</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43037</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42946</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42855</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42764</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42673</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>141600</v>
+      </c>
+      <c r="E8" s="3">
         <v>116700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>245600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>138200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>139100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>123800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>241800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>147100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>141500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>122900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>270800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>145300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>149100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>133400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>256000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>135500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>137400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>109900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>259600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>119800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>122000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>114200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>250500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>106700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>110700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>100200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>217800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>83700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>86200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>83700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>174700</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>67000</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>67600</v>
+      </c>
+      <c r="E9" s="3">
         <v>55100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>127200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>68800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>67600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>58100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>117900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>70200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>65900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>55800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>125100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>61600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>67700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>66900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>120300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>64500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>64900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>57600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>122600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>54400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>57200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>53300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>119300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>45700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>48400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>44300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>101800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>36300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>37300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>35000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>77900</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>28300</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>74000</v>
+      </c>
+      <c r="E10" s="3">
         <v>61600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>118400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>69400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>71500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>65700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>123900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>76900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>75600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>67100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>145700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>83700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>81400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>66500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>135700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>71000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>72500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>52300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>137000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>65400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>64800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>60900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>131200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>61000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>62300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>55900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>116000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>47400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>48900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>48700</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>96800</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>38700</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1127,8 +1140,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1225,8 +1239,11 @@
       <c r="AH12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1323,31 +1340,34 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+        <v>1600</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1358,8 +1378,8 @@
       <c r="M14" s="3">
         <v>0</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>8</v>
+      <c r="N14" s="3">
+        <v>0</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>8</v>
@@ -1376,11 +1396,11 @@
       <c r="S14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T14" s="3">
+      <c r="T14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U14" s="3">
         <v>1600</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>8</v>
@@ -1397,8 +1417,8 @@
       <c r="Z14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
+      <c r="AA14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB14" s="3">
         <v>0</v>
@@ -1421,8 +1441,11 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1472,25 +1495,25 @@
         <v>800</v>
       </c>
       <c r="S15" s="3">
+        <v>800</v>
+      </c>
+      <c r="T15" s="3">
         <v>900</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>700</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>200</v>
-      </c>
-      <c r="V15" s="3">
-        <v>500</v>
       </c>
       <c r="W15" s="3">
         <v>500</v>
       </c>
       <c r="X15" s="3">
+        <v>500</v>
+      </c>
+      <c r="Y15" s="3">
         <v>100</v>
-      </c>
-      <c r="Y15" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Z15" s="3" t="s">
         <v>8</v>
@@ -1501,8 +1524,8 @@
       <c r="AB15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC15" s="3">
-        <v>0</v>
+      <c r="AC15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD15" s="3">
         <v>0</v>
@@ -1519,8 +1542,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1552,204 +1578,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>145500</v>
+      </c>
+      <c r="E17" s="3">
         <v>125700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>236000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>150600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>140500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>128300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>231100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>154500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>137600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>123800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>246500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>140400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>136000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>131500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>225400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>132700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>127600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>128900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>226500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>118400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>118200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>123900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>220400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>109300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>100800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>100500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>188300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>84300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>78800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>82900</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>151800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>66200</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E18" s="3">
         <v>-9000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>9600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-12400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-4500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>10700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-7400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>24300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>4900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>13100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>30600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>9800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-19000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>33100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>3800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-9700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>30100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-2600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>9900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>29500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>7400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>22900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1784,19 +1817,20 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>600</v>
-      </c>
-      <c r="F20" s="3">
-        <v>100</v>
       </c>
       <c r="G20" s="3">
         <v>100</v>
@@ -1805,76 +1839,76 @@
         <v>100</v>
       </c>
       <c r="I20" s="3">
+        <v>100</v>
+      </c>
+      <c r="J20" s="3">
         <v>200</v>
-      </c>
-      <c r="J20" s="3">
-        <v>100</v>
       </c>
       <c r="K20" s="3">
         <v>100</v>
       </c>
       <c r="L20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>100</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R20" s="3">
         <v>100</v>
       </c>
       <c r="S20" s="3">
+        <v>100</v>
+      </c>
+      <c r="T20" s="3">
         <v>-300</v>
-      </c>
-      <c r="T20" s="3">
-        <v>100</v>
       </c>
       <c r="U20" s="3">
         <v>100</v>
       </c>
       <c r="V20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W20" s="3">
         <v>0</v>
       </c>
       <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
         <v>200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>300</v>
       </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
       <c r="AA20" s="3">
         <v>0</v>
       </c>
       <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="3">
         <v>200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>300</v>
-      </c>
-      <c r="AD20" s="3">
-        <v>100</v>
       </c>
       <c r="AE20" s="3">
         <v>100</v>
       </c>
       <c r="AF20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AG20" s="3">
         <v>0</v>
@@ -1882,106 +1916,112 @@
       <c r="AH20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E21" s="3">
         <v>-700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>18900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-3800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>6100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>3000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>18700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>11800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>6600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>31900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>11900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>20400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>9200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>38000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>10900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>16100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-12200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>39300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>7900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>8700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-5100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>34700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>12700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>2200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>32000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>9200</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>2400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>24400</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1989,13 +2029,13 @@
         <v>1000</v>
       </c>
       <c r="E22" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F22" s="3">
         <v>1100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>1200</v>
-      </c>
-      <c r="G22" s="3">
-        <v>900</v>
       </c>
       <c r="H22" s="3">
         <v>900</v>
@@ -2004,278 +2044,287 @@
         <v>900</v>
       </c>
       <c r="J22" s="3">
+        <v>900</v>
+      </c>
+      <c r="K22" s="3">
         <v>1000</v>
-      </c>
-      <c r="K22" s="3">
-        <v>900</v>
       </c>
       <c r="L22" s="3">
         <v>900</v>
       </c>
       <c r="M22" s="3">
+        <v>900</v>
+      </c>
+      <c r="N22" s="3">
         <v>1300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>1200</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>1300</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>1500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>1600</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>1800</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>1400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>1300</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>1500</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>1200</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>800</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>2300</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>1600</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>1200</v>
-      </c>
-      <c r="AB22" s="3">
-        <v>800</v>
       </c>
       <c r="AC22" s="3">
         <v>800</v>
       </c>
       <c r="AD22" s="3">
+        <v>800</v>
+      </c>
+      <c r="AE22" s="3">
         <v>700</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>400</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>200</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>100</v>
       </c>
-      <c r="AH22" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-9900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>9100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-13600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-2200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-5300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>9900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-8300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>3100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-1800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>23200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>3700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>12000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>29200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>7800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-20300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>31800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>2500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-10300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>28000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-4100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>8700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>29000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-1200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>7100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>22900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-2100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>2100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-3100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-1500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-2100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>5800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>3000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>7500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-5100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>7600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-2700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>7500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-1100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>2200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>10900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>2700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>8800</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2372,204 +2421,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-7900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>7000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-10500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-2000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-3900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>7500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-6200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-1300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>17300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>8900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>21800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>5900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-15200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>24200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-7600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>20500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-3100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>6500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>18100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>4400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>14000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-7900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>7000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-10500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-2000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-3900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>7400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-6200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>17400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>9000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>21800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>5900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-15100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>24400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-7600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>20600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-3200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>6400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>18000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>4300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>14000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2666,8 +2724,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2728,8 +2789,8 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>8</v>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>8</v>
@@ -2746,11 +2807,11 @@
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD29" s="3">
         <v>1500</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
@@ -2764,8 +2825,11 @@
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2862,8 +2926,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2960,19 +3027,22 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>-600</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-100</v>
       </c>
       <c r="G32" s="3">
         <v>-100</v>
@@ -2981,76 +3051,76 @@
         <v>-100</v>
       </c>
       <c r="I32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J32" s="3">
         <v>-200</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-100</v>
       </c>
       <c r="K32" s="3">
         <v>-100</v>
       </c>
       <c r="L32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="R32" s="3">
         <v>-100</v>
       </c>
       <c r="S32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="T32" s="3">
         <v>300</v>
-      </c>
-      <c r="T32" s="3">
-        <v>-100</v>
       </c>
       <c r="U32" s="3">
         <v>-100</v>
       </c>
       <c r="V32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="W32" s="3">
         <v>0</v>
       </c>
       <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
         <v>-200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-300</v>
       </c>
-      <c r="Z32" s="3">
-        <v>0</v>
-      </c>
       <c r="AA32" s="3">
         <v>0</v>
       </c>
       <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="3">
         <v>-200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-300</v>
-      </c>
-      <c r="AD32" s="3">
-        <v>-100</v>
       </c>
       <c r="AE32" s="3">
         <v>-100</v>
       </c>
       <c r="AF32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AG32" s="3">
         <v>0</v>
@@ -3058,106 +3128,112 @@
       <c r="AH32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-7900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>7000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-10500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-2000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-3900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>7400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-6200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>17400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>9000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>21800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>5900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-15100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>24400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-7600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>20600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-3200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>6400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>19500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>4300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>14000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3254,209 +3330,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-7900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>7000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-10500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-2000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-3900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>7400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-6200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>17400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>9000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>21800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>5900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-15100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>24400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-7600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>20600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-3200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>6400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>19500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>4300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>14000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45501</v>
+      </c>
+      <c r="E38" s="2">
         <v>45410</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45319</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45228</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45137</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45046</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44955</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44864</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44773</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44682</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44591</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44500</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44409</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44318</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44227</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44136</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44045</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43954</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43863</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43772</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43681</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43590</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43499</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43401</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43310</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43219</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43128</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43037</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42946</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42855</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42764</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42673</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3491,8 +3576,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3527,106 +3613,110 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>9800</v>
+      </c>
+      <c r="E41" s="3">
         <v>6800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>32200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>8200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>11100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>9200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>45500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>9400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>15400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>40400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>77100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>20400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>18900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>26100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>46600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>12800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>19000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>8900</v>
-      </c>
-      <c r="U41" s="3">
-        <v>2200</v>
       </c>
       <c r="V41" s="3">
         <v>2200</v>
       </c>
       <c r="W41" s="3">
+        <v>2200</v>
+      </c>
+      <c r="X41" s="3">
         <v>3500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>13600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>24000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3723,465 +3813,480 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>10700</v>
+      </c>
+      <c r="E43" s="3">
         <v>12800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>9400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>7900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>7800</v>
-      </c>
-      <c r="H43" s="3">
-        <v>8400</v>
       </c>
       <c r="I43" s="3">
         <v>8400</v>
       </c>
       <c r="J43" s="3">
+        <v>8400</v>
+      </c>
+      <c r="K43" s="3">
         <v>10200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>7600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>6900</v>
-      </c>
-      <c r="M43" s="3">
-        <v>7700</v>
       </c>
       <c r="N43" s="3">
         <v>7700</v>
       </c>
       <c r="O43" s="3">
+        <v>7700</v>
+      </c>
+      <c r="P43" s="3">
         <v>4900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>4600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>5300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>7000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>7600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>5400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>3400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>8200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>7100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>8700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>4600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>3200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1700</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>500</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1100</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>400</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>168700</v>
+      </c>
+      <c r="E44" s="3">
         <v>136400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>125800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>174000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>157100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>145000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>154900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>204700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>164500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>152200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>122700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>165100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>134900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>144200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>149100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>213400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>167600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>175000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>147800</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>183100</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>114800</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>104300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>97700</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>131400</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>102400</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>98000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>89500</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>129500</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>84700</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>75700</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>70400</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>96700</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>17700</v>
+      </c>
+      <c r="E45" s="3">
         <v>15400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>13700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>13500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>15800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>13900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>12800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>15700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>15100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>14600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>15100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>13400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>11200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>9700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>8700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>9700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>7600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>7700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>8800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>10700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>12000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>12200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>15100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>13100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>11500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>9800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>9100</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>13300</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>9500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>5400</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>6400</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>8300</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>206900</v>
+      </c>
+      <c r="E46" s="3">
         <v>171400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>181000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>203500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>191800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>176500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>221700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>240000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>202500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>214100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>222500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>206600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>169800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>184600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>209700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>242900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>201800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>197000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>162200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>204300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>137500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>126100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>118200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>150200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>116600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>109600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>101800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>145400</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>96100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>95900</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>101200</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>108200</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E47" s="3">
         <v>4800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>5000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>4900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>5300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>5400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>5500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>5300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>5800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>6100</v>
-      </c>
-      <c r="M47" s="3">
-        <v>6600</v>
       </c>
       <c r="N47" s="3">
         <v>6600</v>
       </c>
       <c r="O47" s="3">
+        <v>6600</v>
+      </c>
+      <c r="P47" s="3">
         <v>6700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>6300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>6100</v>
-      </c>
-      <c r="R47" s="3">
-        <v>6000</v>
       </c>
       <c r="S47" s="3">
         <v>6000</v>
       </c>
       <c r="T47" s="3">
+        <v>6000</v>
+      </c>
+      <c r="U47" s="3">
         <v>5700</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>6400</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>6500</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>6200</v>
-      </c>
-      <c r="X47" s="3">
-        <v>6300</v>
       </c>
       <c r="Y47" s="3">
         <v>6300</v>
@@ -4201,8 +4306,8 @@
       <c r="AD47" s="3">
         <v>6300</v>
       </c>
-      <c r="AE47" s="3" t="s">
-        <v>8</v>
+      <c r="AE47" s="3">
+        <v>6300</v>
       </c>
       <c r="AF47" s="3" t="s">
         <v>8</v>
@@ -4213,106 +4318,112 @@
       <c r="AH47" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>263600</v>
+      </c>
+      <c r="E48" s="3">
         <v>282400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>294500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>304100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>297800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>297700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>291500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>295900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>278300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>276100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>281100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>289600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>281300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>287200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>295200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>304600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>296600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>301100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>304200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>303800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>284400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>282200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>334200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>165900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>144800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>129200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>109700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>98200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>75700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>62500</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>52400</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>45300</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4332,7 +4443,7 @@
         <v>800</v>
       </c>
       <c r="I49" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="J49" s="3">
         <v>900</v>
@@ -4341,13 +4452,13 @@
         <v>900</v>
       </c>
       <c r="L49" s="3">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="M49" s="3">
         <v>600</v>
       </c>
       <c r="N49" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="O49" s="3">
         <v>700</v>
@@ -4368,22 +4479,22 @@
         <v>700</v>
       </c>
       <c r="U49" s="3">
+        <v>700</v>
+      </c>
+      <c r="V49" s="3">
         <v>1700</v>
-      </c>
-      <c r="V49" s="3">
-        <v>700</v>
       </c>
       <c r="W49" s="3">
         <v>700</v>
       </c>
       <c r="X49" s="3">
+        <v>700</v>
+      </c>
+      <c r="Y49" s="3">
         <v>400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>700</v>
-      </c>
-      <c r="Z49" s="3">
-        <v>400</v>
       </c>
       <c r="AA49" s="3">
         <v>400</v>
@@ -4409,8 +4520,11 @@
       <c r="AH49" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI49" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4507,8 +4621,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4605,106 +4722,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>12400</v>
+      </c>
+      <c r="E52" s="3">
         <v>12000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>9200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>12700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>7400</v>
-      </c>
-      <c r="H52" s="3">
-        <v>7900</v>
       </c>
       <c r="I52" s="3">
         <v>7900</v>
       </c>
       <c r="J52" s="3">
+        <v>7900</v>
+      </c>
+      <c r="K52" s="3">
         <v>5600</v>
-      </c>
-      <c r="K52" s="3">
-        <v>5900</v>
       </c>
       <c r="L52" s="3">
         <v>5900</v>
       </c>
       <c r="M52" s="3">
-        <v>4700</v>
+        <v>5900</v>
       </c>
       <c r="N52" s="3">
         <v>4700</v>
       </c>
       <c r="O52" s="3">
+        <v>4700</v>
+      </c>
+      <c r="P52" s="3">
         <v>4600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>5300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>3900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>3000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>2300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>3500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>4800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>2700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>9400</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1200</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1900</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4801,106 +4924,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>488600</v>
+      </c>
+      <c r="E54" s="3">
         <v>471400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>490500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>526000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>503100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>488400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>527500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>547700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>493300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>502800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>515600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>508200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>463200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>482200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>514900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>554700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>506200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>505600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>474100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>518100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>434100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>418900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>295300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>324500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>270400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>249000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>223100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>252900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>181700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>160000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>156000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>155600</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4935,8 +5064,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4971,135 +5101,139 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>77600</v>
+      </c>
+      <c r="E57" s="3">
         <v>37400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>51100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>53500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>59300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>36100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>56500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>77800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>53600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>54500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>45400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>59200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>37700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>40100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>33600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>57100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>40100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>34400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>33100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>55400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>36300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>26700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>25400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>34200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>19500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>14600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>17300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>30100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>17800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>10700</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>9300</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>19300</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E58" s="3">
         <v>15100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>4000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>39900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>13600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3500</v>
-      </c>
-      <c r="L58" s="3">
-        <v>3400</v>
       </c>
       <c r="M58" s="3">
         <v>3400</v>
@@ -5108,447 +5242,459 @@
         <v>3400</v>
       </c>
       <c r="O58" s="3">
+        <v>3400</v>
+      </c>
+      <c r="P58" s="3">
         <v>3300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>20800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>5800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>5700</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>4800</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>2200</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>3200</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>2100</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1600</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>800</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>200</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>600</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>21800</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>100</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>3000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>2400</v>
-      </c>
-      <c r="AF58" s="3">
-        <v>700</v>
       </c>
       <c r="AG58" s="3">
         <v>700</v>
       </c>
       <c r="AH58" s="3">
+        <v>700</v>
+      </c>
+      <c r="AI58" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>46100</v>
+      </c>
+      <c r="E59" s="3">
         <v>43000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>47300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>47800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>44200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>48100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>58100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>49900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>43000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>50200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>67200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>54200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>44700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>49800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>56300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>43500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>39200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>46000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>54500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>38000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>33500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>35200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>26700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>30700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>22800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>33200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>32900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>25700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>17500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>25300</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>25000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>17400</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>127000</v>
+      </c>
+      <c r="E60" s="3">
         <v>95500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>102400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>141200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>107200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>87900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>118300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>141300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>100100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>108200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>116000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>116700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>85700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>110700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>95700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>106300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>84100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>82600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>79800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>95500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>71400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>62700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>52600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>65200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>42800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>69600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>50300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>58800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>37800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>36700</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>35100</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>38800</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>56600</v>
+      </c>
+      <c r="E61" s="3">
         <v>58400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>59400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>60500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>61400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>62400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>63300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>64300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>65100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>66000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>66900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>67700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>68600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>69400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>116300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>160700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>141400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>149800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>103500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>156500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>99200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>77500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>67900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>111200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>76900</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>35600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>28000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>70000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>20200</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>4800</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>3400</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>92300</v>
+      </c>
+      <c r="E62" s="3">
         <v>102200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>106400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>110500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>111000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>114000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>118600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>123500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>103700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>107200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>110000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>118500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>107000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>110100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>112500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>119000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>113200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>112400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>123100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>113100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>110200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>127900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>14700</v>
-      </c>
-      <c r="Z62" s="3">
-        <v>5500</v>
       </c>
       <c r="AA62" s="3">
         <v>5500</v>
       </c>
       <c r="AB62" s="3">
+        <v>5500</v>
+      </c>
+      <c r="AC62" s="3">
         <v>5400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>5500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>4800</v>
-      </c>
-      <c r="AE62" s="3">
-        <v>3700</v>
       </c>
       <c r="AF62" s="3">
         <v>3700</v>
@@ -5557,10 +5703,13 @@
         <v>3700</v>
       </c>
       <c r="AH62" s="3">
+        <v>3700</v>
+      </c>
+      <c r="AI62" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5657,8 +5806,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5755,8 +5907,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5853,106 +6008,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>272900</v>
+      </c>
+      <c r="E66" s="3">
         <v>253000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>265200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>308900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>276500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>261100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>297000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>325800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>265700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>278200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>289700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>300400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>258800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>287800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>321500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>383700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>336500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>342600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>295800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>364600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>280400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>267800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>135000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>185300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>128500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>113900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>87000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>136800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>65300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>48100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>44800</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>58700</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5987,8 +6148,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6085,8 +6247,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6183,8 +6348,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6281,8 +6449,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6379,106 +6550,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>112200</v>
+      </c>
+      <c r="E72" s="3">
         <v>115900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>123800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>116800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>127300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>129300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>133200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>125700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>131900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>129600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>130900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>113500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>110700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>101700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>101200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>79300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>78400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>72500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>87600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>63200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>63000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>61100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>70600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>50000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>53100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>46700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>48100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>28600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>29400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>25100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>24700</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>10700</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6575,8 +6752,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6673,8 +6853,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6771,106 +6954,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>215700</v>
+      </c>
+      <c r="E76" s="3">
         <v>218400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>225200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>217100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>226700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>227300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>230400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>221900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>227600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>224600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>225900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>207800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>204400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>194400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>193500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>171100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>169700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>163100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>178300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>153500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>153700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>151100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>160300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>139200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>141900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>135100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>136100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>116100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>116400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>111900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>111200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>96900</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6967,209 +7156,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45501</v>
+      </c>
+      <c r="E80" s="2">
         <v>45410</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45319</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45228</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45137</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45046</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44955</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44864</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44773</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44682</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44591</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44500</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44409</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44318</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44227</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44136</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44045</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43954</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43863</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43772</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43681</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43590</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43499</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43401</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43310</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43219</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43128</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43037</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42946</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42855</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42764</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42673</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-7900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>7000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-10500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-2000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-3900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>7400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-6200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>17400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>9000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>21800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>5900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-15100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>24400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-7600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>20600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-3200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>6400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>19500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>4300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>14000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7204,106 +7402,110 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E83" s="3">
         <v>8300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>8700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>8600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>7500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>7400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>7900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>7600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>7900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>7500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>7400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>7300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>7200</v>
-      </c>
-      <c r="P83" s="3">
-        <v>7300</v>
       </c>
       <c r="Q83" s="3">
         <v>7300</v>
       </c>
       <c r="R83" s="3">
+        <v>7300</v>
+      </c>
+      <c r="S83" s="3">
         <v>7900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>6600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>6700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>6100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>6500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>5000</v>
-      </c>
-      <c r="X83" s="3">
-        <v>4400</v>
       </c>
       <c r="Y83" s="3">
         <v>4400</v>
       </c>
       <c r="Z83" s="3">
+        <v>4400</v>
+      </c>
+      <c r="AA83" s="3">
         <v>3100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>2800</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>2300</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>2200</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>1800</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>1700</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>1600</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>1500</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7400,8 +7602,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7498,8 +7703,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7596,8 +7804,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7694,8 +7905,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7792,106 +8006,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>16600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-33700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>69700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-29800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>12700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-14000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>49600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-9900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-9400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-31700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>59200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>6200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>14100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>12400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>79400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-15800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>20700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-33500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>56000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-39600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>5100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-13100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>54600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-10900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-1600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-11000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>64800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-22800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-8600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-3500</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>47000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-27900</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7926,106 +8146,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-9100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-8500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-10100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-21400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-5400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-14900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-4100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-2200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-4800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-4100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-3500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-7100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-5800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-8000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-7200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-19100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-12800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-14000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-9000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-17400</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-11700</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-8300</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-7600</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-6500</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8122,8 +8346,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8220,106 +8447,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-8900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-8400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-10000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-21300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>1500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-5400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-14900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-3800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-4100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-2300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-5000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-4100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-6100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-7800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-7000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-9800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-7400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-19000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-13400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-14000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-11900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-17300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-18900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-7700</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-7900</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-7200</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8354,8 +8587,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8452,8 +8686,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8550,8 +8787,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8648,8 +8888,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8746,106 +8989,112 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="E100" s="3">
         <v>9800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-36800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>35200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-10700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>9300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1100</v>
-      </c>
-      <c r="M100" s="3">
-        <v>-700</v>
       </c>
       <c r="N100" s="3">
         <v>-700</v>
       </c>
       <c r="O100" s="3">
+        <v>-700</v>
+      </c>
+      <c r="P100" s="3">
         <v>-18300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-31600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-44300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>11800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-5800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>44700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-51500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>45200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>5500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>22400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-47300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>29500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>14400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>22000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-51800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>39300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>16400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-15300</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>11900</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8942,102 +9191,108 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-25400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>24000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-3000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-36300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>36100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-6000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-25000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-36700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>57300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-7100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-21200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>34400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-6400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>9900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>7100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-1700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-2200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>3600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-3000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>1200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-11100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-10500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>23900</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-23100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DLTH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DLTH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="92">
   <si>
     <t>DLTH</t>
   </si>
@@ -1027,7 +1027,7 @@
         <v>65700</v>
       </c>
       <c r="J10" s="3">
-        <v>123900</v>
+        <v>123800</v>
       </c>
       <c r="K10" s="3">
         <v>76900</v>
@@ -1349,7 +1349,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>1600</v>
+        <v>4000</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>8</v>
@@ -1450,25 +1450,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>800</v>
+        <v>1100</v>
       </c>
       <c r="E15" s="3">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="F15" s="3">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="G15" s="3">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="H15" s="3">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="I15" s="3">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="J15" s="3">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="K15" s="3">
         <v>800</v>
@@ -1585,7 +1585,7 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>145500</v>
+        <v>141500</v>
       </c>
       <c r="E17" s="3">
         <v>125700</v>
@@ -1686,7 +1686,7 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-3900</v>
+        <v>100</v>
       </c>
       <c r="E18" s="3">
         <v>-9000</v>
@@ -1824,25 +1824,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>200</v>
+        <v>-100</v>
       </c>
       <c r="E20" s="3">
         <v>0</v>
       </c>
       <c r="F20" s="3">
-        <v>600</v>
+        <v>-600</v>
       </c>
       <c r="G20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H20" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="I20" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="J20" s="3">
-        <v>200</v>
+        <v>-200</v>
       </c>
       <c r="K20" s="3">
         <v>100</v>
@@ -1925,25 +1925,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>4300</v>
+        <v>1400</v>
       </c>
       <c r="E21" s="3">
-        <v>-700</v>
+        <v>-7800</v>
       </c>
       <c r="F21" s="3">
-        <v>18900</v>
+        <v>11400</v>
       </c>
       <c r="G21" s="3">
-        <v>-3800</v>
+        <v>-11200</v>
       </c>
       <c r="H21" s="3">
-        <v>6100</v>
+        <v>-200</v>
       </c>
       <c r="I21" s="3">
-        <v>3000</v>
+        <v>-3200</v>
       </c>
       <c r="J21" s="3">
-        <v>18700</v>
+        <v>12000</v>
       </c>
       <c r="K21" s="3">
         <v>200</v>
@@ -3036,25 +3036,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-200</v>
+        <v>100</v>
       </c>
       <c r="E32" s="3">
         <v>0</v>
       </c>
       <c r="F32" s="3">
-        <v>-600</v>
+        <v>600</v>
       </c>
       <c r="G32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="H32" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="I32" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="J32" s="3">
-        <v>-200</v>
+        <v>200</v>
       </c>
       <c r="K32" s="3">
         <v>-100</v>
@@ -4024,25 +4024,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>17700</v>
+        <v>3400</v>
       </c>
       <c r="E45" s="3">
-        <v>15400</v>
+        <v>3700</v>
       </c>
       <c r="F45" s="3">
-        <v>13700</v>
+        <v>3400</v>
       </c>
       <c r="G45" s="3">
-        <v>13500</v>
+        <v>3700</v>
       </c>
       <c r="H45" s="3">
-        <v>15800</v>
+        <v>2700</v>
       </c>
       <c r="I45" s="3">
-        <v>13900</v>
+        <v>3000</v>
       </c>
       <c r="J45" s="3">
-        <v>12800</v>
+        <v>3100</v>
       </c>
       <c r="K45" s="3">
         <v>15700</v>
@@ -4428,25 +4428,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>800</v>
+        <v>7600</v>
       </c>
       <c r="E49" s="3">
-        <v>800</v>
+        <v>8200</v>
       </c>
       <c r="F49" s="3">
-        <v>800</v>
+        <v>7500</v>
       </c>
       <c r="G49" s="3">
-        <v>800</v>
+        <v>8300</v>
       </c>
       <c r="H49" s="3">
-        <v>800</v>
+        <v>6200</v>
       </c>
       <c r="I49" s="3">
-        <v>800</v>
+        <v>6900</v>
       </c>
       <c r="J49" s="3">
-        <v>900</v>
+        <v>7000</v>
       </c>
       <c r="K49" s="3">
         <v>900</v>
@@ -4731,25 +4731,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>12400</v>
+        <v>1400</v>
       </c>
       <c r="E52" s="3">
-        <v>12000</v>
+        <v>1400</v>
       </c>
       <c r="F52" s="3">
-        <v>9200</v>
+        <v>1500</v>
       </c>
       <c r="G52" s="3">
-        <v>12700</v>
+        <v>1600</v>
       </c>
       <c r="H52" s="3">
-        <v>7400</v>
+        <v>1700</v>
       </c>
       <c r="I52" s="3">
-        <v>7900</v>
+        <v>1700</v>
       </c>
       <c r="J52" s="3">
-        <v>7900</v>
+        <v>1700</v>
       </c>
       <c r="K52" s="3">
         <v>5600</v>
@@ -5209,25 +5209,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>3300</v>
+        <v>19400</v>
       </c>
       <c r="E58" s="3">
-        <v>15100</v>
+        <v>31700</v>
       </c>
       <c r="F58" s="3">
-        <v>4000</v>
+        <v>20400</v>
       </c>
       <c r="G58" s="3">
-        <v>39900</v>
+        <v>55900</v>
       </c>
       <c r="H58" s="3">
-        <v>3800</v>
+        <v>19800</v>
       </c>
       <c r="I58" s="3">
-        <v>3700</v>
+        <v>19400</v>
       </c>
       <c r="J58" s="3">
-        <v>3600</v>
+        <v>19200</v>
       </c>
       <c r="K58" s="3">
         <v>13600</v>
@@ -5310,25 +5310,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>46100</v>
+        <v>23900</v>
       </c>
       <c r="E59" s="3">
-        <v>43000</v>
+        <v>19400</v>
       </c>
       <c r="F59" s="3">
-        <v>47300</v>
+        <v>23100</v>
       </c>
       <c r="G59" s="3">
-        <v>47800</v>
+        <v>21400</v>
       </c>
       <c r="H59" s="3">
-        <v>44200</v>
+        <v>20400</v>
       </c>
       <c r="I59" s="3">
-        <v>48100</v>
+        <v>22000</v>
       </c>
       <c r="J59" s="3">
-        <v>58100</v>
+        <v>31000</v>
       </c>
       <c r="K59" s="3">
         <v>49900</v>
@@ -5512,25 +5512,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>56600</v>
+        <v>148900</v>
       </c>
       <c r="E61" s="3">
-        <v>58400</v>
+        <v>160600</v>
       </c>
       <c r="F61" s="3">
-        <v>59400</v>
+        <v>165800</v>
       </c>
       <c r="G61" s="3">
-        <v>60500</v>
+        <v>170900</v>
       </c>
       <c r="H61" s="3">
-        <v>61400</v>
+        <v>172400</v>
       </c>
       <c r="I61" s="3">
-        <v>62400</v>
+        <v>176400</v>
       </c>
       <c r="J61" s="3">
-        <v>63300</v>
+        <v>180700</v>
       </c>
       <c r="K61" s="3">
         <v>64300</v>
@@ -5612,26 +5612,26 @@
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>92300</v>
-      </c>
-      <c r="E62" s="3">
-        <v>102200</v>
-      </c>
-      <c r="F62" s="3">
-        <v>106400</v>
-      </c>
-      <c r="G62" s="3">
-        <v>110500</v>
-      </c>
-      <c r="H62" s="3">
-        <v>111000</v>
-      </c>
-      <c r="I62" s="3">
-        <v>114000</v>
-      </c>
-      <c r="J62" s="3">
-        <v>118600</v>
+      <c r="D62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K62" s="3">
         <v>123500</v>
@@ -6017,25 +6017,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>272900</v>
+        <v>275900</v>
       </c>
       <c r="E66" s="3">
-        <v>253000</v>
+        <v>256100</v>
       </c>
       <c r="F66" s="3">
-        <v>265200</v>
+        <v>268300</v>
       </c>
       <c r="G66" s="3">
-        <v>308900</v>
+        <v>312100</v>
       </c>
       <c r="H66" s="3">
-        <v>276500</v>
+        <v>279700</v>
       </c>
       <c r="I66" s="3">
-        <v>261100</v>
+        <v>264300</v>
       </c>
       <c r="J66" s="3">
-        <v>297000</v>
+        <v>300300</v>
       </c>
       <c r="K66" s="3">
         <v>325800</v>
@@ -7409,25 +7409,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>8000</v>
+        <v>7500</v>
       </c>
       <c r="E83" s="3">
-        <v>8300</v>
+        <v>7400</v>
       </c>
       <c r="F83" s="3">
-        <v>8700</v>
+        <v>7700</v>
       </c>
       <c r="G83" s="3">
-        <v>8600</v>
+        <v>7600</v>
       </c>
       <c r="H83" s="3">
+        <v>7900</v>
+      </c>
+      <c r="I83" s="3">
         <v>7500</v>
       </c>
-      <c r="I83" s="3">
-        <v>7400</v>
-      </c>
       <c r="J83" s="3">
-        <v>7900</v>
+        <v>7200</v>
       </c>
       <c r="K83" s="3">
         <v>7600</v>
@@ -8474,7 +8474,7 @@
         <v>-21300</v>
       </c>
       <c r="J94" s="3">
-        <v>1500</v>
+        <v>-2800</v>
       </c>
       <c r="K94" s="3">
         <v>-5400</v>
@@ -8593,26 +8593,26 @@
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -9098,26 +9098,26 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>

--- a/AAII_Financials/Quarterly/DLTH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DLTH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="92">
   <si>
     <t>DLTH</t>
   </si>
@@ -656,456 +656,482 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45690</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45592</v>
+      </c>
+      <c r="F7" s="2">
         <v>45501</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45410</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45319</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45228</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45137</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45046</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44955</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44864</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44773</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44682</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44591</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44500</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44409</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44318</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44227</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44136</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44045</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43954</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43863</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43772</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43681</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43590</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43499</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43401</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43310</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43219</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43128</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43037</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42946</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>42855</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>42764</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>42673</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>241300</v>
+      </c>
+      <c r="E8" s="3">
+        <v>127100</v>
+      </c>
+      <c r="F8" s="3">
         <v>141600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>116700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>245600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>138200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>139100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>123800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>241800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>147100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>141500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>122900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>270800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>145300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>149100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>133400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>256000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>135500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>137400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>109900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>259600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>119800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>122000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>114200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>250500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>106700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>110700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>100200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>217800</v>
-      </c>
-      <c r="AE8" s="3">
-        <v>83700</v>
-      </c>
-      <c r="AF8" s="3">
-        <v>86200</v>
       </c>
       <c r="AG8" s="3">
         <v>83700</v>
       </c>
       <c r="AH8" s="3">
+        <v>86200</v>
+      </c>
+      <c r="AI8" s="3">
+        <v>83700</v>
+      </c>
+      <c r="AJ8" s="3">
         <v>174700</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>67000</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>134800</v>
+      </c>
+      <c r="E9" s="3">
+        <v>60600</v>
+      </c>
+      <c r="F9" s="3">
         <v>67600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>55100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>127200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>68800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>67600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>58100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>117900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>70200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>65900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>55800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>125100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>61600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>67700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>66900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>120300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>64500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>64900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>57600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>122600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>54400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>57200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>53300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>119300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>45700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>48400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>44300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>101800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>36300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>37300</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>35000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AJ9" s="3">
         <v>77900</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AK9" s="3">
         <v>28300</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>106500</v>
+      </c>
+      <c r="E10" s="3">
+        <v>66400</v>
+      </c>
+      <c r="F10" s="3">
         <v>74000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>61600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>118400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>69400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>71500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>65700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>123800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>76900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>75600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>67100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>145700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>83700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>81400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>66500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>135700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>71000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>72500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>52300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>137000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>65400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>64800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>60900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>131200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>61000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>62300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>55900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>116000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>47400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>48900</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>48700</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AJ10" s="3">
         <v>96800</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AK10" s="3">
         <v>38700</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1141,8 +1167,10 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1242,8 +1270,14 @@
       <c r="AI12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1343,20 +1377,26 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3">
+        <v>6200</v>
+      </c>
+      <c r="F14" s="3">
         <v>4000</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1369,11 +1409,11 @@
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1381,11 +1421,11 @@
       <c r="N14" s="3">
         <v>0</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>8</v>
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>8</v>
@@ -1399,15 +1439,15 @@
       <c r="T14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U14" s="3">
+      <c r="U14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W14" s="3">
         <v>1600</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1420,11 +1460,11 @@
       <c r="AA14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="3">
-        <v>0</v>
+      <c r="AB14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD14" s="3">
         <v>0</v>
@@ -1444,19 +1484,25 @@
       <c r="AI14" s="3">
         <v>0</v>
       </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E15" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F15" s="3">
         <v>1100</v>
-      </c>
-      <c r="E15" s="3">
-        <v>1200</v>
-      </c>
-      <c r="F15" s="3">
-        <v>1200</v>
       </c>
       <c r="G15" s="3">
         <v>1200</v>
@@ -1471,10 +1517,10 @@
         <v>1200</v>
       </c>
       <c r="K15" s="3">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="L15" s="3">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="M15" s="3">
         <v>800</v>
@@ -1498,40 +1544,40 @@
         <v>800</v>
       </c>
       <c r="T15" s="3">
+        <v>800</v>
+      </c>
+      <c r="U15" s="3">
+        <v>800</v>
+      </c>
+      <c r="V15" s="3">
         <v>900</v>
       </c>
-      <c r="U15" s="3">
+      <c r="W15" s="3">
         <v>700</v>
       </c>
-      <c r="V15" s="3">
+      <c r="X15" s="3">
         <v>200</v>
       </c>
-      <c r="W15" s="3">
+      <c r="Y15" s="3">
         <v>500</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Z15" s="3">
         <v>500</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="AA15" s="3">
         <v>100</v>
       </c>
-      <c r="Z15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA15" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB15" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AC15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD15" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE15" s="3">
-        <v>0</v>
+      <c r="AD15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AF15" s="3">
         <v>0</v>
@@ -1545,8 +1591,14 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1579,210 +1631,224 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>245500</v>
+      </c>
+      <c r="E17" s="3">
+        <v>143500</v>
+      </c>
+      <c r="F17" s="3">
         <v>141500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>125700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>236000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>150600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>140500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>128300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>231100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>154500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>137600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>123800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>246500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>140400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>136000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>131500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>225400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>132700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>127600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>128900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>226500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>118400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>118200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>123900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>220400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>109300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>100800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>100500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>188300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>84300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>78800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>82900</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>151800</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>66200</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-16400</v>
+      </c>
+      <c r="F18" s="3">
         <v>100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-9000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>9600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-12400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-1400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-4500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>10700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-7400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>3900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>24300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>4900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>13100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>1900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>30600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>2800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>9800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-19000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>33100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>1400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>3800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-9700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>30100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-2600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>9900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>-300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>29500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>-600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>7400</v>
-      </c>
-      <c r="AG18" s="3">
-        <v>800</v>
-      </c>
-      <c r="AH18" s="3">
-        <v>22900</v>
       </c>
       <c r="AI18" s="3">
         <v>800</v>
       </c>
+      <c r="AJ18" s="3">
+        <v>22900</v>
+      </c>
+      <c r="AK18" s="3">
+        <v>800</v>
+      </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1818,513 +1884,545 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>-100</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>-600</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>-100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-300</v>
-      </c>
-      <c r="P20" s="3">
-        <v>100</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>0</v>
       </c>
       <c r="R20" s="3">
         <v>100</v>
       </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>100</v>
-      </c>
-      <c r="T20" s="3">
-        <v>-300</v>
       </c>
       <c r="U20" s="3">
         <v>100</v>
       </c>
       <c r="V20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="W20" s="3">
         <v>100</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
       <c r="X20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3">
         <v>200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>300</v>
       </c>
-      <c r="AA20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB20" s="3">
-        <v>0</v>
-      </c>
       <c r="AC20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="3">
         <v>200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>100</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>100</v>
       </c>
-      <c r="AG20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH20" s="3">
-        <v>0</v>
-      </c>
       <c r="AI20" s="3">
         <v>0</v>
       </c>
+      <c r="AJ20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-15400</v>
+      </c>
+      <c r="F21" s="3">
         <v>1400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-7800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>11400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-11200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-3200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>12000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>11800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>6600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>31900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>11900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>20400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>9200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>38000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>10900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>16100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-12200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>39300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>7900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>8700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>-5100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>34700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>12700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>2200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>32000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>1300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>9200</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>2400</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AJ21" s="3">
         <v>24400</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AK21" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E22" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F22" s="3">
         <v>1000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>1000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>1100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>1200</v>
-      </c>
-      <c r="H22" s="3">
-        <v>900</v>
-      </c>
-      <c r="I22" s="3">
-        <v>900</v>
       </c>
       <c r="J22" s="3">
         <v>900</v>
       </c>
       <c r="K22" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="L22" s="3">
         <v>900</v>
       </c>
       <c r="M22" s="3">
+        <v>1000</v>
+      </c>
+      <c r="N22" s="3">
         <v>900</v>
-      </c>
-      <c r="N22" s="3">
-        <v>1300</v>
       </c>
       <c r="O22" s="3">
         <v>900</v>
       </c>
       <c r="P22" s="3">
+        <v>1300</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>900</v>
+      </c>
+      <c r="R22" s="3">
         <v>1200</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>1300</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>1500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>1600</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>1800</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>1400</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>1300</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>1500</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>1200</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>800</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>2300</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>1600</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>1200</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>800</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AF22" s="3">
         <v>800</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AG22" s="3">
         <v>700</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AH22" s="3">
         <v>400</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AI22" s="3">
         <v>200</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AJ22" s="3">
         <v>100</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AK22" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-23800</v>
+      </c>
+      <c r="F23" s="3">
         <v>-4700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-9900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>9100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-13600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-2200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-5300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>9900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-8300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>3100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-1800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>23200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>3700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>12000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>29200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>1300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>7800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-20300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>31800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>2500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-10300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>28000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-4100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>8700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>-900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>29000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>-1200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>7100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>22900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
+        <v>4700</v>
+      </c>
+      <c r="F24" s="3">
         <v>-1000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>-2100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>2100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>-3100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>-200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>-1500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>2500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>-2100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>-400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>5800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>3000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>7500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>1900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>-5100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>7600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>-200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>-2700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>7500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>-1100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>2200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>-200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>10900</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>-500</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>2700</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AI24" s="3">
         <v>200</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AJ24" s="3">
         <v>8800</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AK24" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2424,210 +2522,228 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-28500</v>
+      </c>
+      <c r="F26" s="3">
         <v>-3700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-7900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>7000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-10500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-2000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-3900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>7500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-6200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>2300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-1300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>17300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>2800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>8900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>21800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>5900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-15200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>24200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>1800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-7600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>20500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-3100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>6500</v>
-      </c>
-      <c r="AC26" s="3">
-        <v>-700</v>
-      </c>
-      <c r="AD26" s="3">
-        <v>18100</v>
       </c>
       <c r="AE26" s="3">
         <v>-700</v>
       </c>
       <c r="AF26" s="3">
+        <v>18100</v>
+      </c>
+      <c r="AG26" s="3">
+        <v>-700</v>
+      </c>
+      <c r="AH26" s="3">
         <v>4400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>400</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>14000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-28500</v>
+      </c>
+      <c r="F27" s="3">
         <v>-3700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-7900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>7000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-10500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-2000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-3900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>7400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-6200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>2400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-1300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>17400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>2800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>9000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>21800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>5900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-15100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>24400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>1900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-7600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>20600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-3200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>6400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>-700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>18000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>-800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>4300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>14000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2727,8 +2843,14 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2792,11 +2914,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y29" s="3" t="s">
-        <v>8</v>
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
+        <v>0</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>8</v>
@@ -2810,15 +2932,15 @@
       <c r="AC29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AD29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF29" s="3">
         <v>1500</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG29" s="3" t="s">
         <v>8</v>
       </c>
@@ -2828,8 +2950,14 @@
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2929,8 +3057,14 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3030,210 +3164,228 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>100</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>600</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>-200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>300</v>
-      </c>
-      <c r="P32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>0</v>
       </c>
       <c r="R32" s="3">
         <v>-100</v>
       </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>-100</v>
-      </c>
-      <c r="T32" s="3">
-        <v>300</v>
       </c>
       <c r="U32" s="3">
         <v>-100</v>
       </c>
       <c r="V32" s="3">
+        <v>300</v>
+      </c>
+      <c r="W32" s="3">
         <v>-100</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
       <c r="X32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3">
         <v>-200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-300</v>
       </c>
-      <c r="AA32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB32" s="3">
-        <v>0</v>
-      </c>
       <c r="AC32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="3">
         <v>-200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>-300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>-100</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>-100</v>
       </c>
-      <c r="AG32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH32" s="3">
-        <v>0</v>
-      </c>
       <c r="AI32" s="3">
         <v>0</v>
       </c>
+      <c r="AJ32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-28500</v>
+      </c>
+      <c r="F33" s="3">
         <v>-3700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-7900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>7000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-10500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-2000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-3900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>7400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-6200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>2400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-1300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>17400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>2800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>9000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>21800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>5900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-15100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>24400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>1900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-7600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>20600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-3200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>6400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>-700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>19500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>-800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>4300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>14000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3333,215 +3485,233 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-28500</v>
+      </c>
+      <c r="F35" s="3">
         <v>-3700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-7900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>7000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-10500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-2000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-3900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>7400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-6200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>2400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-1300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>17400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>2800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>9000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>21800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>5900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-15100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>24400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>1900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-7600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>20600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-3200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>6400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>-700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>19500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>-800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>4300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>14000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45690</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45592</v>
+      </c>
+      <c r="F38" s="2">
         <v>45501</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45410</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45319</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45228</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45137</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45046</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44955</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44864</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44773</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44682</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44591</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44500</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44409</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44318</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44227</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44136</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44045</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43954</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43863</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43772</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43681</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43590</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43499</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43401</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43310</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43219</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43128</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43037</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42946</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>42855</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>42764</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>42673</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3577,8 +3747,10 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3614,109 +3786,117 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E41" s="3">
+        <v>9300</v>
+      </c>
+      <c r="F41" s="3">
         <v>9800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>6800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>32200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>8200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>11100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>9200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>45500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>9400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>15400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>40400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>77100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>20400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>18900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>26100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>46600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>12800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>19000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>8900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>2200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>2200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>3500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>1000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>2500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>2400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>1200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>2900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>1000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>1400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>13600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>24000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AK41" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3816,218 +3996,236 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E43" s="3">
+        <v>6700</v>
+      </c>
+      <c r="F43" s="3">
         <v>10700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>12800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>9400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>7900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>7800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>8400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>8400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>10200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>7600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>6900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>7700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>7700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>4900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>4600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>5300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>7000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>7600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>5400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>3400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>8200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>7100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>8700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>4600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>3200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>1700</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>500</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AI43" s="3">
         <v>1100</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AJ43" s="3">
         <v>400</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AK43" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>166500</v>
+      </c>
+      <c r="E44" s="3">
+        <v>231400</v>
+      </c>
+      <c r="F44" s="3">
         <v>168700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>136400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>125800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>174000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>157100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>145000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>154900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>204700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>164500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>152200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>122700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>165100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>134900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>144200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>149100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>213400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>167600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>175000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>147800</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>183100</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>114800</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>104300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>97700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>131400</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>102400</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>98000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>89500</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>129500</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>84700</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AI44" s="3">
         <v>75700</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AJ44" s="3">
         <v>70400</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AK44" s="3">
         <v>96700</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>3400</v>
+      <c r="D45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E45" s="3">
-        <v>3700</v>
+        <v>4600</v>
       </c>
       <c r="F45" s="3">
         <v>3400</v>
@@ -4036,263 +4234,275 @@
         <v>3700</v>
       </c>
       <c r="H45" s="3">
+        <v>3400</v>
+      </c>
+      <c r="I45" s="3">
+        <v>3700</v>
+      </c>
+      <c r="J45" s="3">
         <v>2700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>3000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>3100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>15700</v>
-      </c>
-      <c r="L45" s="3">
-        <v>15100</v>
-      </c>
-      <c r="M45" s="3">
-        <v>14600</v>
       </c>
       <c r="N45" s="3">
         <v>15100</v>
       </c>
       <c r="O45" s="3">
+        <v>14600</v>
+      </c>
+      <c r="P45" s="3">
+        <v>15100</v>
+      </c>
+      <c r="Q45" s="3">
         <v>13400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>11200</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>9700</v>
-      </c>
-      <c r="R45" s="3">
-        <v>8700</v>
       </c>
       <c r="S45" s="3">
         <v>9700</v>
       </c>
       <c r="T45" s="3">
+        <v>8700</v>
+      </c>
+      <c r="U45" s="3">
+        <v>9700</v>
+      </c>
+      <c r="V45" s="3">
         <v>7600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>7700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>8800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>10700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>12000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>12200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>15100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>13100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>11500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>9800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>9100</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>13300</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>9500</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AI45" s="3">
         <v>5400</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AJ45" s="3">
         <v>6400</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AK45" s="3">
         <v>8300</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>191600</v>
+      </c>
+      <c r="E46" s="3">
+        <v>264300</v>
+      </c>
+      <c r="F46" s="3">
         <v>206900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>171400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>181000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>203500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>191800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>176500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>221700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>240000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>202500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>214100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>222500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>206600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>169800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>184600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>209700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>242900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>201800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>197000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>162200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>204300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>137500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>126100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>118200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>150200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>116600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>109600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>101800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>145400</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>96100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>95900</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AJ46" s="3">
         <v>101200</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AK46" s="3">
         <v>108200</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>4900</v>
+        <v>4500</v>
       </c>
       <c r="E47" s="3">
         <v>4800</v>
       </c>
       <c r="F47" s="3">
+        <v>4900</v>
+      </c>
+      <c r="G47" s="3">
+        <v>4800</v>
+      </c>
+      <c r="H47" s="3">
         <v>5000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>4900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>5300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>5400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>5500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>5300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>5800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>6100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>6600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>6600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>6700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>6300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>6100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>6000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>6000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>5700</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>6400</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>6500</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>6200</v>
-      </c>
-      <c r="Y47" s="3">
-        <v>6300</v>
-      </c>
-      <c r="Z47" s="3">
-        <v>6300</v>
       </c>
       <c r="AA47" s="3">
         <v>6300</v>
@@ -4309,11 +4519,11 @@
       <c r="AE47" s="3">
         <v>6300</v>
       </c>
-      <c r="AF47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG47" s="3" t="s">
-        <v>8</v>
+      <c r="AF47" s="3">
+        <v>6300</v>
+      </c>
+      <c r="AG47" s="3">
+        <v>6300</v>
       </c>
       <c r="AH47" s="3" t="s">
         <v>8</v>
@@ -4321,150 +4531,162 @@
       <c r="AI47" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK47" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>247200</v>
+      </c>
+      <c r="E48" s="3">
+        <v>252500</v>
+      </c>
+      <c r="F48" s="3">
         <v>263600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>282400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>294500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>304100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>297800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>297700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>291500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>295900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>278300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>276100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>281100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>289600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>281300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>287200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>295200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>304600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>296600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>301100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>304200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>303800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>284400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>282200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>334200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>165900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>144800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>129200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>109700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>98200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>75700</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AI48" s="3">
         <v>62500</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AJ48" s="3">
         <v>52400</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AK48" s="3">
         <v>45300</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>0</v>
+      </c>
+      <c r="E49" s="3">
+        <v>10100</v>
+      </c>
+      <c r="F49" s="3">
         <v>7600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>8200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>7500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>8300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>6200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>6900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>7000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>600</v>
-      </c>
-      <c r="O49" s="3">
-        <v>700</v>
-      </c>
-      <c r="P49" s="3">
-        <v>700</v>
       </c>
       <c r="Q49" s="3">
         <v>700</v>
@@ -4482,16 +4704,16 @@
         <v>700</v>
       </c>
       <c r="V49" s="3">
-        <v>1700</v>
+        <v>700</v>
       </c>
       <c r="W49" s="3">
         <v>700</v>
       </c>
       <c r="X49" s="3">
+        <v>1700</v>
+      </c>
+      <c r="Y49" s="3">
         <v>700</v>
-      </c>
-      <c r="Y49" s="3">
-        <v>400</v>
       </c>
       <c r="Z49" s="3">
         <v>700</v>
@@ -4500,7 +4722,7 @@
         <v>400</v>
       </c>
       <c r="AB49" s="3">
-        <v>400</v>
+        <v>700</v>
       </c>
       <c r="AC49" s="3">
         <v>400</v>
@@ -4523,8 +4745,14 @@
       <c r="AI49" s="3">
         <v>400</v>
       </c>
+      <c r="AJ49" s="3">
+        <v>400</v>
+      </c>
+      <c r="AK49" s="3">
+        <v>400</v>
+      </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4624,8 +4852,14 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4725,109 +4959,121 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E52" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F52" s="3">
         <v>1400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>1400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>1500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>1600</v>
-      </c>
-      <c r="H52" s="3">
-        <v>1700</v>
-      </c>
-      <c r="I52" s="3">
-        <v>1700</v>
       </c>
       <c r="J52" s="3">
         <v>1700</v>
       </c>
       <c r="K52" s="3">
+        <v>1700</v>
+      </c>
+      <c r="L52" s="3">
+        <v>1700</v>
+      </c>
+      <c r="M52" s="3">
         <v>5600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>5900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>5900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>4700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>4700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>4600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>3400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>3300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>1100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>1200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>2900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>5300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>3900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>3000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>1700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>2300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>3500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>4800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>2700</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>9400</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AI52" s="3">
         <v>1200</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AJ52" s="3">
         <v>1900</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AK52" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4927,109 +5173,121 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>452400</v>
+      </c>
+      <c r="E54" s="3">
+        <v>533100</v>
+      </c>
+      <c r="F54" s="3">
         <v>488600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>471400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>490500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>526000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>503100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>488400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>527500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>547700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>493300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>502800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>515600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>508200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>463200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>482200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>514900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>554700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>506200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>505600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>474100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>518100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>434100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>418900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>295300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>324500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>270400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>249000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>223100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>252900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>181700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>160000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>156000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AK54" s="3">
         <v>155600</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5065,8 +5323,10 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5102,513 +5362,545 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>73900</v>
+      </c>
+      <c r="E57" s="3">
+        <v>104500</v>
+      </c>
+      <c r="F57" s="3">
         <v>77600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>37400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>51100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>53500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>59300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>36100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>56500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>77800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>53600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>54500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>45400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>59200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>37700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>40100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>33600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>57100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>40100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>34400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>33100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>55400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>36300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>26700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>25400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>34200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>19500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>14600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>17300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>30100</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>17800</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>10700</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AJ57" s="3">
         <v>9300</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AK57" s="3">
         <v>19300</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>19000</v>
+      </c>
+      <c r="E58" s="3">
+        <v>62900</v>
+      </c>
+      <c r="F58" s="3">
         <v>19400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>31700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>20400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>55900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>19800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>19400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>19200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>13600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>3500</v>
-      </c>
-      <c r="M58" s="3">
-        <v>3400</v>
-      </c>
-      <c r="N58" s="3">
-        <v>3400</v>
       </c>
       <c r="O58" s="3">
         <v>3400</v>
       </c>
       <c r="P58" s="3">
+        <v>3400</v>
+      </c>
+      <c r="Q58" s="3">
+        <v>3400</v>
+      </c>
+      <c r="R58" s="3">
         <v>3300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>20800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>5800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>5700</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>4800</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>2200</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>3200</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>2100</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>1600</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>800</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>1000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>200</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>600</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>21800</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>100</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>3000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AH58" s="3">
         <v>2400</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AI58" s="3">
         <v>700</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AJ58" s="3">
         <v>700</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AK58" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>100</v>
+      </c>
+      <c r="E59" s="3">
+        <v>22900</v>
+      </c>
+      <c r="F59" s="3">
         <v>23900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>19400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>23100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>21400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>20400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>22000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>31000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>49900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>43000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>50200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>67200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>54200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>44700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>49800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>56300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>43500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>39200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>46000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>54500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>38000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>33500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>35200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>26700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>30700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>22800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>33200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>32900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>25700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>17500</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>25300</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AJ59" s="3">
         <v>25000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AK59" s="3">
         <v>17400</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>128500</v>
+      </c>
+      <c r="E60" s="3">
+        <v>203600</v>
+      </c>
+      <c r="F60" s="3">
         <v>127000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>95500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>102400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>141200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>107200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>87900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>118300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>141300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>100100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>108200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>116000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>116700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>85700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>110700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>95700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>106300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>84100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>82600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>79800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>95500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>71400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>62700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>52600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>65200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>42800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>69600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>50300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>58800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>37800</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>36700</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AJ60" s="3">
         <v>35100</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AK60" s="3">
         <v>38800</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>144100</v>
+      </c>
+      <c r="E61" s="3">
+        <v>144200</v>
+      </c>
+      <c r="F61" s="3">
         <v>148900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>160600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>165800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>170900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>172400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>176400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>180700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>64300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>65100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>66000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>66900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>67700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>68600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>69400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>116300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>160700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>141400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>149800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>103500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>156500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>99200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>77500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>67900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>111200</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>76900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>35600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>28000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>70000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>20200</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AI61" s="3">
         <v>4800</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AJ61" s="3">
         <v>3400</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AK61" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5633,83 +5925,89 @@
       <c r="J62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M62" s="3">
         <v>123500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>103700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>107200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>110000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>118500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>107000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>110100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>112500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>119000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>113200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>112400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>123100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>113100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>110200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>127900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>14700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>5500</v>
-      </c>
-      <c r="AB62" s="3">
-        <v>5500</v>
-      </c>
-      <c r="AC62" s="3">
-        <v>5400</v>
       </c>
       <c r="AD62" s="3">
         <v>5500</v>
       </c>
       <c r="AE62" s="3">
+        <v>5400</v>
+      </c>
+      <c r="AF62" s="3">
+        <v>5500</v>
+      </c>
+      <c r="AG62" s="3">
         <v>4800</v>
-      </c>
-      <c r="AF62" s="3">
-        <v>3700</v>
-      </c>
-      <c r="AG62" s="3">
-        <v>3700</v>
       </c>
       <c r="AH62" s="3">
         <v>3700</v>
       </c>
       <c r="AI62" s="3">
+        <v>3700</v>
+      </c>
+      <c r="AJ62" s="3">
+        <v>3700</v>
+      </c>
+      <c r="AK62" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5809,8 +6107,14 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5910,8 +6214,14 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6011,109 +6321,121 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>272800</v>
+      </c>
+      <c r="E66" s="3">
+        <v>348000</v>
+      </c>
+      <c r="F66" s="3">
         <v>275900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>256100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>268300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>312100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>279700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>264300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>300300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>325800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>265700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>278200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>289700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>300400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>258800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>287800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>321500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>383700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>336500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>342600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>295800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>364600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>280400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>267800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>135000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>185300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>128500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>113900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>87000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>136800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>65300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>48100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AJ66" s="3">
         <v>44800</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AK66" s="3">
         <v>58700</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6149,8 +6471,10 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6250,8 +6574,14 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6351,8 +6681,14 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6452,8 +6788,14 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6553,109 +6895,121 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>77700</v>
+      </c>
+      <c r="E72" s="3">
+        <v>83700</v>
+      </c>
+      <c r="F72" s="3">
         <v>112200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>115900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>123800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>116800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>127300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>129300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>133200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>125700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>131900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>129600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>130900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>113500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>110700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>101700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>101200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>79300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>78400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>72500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>87600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>63200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>63000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>61100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>70600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>50000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>53100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>46700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>48100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>28600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>29400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>25100</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AJ72" s="3">
         <v>24700</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AK72" s="3">
         <v>10700</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6755,8 +7109,14 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6856,8 +7216,14 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6957,109 +7323,121 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>182700</v>
+      </c>
+      <c r="E76" s="3">
+        <v>188100</v>
+      </c>
+      <c r="F76" s="3">
         <v>215700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>218400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>225200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>217100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>226700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>227300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>230400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>221900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>227600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>224600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>225900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>207800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>204400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>194400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>193500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>171100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>169700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>163100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>178300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>153500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>153700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>151100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>160300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>139200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>141900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>135100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>136100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>116100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>116400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>111900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>111200</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AK76" s="3">
         <v>96900</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7159,215 +7537,233 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45690</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45592</v>
+      </c>
+      <c r="F80" s="2">
         <v>45501</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45410</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45319</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45228</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45137</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45046</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44955</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44864</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44773</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44682</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44591</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44500</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44409</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44318</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44227</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44136</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44045</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43954</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43863</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43772</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43681</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43590</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43499</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43401</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43310</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43219</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43128</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43037</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42946</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>42855</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>42764</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>42673</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-28500</v>
+      </c>
+      <c r="F81" s="3">
         <v>-3700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-7900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>7000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-10500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-2000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-3900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>7400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-6200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>2400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-1300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>17400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>2800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>9000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>21800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>5900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-15100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>24400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>1900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-7600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>20600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-3200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>6400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>-700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>19500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>-800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>4300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>14000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7403,109 +7799,117 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E83" s="3">
+        <v>8600</v>
+      </c>
+      <c r="F83" s="3">
         <v>7500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>7400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>7700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>7600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>7900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>7500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>7200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>7600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>7900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>7500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>7400</v>
-      </c>
-      <c r="O83" s="3">
-        <v>7300</v>
-      </c>
-      <c r="P83" s="3">
-        <v>7200</v>
       </c>
       <c r="Q83" s="3">
         <v>7300</v>
       </c>
       <c r="R83" s="3">
+        <v>7200</v>
+      </c>
+      <c r="S83" s="3">
         <v>7300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
+        <v>7300</v>
+      </c>
+      <c r="U83" s="3">
         <v>7900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>6600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>6700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>6100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>6500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>5000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>4400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>4400</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>3100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>2800</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>2300</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>2200</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>1800</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>1700</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AI83" s="3">
         <v>1600</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AJ83" s="3">
         <v>1500</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AK83" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7605,8 +8009,14 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7706,8 +8116,14 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7807,8 +8223,14 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7908,8 +8330,14 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8009,109 +8437,121 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>41200</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-41100</v>
+      </c>
+      <c r="F89" s="3">
         <v>16600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-33700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>69700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-29800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>12700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-14000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>49600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-9900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-9400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-31700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>59200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>6200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>14100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>12400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>79400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-15800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>20700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-33500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>56000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-39600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>5100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>-13100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>54600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>-10900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>-1600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>-11000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>64800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>-22800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>-8600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>-3500</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>47000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AK89" s="3">
         <v>-27900</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8147,109 +8587,117 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="F91" s="3">
         <v>-1700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-1500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-9100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-8500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-10100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-21400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-2800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-5400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-14900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-3900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-1200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-4100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-2000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-2200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-4800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-4100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-3500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-7100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-5800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-8000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-7200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-19100</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-12800</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-14000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-9000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-17400</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-11700</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AI91" s="3">
         <v>-8300</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AJ91" s="3">
         <v>-7600</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AK91" s="3">
         <v>-6500</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8349,8 +8797,14 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8450,109 +8904,121 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="F94" s="3">
         <v>-1600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-1500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-8900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-8400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-10000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-21300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-2800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-5400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-14900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-3800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-1200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-4100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-2000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-2300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-5000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-4100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-6100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-7800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-7000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-9800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-7400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-19000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-13400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-14000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-11900</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-17300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-18900</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AI94" s="3">
         <v>-7700</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AJ94" s="3">
         <v>-7900</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AK94" s="3">
         <v>-7200</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8588,8 +9054,10 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8614,11 +9082,11 @@
       <c r="J96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -8689,8 +9157,14 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8790,8 +9264,14 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8891,8 +9371,14 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8992,109 +9478,121 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-44700</v>
+      </c>
+      <c r="E100" s="3">
+        <v>43200</v>
+      </c>
+      <c r="F100" s="3">
         <v>-12000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>9800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-36800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>35200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-1000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-10700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>9300</v>
-      </c>
-      <c r="L100" s="3">
-        <v>-700</v>
-      </c>
-      <c r="M100" s="3">
-        <v>-1100</v>
       </c>
       <c r="N100" s="3">
         <v>-700</v>
       </c>
       <c r="O100" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="P100" s="3">
         <v>-700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
+        <v>-700</v>
+      </c>
+      <c r="R100" s="3">
         <v>-18300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-31600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-44300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>11800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-5800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>44700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-51500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>45200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>5500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>22400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-47300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>29500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>14400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>22000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-51800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>39300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>16400</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AI100" s="3">
         <v>800</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AJ100" s="3">
         <v>-15300</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AK100" s="3">
         <v>11900</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9119,11 +9617,11 @@
       <c r="J101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -9194,105 +9692,117 @@
       <c r="AI101" s="3">
         <v>0</v>
       </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-500</v>
+      </c>
+      <c r="F102" s="3">
         <v>3000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-25400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>24000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-3000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>1900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-36300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>36100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-6000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-25000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-36700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>57300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>1500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-7100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-21200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>34400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-6400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>9900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>7100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-1700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-2200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>3600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-3000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>1200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>-800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>-11100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>-10500</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AJ102" s="3">
         <v>23900</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AK102" s="3">
         <v>-23100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DLTH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DLTH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="92">
   <si>
     <t>DLTH</t>
   </si>
@@ -1388,8 +1388,8 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
+      <c r="D14" s="3">
+        <v>0</v>
       </c>
       <c r="E14" s="3">
         <v>6200</v>
@@ -1496,7 +1496,7 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>8500</v>
+        <v>1000</v>
       </c>
       <c r="E15" s="3">
         <v>1000</v>
@@ -1639,7 +1639,7 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>245500</v>
+        <v>242700</v>
       </c>
       <c r="E17" s="3">
         <v>143500</v>
@@ -1651,7 +1651,7 @@
         <v>125700</v>
       </c>
       <c r="H17" s="3">
-        <v>236000</v>
+        <v>236800</v>
       </c>
       <c r="I17" s="3">
         <v>150600</v>
@@ -1746,7 +1746,7 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-4200</v>
+        <v>-1400</v>
       </c>
       <c r="E18" s="3">
         <v>-16400</v>
@@ -1758,7 +1758,7 @@
         <v>-9000</v>
       </c>
       <c r="H18" s="3">
-        <v>9600</v>
+        <v>8900</v>
       </c>
       <c r="I18" s="3">
         <v>-12400</v>
@@ -1999,7 +1999,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>4300</v>
+        <v>-400</v>
       </c>
       <c r="E21" s="3">
         <v>-15400</v>
@@ -2011,7 +2011,7 @@
         <v>-7800</v>
       </c>
       <c r="H21" s="3">
-        <v>11400</v>
+        <v>10600</v>
       </c>
       <c r="I21" s="3">
         <v>-11200</v>
@@ -2213,7 +2213,7 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-5600</v>
+        <v>-2700</v>
       </c>
       <c r="E23" s="3">
         <v>-23800</v>
@@ -2225,7 +2225,7 @@
         <v>-9900</v>
       </c>
       <c r="H23" s="3">
-        <v>9100</v>
+        <v>8300</v>
       </c>
       <c r="I23" s="3">
         <v>-13600</v>
@@ -2320,7 +2320,7 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="E24" s="3">
         <v>4700</v>
@@ -2332,7 +2332,7 @@
         <v>-2100</v>
       </c>
       <c r="H24" s="3">
-        <v>2100</v>
+        <v>1900</v>
       </c>
       <c r="I24" s="3">
         <v>-3100</v>
@@ -2534,7 +2534,7 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-5600</v>
+        <v>-3500</v>
       </c>
       <c r="E26" s="3">
         <v>-28500</v>
@@ -2546,7 +2546,7 @@
         <v>-7900</v>
       </c>
       <c r="H26" s="3">
-        <v>7000</v>
+        <v>6400</v>
       </c>
       <c r="I26" s="3">
         <v>-10500</v>
@@ -2641,7 +2641,7 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-5600</v>
+        <v>-3500</v>
       </c>
       <c r="E27" s="3">
         <v>-28500</v>
@@ -2653,7 +2653,7 @@
         <v>-7900</v>
       </c>
       <c r="H27" s="3">
-        <v>7000</v>
+        <v>6400</v>
       </c>
       <c r="I27" s="3">
         <v>-10500</v>
@@ -3283,7 +3283,7 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-5600</v>
+        <v>-3500</v>
       </c>
       <c r="E33" s="3">
         <v>-28500</v>
@@ -3295,7 +3295,7 @@
         <v>-7900</v>
       </c>
       <c r="H33" s="3">
-        <v>7000</v>
+        <v>6400</v>
       </c>
       <c r="I33" s="3">
         <v>-10500</v>
@@ -3497,7 +3497,7 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-5600</v>
+        <v>-3500</v>
       </c>
       <c r="E35" s="3">
         <v>-28500</v>
@@ -3509,7 +3509,7 @@
         <v>-7900</v>
       </c>
       <c r="H35" s="3">
-        <v>7000</v>
+        <v>6400</v>
       </c>
       <c r="I35" s="3">
         <v>-10500</v>
@@ -4008,7 +4008,7 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>4000</v>
+        <v>6300</v>
       </c>
       <c r="E43" s="3">
         <v>6700</v>
@@ -4221,8 +4221,8 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>8</v>
+      <c r="D45" s="3">
+        <v>3700</v>
       </c>
       <c r="E45" s="3">
         <v>4600</v>
@@ -4650,7 +4650,7 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>0</v>
+        <v>7900</v>
       </c>
       <c r="E49" s="3">
         <v>10100</v>
@@ -4971,7 +4971,7 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>9100</v>
+        <v>1200</v>
       </c>
       <c r="E52" s="3">
         <v>1300</v>
@@ -5197,7 +5197,7 @@
         <v>471400</v>
       </c>
       <c r="H54" s="3">
-        <v>490500</v>
+        <v>491200</v>
       </c>
       <c r="I54" s="3">
         <v>526000</v>
@@ -5584,7 +5584,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>100</v>
+        <v>28400</v>
       </c>
       <c r="E59" s="3">
         <v>22900</v>
@@ -5596,7 +5596,7 @@
         <v>19400</v>
       </c>
       <c r="H59" s="3">
-        <v>23100</v>
+        <v>26300</v>
       </c>
       <c r="I59" s="3">
         <v>21400</v>
@@ -5691,7 +5691,7 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>128500</v>
+        <v>128600</v>
       </c>
       <c r="E60" s="3">
         <v>203600</v>
@@ -5703,7 +5703,7 @@
         <v>95500</v>
       </c>
       <c r="H60" s="3">
-        <v>102400</v>
+        <v>105600</v>
       </c>
       <c r="I60" s="3">
         <v>141200</v>
@@ -6345,7 +6345,7 @@
         <v>256100</v>
       </c>
       <c r="H66" s="3">
-        <v>268300</v>
+        <v>271500</v>
       </c>
       <c r="I66" s="3">
         <v>312100</v>
@@ -6919,7 +6919,7 @@
         <v>115900</v>
       </c>
       <c r="H72" s="3">
-        <v>123800</v>
+        <v>121400</v>
       </c>
       <c r="I72" s="3">
         <v>116800</v>
@@ -7347,7 +7347,7 @@
         <v>218400</v>
       </c>
       <c r="H76" s="3">
-        <v>225200</v>
+        <v>222800</v>
       </c>
       <c r="I76" s="3">
         <v>217100</v>
@@ -7661,7 +7661,7 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-5600</v>
+        <v>-3500</v>
       </c>
       <c r="E81" s="3">
         <v>-28500</v>
@@ -7673,7 +7673,7 @@
         <v>-7900</v>
       </c>
       <c r="H81" s="3">
-        <v>7000</v>
+        <v>6400</v>
       </c>
       <c r="I81" s="3">
         <v>-10500</v>

--- a/AAII_Financials/Quarterly/DLTH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DLTH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="92">
   <si>
     <t>DLTH</t>
   </si>
@@ -656,482 +656,495 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45781</v>
+      </c>
+      <c r="E7" s="2">
         <v>45690</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45592</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45501</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45410</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45319</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45228</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45137</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45046</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44955</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44864</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44773</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44682</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44591</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44500</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44409</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44318</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44227</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44136</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44045</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43954</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43863</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43772</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43681</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43590</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43499</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43401</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43310</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43219</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43128</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43037</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42946</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42855</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42764</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42673</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>102700</v>
+      </c>
+      <c r="E8" s="3">
         <v>241300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>127100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>141600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>116700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>245600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>138200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>139100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>123800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>241800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>147100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>141500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>122900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>270800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>145300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>149100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>133400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>256000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>135500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>137400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>109900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>259600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>119800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>122000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>114200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>250500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>106700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>110700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>100200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>217800</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>83700</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>86200</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>83700</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>174700</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>67000</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>49300</v>
+      </c>
+      <c r="E9" s="3">
         <v>134800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>60600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>67600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>55100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>127200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>68800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>67600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>58100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>117900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>70200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>65900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>55800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>125100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>61600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>67700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>66900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>120300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>64500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>64900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>57600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>122600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>54400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>57200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>53300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>119300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>45700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>48400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>44300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>101800</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>36300</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>37300</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>35000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>77900</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>28300</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>53400</v>
+      </c>
+      <c r="E10" s="3">
         <v>106500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>66400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>74000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>61600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>118400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>69400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>71500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>65700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>123800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>76900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>75600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>67100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>145700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>83700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>81400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>66500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>135700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>71000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>72500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>52300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>137000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>65400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>64800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>60900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>131200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>61000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>62300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>55900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>116000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>47400</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>48900</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>48700</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>96800</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>38700</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1169,8 +1182,9 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1276,8 +1290,11 @@
       <c r="AK12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1383,23 +1400,26 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>6200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>4000</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1415,8 +1435,8 @@
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1427,8 +1447,8 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>8</v>
+      <c r="Q14" s="3">
+        <v>0</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>8</v>
@@ -1445,12 +1465,12 @@
       <c r="V14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W14" s="3">
+      <c r="W14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X14" s="3">
         <v>1600</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1466,8 +1486,8 @@
       <c r="AC14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
+      <c r="AD14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AE14" s="3">
         <v>0</v>
@@ -1490,8 +1510,11 @@
       <c r="AK14" s="3">
         <v>0</v>
       </c>
+      <c r="AL14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1502,10 +1525,10 @@
         <v>1000</v>
       </c>
       <c r="F15" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G15" s="3">
         <v>1100</v>
-      </c>
-      <c r="G15" s="3">
-        <v>1200</v>
       </c>
       <c r="H15" s="3">
         <v>1200</v>
@@ -1523,7 +1546,7 @@
         <v>1200</v>
       </c>
       <c r="M15" s="3">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="N15" s="3">
         <v>800</v>
@@ -1550,26 +1573,26 @@
         <v>800</v>
       </c>
       <c r="V15" s="3">
+        <v>800</v>
+      </c>
+      <c r="W15" s="3">
         <v>900</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>700</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>200</v>
-      </c>
-      <c r="Y15" s="3">
-        <v>500</v>
       </c>
       <c r="Z15" s="3">
         <v>500</v>
       </c>
       <c r="AA15" s="3">
+        <v>500</v>
+      </c>
+      <c r="AB15" s="3">
         <v>100</v>
       </c>
-      <c r="AB15" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC15" s="3" t="s">
         <v>8</v>
       </c>
@@ -1579,8 +1602,8 @@
       <c r="AE15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF15" s="3">
-        <v>0</v>
+      <c r="AF15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AG15" s="3">
         <v>0</v>
@@ -1597,8 +1620,11 @@
       <c r="AK15" s="3">
         <v>0</v>
       </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1633,222 +1659,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>115100</v>
+      </c>
+      <c r="E17" s="3">
         <v>242700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>143500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>141500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>125700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>236800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>150600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>140500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>128300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>231100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>154500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>137600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>123800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>246500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>140400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>136000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>131500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>225400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>132700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>127600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>128900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>226500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>118400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>118200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>123900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>220400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>109300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>100800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>100500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>188300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>84300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>78800</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>82900</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>151800</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>66200</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-12400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-1400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-16400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-9000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>8900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-12400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-1400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-4500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>10700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-7400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>3900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>24300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>4900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>13100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>30600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>9800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-19000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>33100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>3800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-9700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>30100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-2600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>9900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>29500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-600</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>7400</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>800</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>22900</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1886,106 +1919,107 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E20" s="3">
         <v>0</v>
       </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>-100</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>-600</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K20" s="3">
         <v>-100</v>
       </c>
       <c r="L20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M20" s="3">
         <v>-200</v>
-      </c>
-      <c r="M20" s="3">
-        <v>100</v>
       </c>
       <c r="N20" s="3">
         <v>100</v>
       </c>
       <c r="O20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>100</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U20" s="3">
         <v>100</v>
       </c>
       <c r="V20" s="3">
+        <v>100</v>
+      </c>
+      <c r="W20" s="3">
         <v>-300</v>
-      </c>
-      <c r="W20" s="3">
-        <v>100</v>
       </c>
       <c r="X20" s="3">
         <v>100</v>
       </c>
       <c r="Y20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z20" s="3">
         <v>0</v>
       </c>
       <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="3">
         <v>200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>300</v>
       </c>
-      <c r="AC20" s="3">
-        <v>0</v>
-      </c>
       <c r="AD20" s="3">
         <v>0</v>
       </c>
       <c r="AE20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF20" s="3">
         <v>200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>300</v>
-      </c>
-      <c r="AG20" s="3">
-        <v>100</v>
       </c>
       <c r="AH20" s="3">
         <v>100</v>
       </c>
       <c r="AI20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AJ20" s="3">
         <v>0</v>
@@ -1993,138 +2027,144 @@
       <c r="AK20" s="3">
         <v>0</v>
       </c>
+      <c r="AL20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-11500</v>
+      </c>
+      <c r="E21" s="3">
         <v>-400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-15400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-7800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>10600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-11200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-3200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>12000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>11800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>6600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>31900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>11900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>20400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>9200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>38000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>10900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>16100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-12200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>39300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>7900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>8700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-5100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>34700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>12700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>2200</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>32000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1300</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>9200</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>2400</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>24400</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>1300</v>
+        <v>1500</v>
       </c>
       <c r="E22" s="3">
         <v>1300</v>
       </c>
       <c r="F22" s="3">
-        <v>1000</v>
+        <v>1300</v>
       </c>
       <c r="G22" s="3">
         <v>1000</v>
       </c>
       <c r="H22" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I22" s="3">
         <v>1100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1200</v>
-      </c>
-      <c r="J22" s="3">
-        <v>900</v>
       </c>
       <c r="K22" s="3">
         <v>900</v>
@@ -2133,296 +2173,305 @@
         <v>900</v>
       </c>
       <c r="M22" s="3">
+        <v>900</v>
+      </c>
+      <c r="N22" s="3">
         <v>1000</v>
-      </c>
-      <c r="N22" s="3">
-        <v>900</v>
       </c>
       <c r="O22" s="3">
         <v>900</v>
       </c>
       <c r="P22" s="3">
+        <v>900</v>
+      </c>
+      <c r="Q22" s="3">
         <v>1300</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>1200</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>1300</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>1500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>1600</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>1800</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>1400</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>1300</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>1500</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>1200</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>800</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>2300</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>1600</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>1200</v>
-      </c>
-      <c r="AE22" s="3">
-        <v>800</v>
       </c>
       <c r="AF22" s="3">
         <v>800</v>
       </c>
       <c r="AG22" s="3">
+        <v>800</v>
+      </c>
+      <c r="AH22" s="3">
         <v>700</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>400</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>200</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>100</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-2700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-23800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-4700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-9900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>8300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-13600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-2200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-5300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>9900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-8300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>3100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-1800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>23200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>3700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>12000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>29200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>7800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-20300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>31800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>2500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-10300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>28000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-4100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>8700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>29000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-1200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>7100</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>600</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>22900</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E24" s="3">
         <v>800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>4700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-1000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-2100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-3100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-1500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-2100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>5800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>3000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>7500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-5100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>7600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-2700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>7500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-1100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>2200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>10900</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-500</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>2700</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>200</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>8800</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2528,222 +2577,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-15300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-3500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-28500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-3700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-7900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>6400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-10500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-2000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-3900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>7500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-6200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>17300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>2800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>8900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>21800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>5900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-15200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>24200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-7600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>20500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-3100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>6500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>18100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-700</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>4400</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>400</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>14000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-15300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-3500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-28500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-3700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-7900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>6400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-10500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-2000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-3900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>7400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-6200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>17400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>2800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>9000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>21800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>5900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-15100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>24400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-7600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>20600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-3200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>6400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>18000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-800</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>4300</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>400</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>14000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2849,8 +2907,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2920,8 +2981,8 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>8</v>
+      <c r="Z29" s="3">
+        <v>0</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>8</v>
@@ -2938,12 +2999,12 @@
       <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AF29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG29" s="3">
         <v>1500</v>
       </c>
-      <c r="AG29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
@@ -2956,8 +3017,11 @@
       <c r="AK29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3063,8 +3127,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3170,106 +3237,109 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="E32" s="3">
         <v>0</v>
       </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>100</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>600</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K32" s="3">
         <v>100</v>
       </c>
       <c r="L32" s="3">
+        <v>100</v>
+      </c>
+      <c r="M32" s="3">
         <v>200</v>
-      </c>
-      <c r="M32" s="3">
-        <v>-100</v>
       </c>
       <c r="N32" s="3">
         <v>-100</v>
       </c>
       <c r="O32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-100</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="U32" s="3">
         <v>-100</v>
       </c>
       <c r="V32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="W32" s="3">
         <v>300</v>
-      </c>
-      <c r="W32" s="3">
-        <v>-100</v>
       </c>
       <c r="X32" s="3">
         <v>-100</v>
       </c>
       <c r="Y32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Z32" s="3">
         <v>0</v>
       </c>
       <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="3">
         <v>-200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-300</v>
       </c>
-      <c r="AC32" s="3">
-        <v>0</v>
-      </c>
       <c r="AD32" s="3">
         <v>0</v>
       </c>
       <c r="AE32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF32" s="3">
         <v>-200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-300</v>
-      </c>
-      <c r="AG32" s="3">
-        <v>-100</v>
       </c>
       <c r="AH32" s="3">
         <v>-100</v>
       </c>
       <c r="AI32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AJ32" s="3">
         <v>0</v>
@@ -3277,115 +3347,121 @@
       <c r="AK32" s="3">
         <v>0</v>
       </c>
+      <c r="AL32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-15300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-3500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-28500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-3700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-7900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>6400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-10500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-2000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-3900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>7400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-6200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>17400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>2800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>9000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>21800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>5900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-15100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>24400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-7600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>20600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-3200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>6400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>19500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>4300</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>400</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>14000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3491,227 +3567,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-15300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-3500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-28500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-3700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-7900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>6400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-10500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-2000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-3900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>7400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-6200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>17400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>2800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>9000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>21800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>5900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-15100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>24400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-7600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>20600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-3200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>6400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>19500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>4300</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>400</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>14000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45781</v>
+      </c>
+      <c r="E38" s="2">
         <v>45690</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45592</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45501</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45410</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45319</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45228</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45137</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45046</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44955</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44864</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44773</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44682</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44591</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44500</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44409</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44318</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44227</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44136</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44045</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43954</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43863</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43772</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43681</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43590</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43499</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43401</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43310</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43219</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43128</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43037</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42946</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42855</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42764</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42673</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3749,8 +3834,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3788,115 +3874,119 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E41" s="3">
         <v>3300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>9300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>9800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>6800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>32200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>8200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>11100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>9200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>45500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>9400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>15400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>40400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>77100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>20400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>18900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>26100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>46600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>12800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>19000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>8900</v>
-      </c>
-      <c r="X41" s="3">
-        <v>2200</v>
       </c>
       <c r="Y41" s="3">
         <v>2200</v>
       </c>
       <c r="Z41" s="3">
+        <v>2200</v>
+      </c>
+      <c r="AA41" s="3">
         <v>3500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>2400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>2900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1400</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>13600</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>24000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4002,222 +4092,231 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E43" s="3">
         <v>6300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>6700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>10700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>12800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>9400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>7900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>7800</v>
-      </c>
-      <c r="K43" s="3">
-        <v>8400</v>
       </c>
       <c r="L43" s="3">
         <v>8400</v>
       </c>
       <c r="M43" s="3">
+        <v>8400</v>
+      </c>
+      <c r="N43" s="3">
         <v>10200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>7600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>6900</v>
-      </c>
-      <c r="P43" s="3">
-        <v>7700</v>
       </c>
       <c r="Q43" s="3">
         <v>7700</v>
       </c>
       <c r="R43" s="3">
+        <v>7700</v>
+      </c>
+      <c r="S43" s="3">
         <v>4900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>4600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>5300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>7000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>7600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>5400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>3400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>8200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>7100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>8700</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>4600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>3200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>600</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>300</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1700</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>500</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>1100</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>400</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>176100</v>
+      </c>
+      <c r="E44" s="3">
         <v>166500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>231400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>168700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>136400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>125800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>174000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>157100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>145000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>154900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>204700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>164500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>152200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>122700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>165100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>134900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>144200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>149100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>213400</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>167600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>175000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>147800</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>183100</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>114800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>104300</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>97700</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>131400</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>102400</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>98000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>89500</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>129500</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>84700</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>75700</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>70400</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>96700</v>
       </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4225,287 +4324,293 @@
         <v>3700</v>
       </c>
       <c r="E45" s="3">
+        <v>3700</v>
+      </c>
+      <c r="F45" s="3">
         <v>4600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>3400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>15700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>15100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>14600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>15100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>13400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>11200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>9700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>8700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>9700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>7600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>7700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>8800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>10700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>12000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>12200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>15100</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>13100</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>11500</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>9800</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>9100</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>13300</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>9500</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>5400</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>6400</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>8300</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>211100</v>
+      </c>
+      <c r="E46" s="3">
         <v>191600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>264300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>206900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>171400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>181000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>203500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>191800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>176500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>221700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>240000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>202500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>214100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>222500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>206600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>169800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>184600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>209700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>242900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>201800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>197000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>162200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>204300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>137500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>126100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>118200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>150200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>116600</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>109600</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>101800</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>145400</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>96100</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>95900</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>101200</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>108200</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E47" s="3">
         <v>4500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>4800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>4900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>4800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>5000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>4900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>5300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>5400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>5500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>5300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>5800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>6100</v>
-      </c>
-      <c r="P47" s="3">
-        <v>6600</v>
       </c>
       <c r="Q47" s="3">
         <v>6600</v>
       </c>
       <c r="R47" s="3">
+        <v>6600</v>
+      </c>
+      <c r="S47" s="3">
         <v>6700</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>6300</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>6100</v>
-      </c>
-      <c r="U47" s="3">
-        <v>6000</v>
       </c>
       <c r="V47" s="3">
         <v>6000</v>
       </c>
       <c r="W47" s="3">
+        <v>6000</v>
+      </c>
+      <c r="X47" s="3">
         <v>5700</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>6400</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>6500</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>6200</v>
-      </c>
-      <c r="AA47" s="3">
-        <v>6300</v>
       </c>
       <c r="AB47" s="3">
         <v>6300</v>
@@ -4525,8 +4630,8 @@
       <c r="AG47" s="3">
         <v>6300</v>
       </c>
-      <c r="AH47" s="3" t="s">
-        <v>8</v>
+      <c r="AH47" s="3">
+        <v>6300</v>
       </c>
       <c r="AI47" s="3" t="s">
         <v>8</v>
@@ -4537,115 +4642,121 @@
       <c r="AK47" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL47" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>238500</v>
+      </c>
+      <c r="E48" s="3">
         <v>247200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>252500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>263600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>282400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>294500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>304100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>297800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>297700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>291500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>295900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>278300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>276100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>281100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>289600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>281300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>287200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>295200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>304600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>296600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>301100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>304200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>303800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>284400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>282200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>334200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>165900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>144800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>129200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>109700</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>98200</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>75700</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>62500</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>52400</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>45300</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4653,43 +4764,43 @@
         <v>7900</v>
       </c>
       <c r="E49" s="3">
+        <v>7900</v>
+      </c>
+      <c r="F49" s="3">
         <v>10100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>7600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>8200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>7500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>8300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>6200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>6900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>7000</v>
-      </c>
-      <c r="M49" s="3">
-        <v>900</v>
       </c>
       <c r="N49" s="3">
         <v>900</v>
       </c>
       <c r="O49" s="3">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="P49" s="3">
         <v>600</v>
       </c>
       <c r="Q49" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="R49" s="3">
         <v>700</v>
@@ -4710,22 +4821,22 @@
         <v>700</v>
       </c>
       <c r="X49" s="3">
+        <v>700</v>
+      </c>
+      <c r="Y49" s="3">
         <v>1700</v>
-      </c>
-      <c r="Y49" s="3">
-        <v>700</v>
       </c>
       <c r="Z49" s="3">
         <v>700</v>
       </c>
       <c r="AA49" s="3">
+        <v>700</v>
+      </c>
+      <c r="AB49" s="3">
         <v>400</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>700</v>
-      </c>
-      <c r="AC49" s="3">
-        <v>400</v>
       </c>
       <c r="AD49" s="3">
         <v>400</v>
@@ -4751,8 +4862,11 @@
       <c r="AK49" s="3">
         <v>400</v>
       </c>
+      <c r="AL49" s="3">
+        <v>400</v>
+      </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4858,8 +4972,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4965,31 +5082,34 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E52" s="3">
         <v>1200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1300</v>
-      </c>
-      <c r="F52" s="3">
-        <v>1400</v>
       </c>
       <c r="G52" s="3">
         <v>1400</v>
       </c>
       <c r="H52" s="3">
+        <v>1400</v>
+      </c>
+      <c r="I52" s="3">
         <v>1500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1600</v>
-      </c>
-      <c r="J52" s="3">
-        <v>1700</v>
       </c>
       <c r="K52" s="3">
         <v>1700</v>
@@ -4998,82 +5118,85 @@
         <v>1700</v>
       </c>
       <c r="M52" s="3">
+        <v>1700</v>
+      </c>
+      <c r="N52" s="3">
         <v>5600</v>
-      </c>
-      <c r="N52" s="3">
-        <v>5900</v>
       </c>
       <c r="O52" s="3">
         <v>5900</v>
       </c>
       <c r="P52" s="3">
-        <v>4700</v>
+        <v>5900</v>
       </c>
       <c r="Q52" s="3">
         <v>4700</v>
       </c>
       <c r="R52" s="3">
+        <v>4700</v>
+      </c>
+      <c r="S52" s="3">
         <v>4600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>3400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>3300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>2900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>5300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>3900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>3000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>2300</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>3500</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>4800</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>2700</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>9400</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1200</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>1900</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5179,115 +5302,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>463700</v>
+      </c>
+      <c r="E54" s="3">
         <v>452400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>533100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>488600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>471400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>491200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>526000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>503100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>488400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>527500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>547700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>493300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>502800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>515600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>508200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>463200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>482200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>514900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>554700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>506200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>505600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>474100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>518100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>434100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>418900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>295300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>324500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>270400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>249000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>223100</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>252900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>181700</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>160000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>156000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>155600</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5325,8 +5454,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5364,153 +5494,157 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>45900</v>
+      </c>
+      <c r="E57" s="3">
         <v>73900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>104500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>77600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>37400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>51100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>53500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>59300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>36100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>56500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>77800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>53600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>54500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>45400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>59200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>37700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>40100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>33600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>57100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>40100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>34400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>33100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>55400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>36300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>26700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>25400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>34200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>19500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>14600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>17300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>30100</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>17800</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>10700</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>9300</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>19300</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>83400</v>
+      </c>
+      <c r="E58" s="3">
         <v>19000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>62900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>19400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>31700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>20400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>55900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>19800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>19400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>19200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>13600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>3500</v>
-      </c>
-      <c r="O58" s="3">
-        <v>3400</v>
       </c>
       <c r="P58" s="3">
         <v>3400</v>
@@ -5519,388 +5653,400 @@
         <v>3400</v>
       </c>
       <c r="R58" s="3">
+        <v>3400</v>
+      </c>
+      <c r="S58" s="3">
         <v>3300</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>20800</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>5800</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>5700</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>4800</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>2200</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>3200</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>2100</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1600</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>800</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>200</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>600</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>21800</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>100</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>3000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>2400</v>
-      </c>
-      <c r="AI58" s="3">
-        <v>700</v>
       </c>
       <c r="AJ58" s="3">
         <v>700</v>
       </c>
       <c r="AK58" s="3">
+        <v>700</v>
+      </c>
+      <c r="AL58" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>20700</v>
+      </c>
+      <c r="E59" s="3">
         <v>28400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>22900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>23900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>19400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>26300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>21400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>20400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>22000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>31000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>49900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>43000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>50200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>67200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>54200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>44700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>49800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>56300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>43500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>39200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>46000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>54500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>38000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>33500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>35200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>26700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>30700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>22800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>33200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>32900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>25700</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>17500</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>25300</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>25000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>17400</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>157000</v>
+      </c>
+      <c r="E60" s="3">
         <v>128600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>203600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>127000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>95500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>105600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>141200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>107200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>87900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>118300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>141300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>100100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>108200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>116000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>116700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>85700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>110700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>95700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>106300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>84100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>82600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>79800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>95500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>71400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>62700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>52600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>65200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>42800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>69600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>50300</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>58800</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>37800</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>36700</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>35100</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>38800</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>140500</v>
+      </c>
+      <c r="E61" s="3">
         <v>144100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>144200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>148900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>160600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>165800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>170900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>172400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>176400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>180700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>64300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>65100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>66000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>66900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>67700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>68600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>69400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>116300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>160700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>141400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>149800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>103500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>156500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>99200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>77500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>67900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>111200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>76900</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>35600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>28000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>70000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>20200</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>4800</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>3400</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5931,71 +6077,71 @@
       <c r="L62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M62" s="3">
+      <c r="M62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N62" s="3">
         <v>123500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>103700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>107200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>110000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>118500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>107000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>110100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>112500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>119000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>113200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>112400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>123100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>113100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>110200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>127900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>14700</v>
-      </c>
-      <c r="AC62" s="3">
-        <v>5500</v>
       </c>
       <c r="AD62" s="3">
         <v>5500</v>
       </c>
       <c r="AE62" s="3">
+        <v>5500</v>
+      </c>
+      <c r="AF62" s="3">
         <v>5400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>5500</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>4800</v>
-      </c>
-      <c r="AH62" s="3">
-        <v>3700</v>
       </c>
       <c r="AI62" s="3">
         <v>3700</v>
@@ -6004,10 +6150,13 @@
         <v>3700</v>
       </c>
       <c r="AK62" s="3">
+        <v>3700</v>
+      </c>
+      <c r="AL62" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6113,8 +6262,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6220,8 +6372,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6327,115 +6482,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>298800</v>
+      </c>
+      <c r="E66" s="3">
         <v>272800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>348000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>275900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>256100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>271500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>312100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>279700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>264300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>300300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>325800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>265700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>278200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>289700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>300400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>258800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>287800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>321500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>383700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>336500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>342600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>295800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>364600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>280400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>267800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>135000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>185300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>128500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>113900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>87000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>136800</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>65300</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>48100</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>44800</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>58700</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6473,8 +6634,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6580,8 +6742,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6687,8 +6852,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6794,8 +6962,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6901,115 +7072,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>62400</v>
+      </c>
+      <c r="E72" s="3">
         <v>77700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>83700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>112200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>115900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>121400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>116800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>127300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>129300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>133200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>125700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>131900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>129600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>130900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>113500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>110700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>101700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>101200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>79300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>78400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>72500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>87600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>63200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>63000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>61100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>70600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>50000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>53100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>46700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>48100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>28600</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>29400</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>25100</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>24700</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>10700</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7115,8 +7292,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7222,8 +7402,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7329,115 +7512,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>167900</v>
+      </c>
+      <c r="E76" s="3">
         <v>182700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>188100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>215700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>218400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>222800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>217100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>226700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>227300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>230400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>221900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>227600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>224600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>225900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>207800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>204400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>194400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>193500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>171100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>169700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>163100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>178300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>153500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>153700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>151100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>160300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>139200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>141900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>135100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>136100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>116100</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>116400</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>111900</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>111200</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>96900</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7543,227 +7732,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45781</v>
+      </c>
+      <c r="E80" s="2">
         <v>45690</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45592</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45501</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45410</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45319</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45228</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45137</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45046</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44955</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44864</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44773</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44682</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44591</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44500</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44409</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44318</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44227</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44136</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44045</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43954</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43863</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43772</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43681</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43590</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43499</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43401</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43310</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43219</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43128</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43037</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42946</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42855</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42764</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42673</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-15300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-3500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-28500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-3700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-7900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>6400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-10500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-2000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-3900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>7400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-6200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>17400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>2800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>9000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>21800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>5900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-15100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>24400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-7600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>20600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-3200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>6400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>19500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>4300</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>400</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>14000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7801,115 +7999,119 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E83" s="3">
         <v>8500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>8600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>7500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>7400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>7700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>7600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>7900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>7500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>7200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>7600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>7900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>7500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>7400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>7300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>7200</v>
-      </c>
-      <c r="S83" s="3">
-        <v>7300</v>
       </c>
       <c r="T83" s="3">
         <v>7300</v>
       </c>
       <c r="U83" s="3">
+        <v>7300</v>
+      </c>
+      <c r="V83" s="3">
         <v>7900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>6600</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>6700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>6100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>6500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>5000</v>
-      </c>
-      <c r="AA83" s="3">
-        <v>4400</v>
       </c>
       <c r="AB83" s="3">
         <v>4400</v>
       </c>
       <c r="AC83" s="3">
+        <v>4400</v>
+      </c>
+      <c r="AD83" s="3">
         <v>3100</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>2800</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>2300</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>2200</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>1800</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>1700</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>1600</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>1500</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8015,8 +8217,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8122,8 +8327,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8229,8 +8437,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8336,8 +8547,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8443,115 +8657,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-56500</v>
+      </c>
+      <c r="E89" s="3">
         <v>41200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-41100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>16600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-33700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>69700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-29800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>12700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-14000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>49600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-9900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-9400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-31700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>59200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>6200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>14100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>12400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>79400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-15800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>20700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-33500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>56000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-39600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>5100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-13100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>54600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-10900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-1600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-11000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>64800</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-22800</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-8600</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-3500</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>47000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-27900</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8589,115 +8809,119 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-9100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-8500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-10100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-21400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-5400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-14900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-3000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-2000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-2200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-4800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-4100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-3500</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-7100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-5800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-8000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-7200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-19100</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-12800</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-14000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-9000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-17400</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-11700</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-8300</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-7600</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-6500</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8803,8 +9027,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8910,115 +9137,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-8900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-8400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-10000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-21300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-5400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-14900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-3800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-4100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-2900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-2000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-2300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-5000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-4100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-6100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-7800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-7000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-9800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-7400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-19000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-13400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-14000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-11900</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-17300</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-18900</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-7700</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-7900</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-7200</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9056,8 +9289,9 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9088,8 +9322,8 @@
       <c r="L96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -9163,8 +9397,11 @@
       <c r="AK96" s="3">
         <v>0</v>
       </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9270,8 +9507,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9377,8 +9617,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9484,115 +9727,121 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>63000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-44700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>43200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-12000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>9800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-36800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>35200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-10700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>9300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1100</v>
-      </c>
-      <c r="P100" s="3">
-        <v>-700</v>
       </c>
       <c r="Q100" s="3">
         <v>-700</v>
       </c>
       <c r="R100" s="3">
+        <v>-700</v>
+      </c>
+      <c r="S100" s="3">
         <v>-18300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-31600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-44300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>11800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-5800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>44700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-51500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>45200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>5500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>22400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-47300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>29500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>14400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>22000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-51800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>39300</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>16400</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>800</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-15300</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>11900</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9623,8 +9872,8 @@
       <c r="L101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -9698,111 +9947,117 @@
       <c r="AK101" s="3">
         <v>0</v>
       </c>
+      <c r="AL101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-6000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>3000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-25400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>24000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-3000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-36300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>36100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-6000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-25000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-36700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>57300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-7100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-21200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>34400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-6400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>9900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>7100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-2200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>3600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-3000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>1200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-800</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-11100</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-10500</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>23900</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-23100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DLTH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DLTH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="92">
   <si>
     <t>DLTH</t>
   </si>
@@ -656,508 +656,520 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AM102"/>
+  <dimension ref="A5:AN102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45963</v>
+      </c>
+      <c r="E7" s="2">
         <v>45872</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45781</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45690</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45592</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45501</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45410</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45319</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45228</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45137</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45046</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44955</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44864</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44773</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44682</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44591</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44500</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44409</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44318</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44227</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44136</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44045</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43954</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43863</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43772</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43681</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43590</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43499</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43401</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43310</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43219</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43128</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43037</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42946</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42855</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42764</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42673</v>
       </c>
     </row>
-    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>114900</v>
+      </c>
+      <c r="E8" s="3">
         <v>131700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>102700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>241300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>127100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>141600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>116700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>245600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>138200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>139100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>123800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>241800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>147100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>141500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>122900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>270800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>145300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>149100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>133400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>256000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>135500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>137400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>109900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>259600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>119800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>122000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>114200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>250500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>106700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>110700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>100200</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>217800</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>83700</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>86200</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>83700</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>174700</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>67000</v>
       </c>
     </row>
-    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>53000</v>
+      </c>
+      <c r="E9" s="3">
         <v>59700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>49300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>134800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>60600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>67600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>55100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>127200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>68800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>67600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>58100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>117900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>70200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>65900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>55800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>125100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>61600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>67700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>66900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>120300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>64500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>64900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>57600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>122600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>54400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>57200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>53300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>119300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>45700</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>48400</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>44300</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>101800</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>36300</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>37300</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>35000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>77900</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>28300</v>
       </c>
     </row>
-    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>61800</v>
+      </c>
+      <c r="E10" s="3">
         <v>72000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>53400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>106500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>66400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>74000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>61600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>118400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>69400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>71500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>65700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>123800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>76900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>75600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>67100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>145700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>83700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>81400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>66500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>135700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>71000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>72500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>52300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>137000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>65400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>64800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>60900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>131200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>61000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>62300</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>55900</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>116000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>47400</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>48900</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>48700</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>96800</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>38700</v>
       </c>
     </row>
-    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1197,8 +1209,9 @@
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
+      <c r="AN11" s="3"/>
     </row>
-    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1310,8 +1323,11 @@
       <c r="AM12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AN12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1423,29 +1439,32 @@
       <c r="AM13" s="3">
         <v>0</v>
       </c>
+      <c r="AN13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3">
         <v>900</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
+      <c r="F14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>6200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>1600</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1461,8 +1480,8 @@
       <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1473,8 +1492,8 @@
       <c r="R14" s="3">
         <v>0</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>8</v>
+      <c r="S14" s="3">
+        <v>0</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>8</v>
@@ -1491,12 +1510,12 @@
       <c r="X14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Y14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z14" s="3">
         <v>1600</v>
       </c>
-      <c r="Z14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1512,8 +1531,8 @@
       <c r="AE14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF14" s="3">
-        <v>0</v>
+      <c r="AF14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AG14" s="3">
         <v>0</v>
@@ -1536,8 +1555,11 @@
       <c r="AM14" s="3">
         <v>0</v>
       </c>
+      <c r="AN14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1554,10 +1576,10 @@
         <v>1000</v>
       </c>
       <c r="H15" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I15" s="3">
         <v>1100</v>
-      </c>
-      <c r="I15" s="3">
-        <v>1200</v>
       </c>
       <c r="J15" s="3">
         <v>1200</v>
@@ -1575,7 +1597,7 @@
         <v>1200</v>
       </c>
       <c r="O15" s="3">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="P15" s="3">
         <v>800</v>
@@ -1602,26 +1624,26 @@
         <v>800</v>
       </c>
       <c r="X15" s="3">
+        <v>800</v>
+      </c>
+      <c r="Y15" s="3">
         <v>900</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>700</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>200</v>
-      </c>
-      <c r="AA15" s="3">
-        <v>500</v>
       </c>
       <c r="AB15" s="3">
         <v>500</v>
       </c>
       <c r="AC15" s="3">
+        <v>500</v>
+      </c>
+      <c r="AD15" s="3">
         <v>100</v>
       </c>
-      <c r="AD15" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE15" s="3" t="s">
         <v>8</v>
       </c>
@@ -1631,8 +1653,8 @@
       <c r="AG15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH15" s="3">
-        <v>0</v>
+      <c r="AH15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AI15" s="3">
         <v>0</v>
@@ -1649,8 +1671,11 @@
       <c r="AM15" s="3">
         <v>0</v>
       </c>
+      <c r="AN15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1687,234 +1712,241 @@
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
+      <c r="AN16" s="3"/>
     </row>
-    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>123700</v>
+      </c>
+      <c r="E17" s="3">
         <v>128500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>115100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>242700</v>
       </c>
-      <c r="G17" s="3">
-        <v>143500</v>
-      </c>
       <c r="H17" s="3">
+        <v>143000</v>
+      </c>
+      <c r="I17" s="3">
         <v>141600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>125700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>236800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>150600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>140500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>128300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>231100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>154500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>137600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>123800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>246500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>140400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>136000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>131500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>225400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>132700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>127600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>128900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>226500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>118400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>118200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>123900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>220400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>109300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>100800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>100500</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>188300</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>84300</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>78800</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>82900</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>151800</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>66200</v>
       </c>
     </row>
-    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="E18" s="3">
         <v>3300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-12400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-1400</v>
       </c>
-      <c r="G18" s="3">
-        <v>-16400</v>
-      </c>
       <c r="H18" s="3">
-        <v>0</v>
+        <v>-15900</v>
       </c>
       <c r="I18" s="3">
+        <v>0</v>
+      </c>
+      <c r="J18" s="3">
         <v>-9000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>8900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-12400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-4500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>10700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-7400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>3900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>24300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>4900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>13100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>30600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>2800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>9800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-19000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>33100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>3800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-9700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>30100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-2600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>9900</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>29500</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-600</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>7400</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>800</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>22900</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1954,112 +1986,113 @@
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
+      <c r="AN19" s="3"/>
     </row>
-    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
         <v>100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>200</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
         <v>0</v>
       </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>-100</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>-600</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M20" s="3">
         <v>-100</v>
       </c>
       <c r="N20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="O20" s="3">
         <v>-200</v>
-      </c>
-      <c r="O20" s="3">
-        <v>100</v>
       </c>
       <c r="P20" s="3">
         <v>100</v>
       </c>
       <c r="Q20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>100</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W20" s="3">
         <v>100</v>
       </c>
       <c r="X20" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-300</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>100</v>
       </c>
       <c r="Z20" s="3">
         <v>100</v>
       </c>
       <c r="AA20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB20" s="3">
         <v>0</v>
       </c>
       <c r="AC20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="3">
         <v>200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>300</v>
       </c>
-      <c r="AE20" s="3">
-        <v>0</v>
-      </c>
       <c r="AF20" s="3">
         <v>0</v>
       </c>
       <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH20" s="3">
         <v>200</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>300</v>
-      </c>
-      <c r="AI20" s="3">
-        <v>100</v>
       </c>
       <c r="AJ20" s="3">
         <v>100</v>
       </c>
       <c r="AK20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AL20" s="3">
         <v>0</v>
@@ -2067,150 +2100,156 @@
       <c r="AM20" s="3">
         <v>0</v>
       </c>
+      <c r="AN20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="E21" s="3">
         <v>4200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-11500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-400</v>
       </c>
-      <c r="G21" s="3">
-        <v>-15400</v>
-      </c>
       <c r="H21" s="3">
+        <v>-14900</v>
+      </c>
+      <c r="I21" s="3">
         <v>1300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-7800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>10600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-11200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-3200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>12000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>11800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>6600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>31900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>11900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>20400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>9200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>38000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>10900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>16100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-12200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>39300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>7900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>8700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-5100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>34700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>12700</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>2200</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>32000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1300</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>9200</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>2400</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>24400</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>1500</v>
+        <v>1200</v>
       </c>
       <c r="E22" s="3">
         <v>1500</v>
       </c>
       <c r="F22" s="3">
-        <v>1300</v>
+        <v>1500</v>
       </c>
       <c r="G22" s="3">
         <v>1300</v>
       </c>
       <c r="H22" s="3">
-        <v>1000</v>
+        <v>1300</v>
       </c>
       <c r="I22" s="3">
         <v>1000</v>
       </c>
       <c r="J22" s="3">
+        <v>1000</v>
+      </c>
+      <c r="K22" s="3">
         <v>1100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1200</v>
-      </c>
-      <c r="L22" s="3">
-        <v>900</v>
       </c>
       <c r="M22" s="3">
         <v>900</v>
@@ -2219,308 +2258,317 @@
         <v>900</v>
       </c>
       <c r="O22" s="3">
+        <v>900</v>
+      </c>
+      <c r="P22" s="3">
         <v>1000</v>
-      </c>
-      <c r="P22" s="3">
-        <v>900</v>
       </c>
       <c r="Q22" s="3">
         <v>900</v>
       </c>
       <c r="R22" s="3">
+        <v>900</v>
+      </c>
+      <c r="S22" s="3">
         <v>1300</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>900</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>1200</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>1300</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>1500</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>1600</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>1800</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>1400</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>1300</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>1500</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>1200</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>800</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>2300</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>1600</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>1200</v>
-      </c>
-      <c r="AG22" s="3">
-        <v>800</v>
       </c>
       <c r="AH22" s="3">
         <v>800</v>
       </c>
       <c r="AI22" s="3">
+        <v>800</v>
+      </c>
+      <c r="AJ22" s="3">
         <v>700</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>400</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>200</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>100</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="E23" s="3">
         <v>900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-14000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-2700</v>
       </c>
-      <c r="G23" s="3">
-        <v>-23800</v>
-      </c>
       <c r="H23" s="3">
+        <v>-23300</v>
+      </c>
+      <c r="I23" s="3">
         <v>-2400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-9900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>8300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-13600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-2200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-5300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>9900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-8300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>3100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-1800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>23200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>3700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>12000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>29200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>7800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-20300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>31800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>2500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-10300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>28000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-4100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>8700</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>29000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-1200</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>7100</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>600</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>22900</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="3">
         <v>-400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>800</v>
       </c>
-      <c r="G24" s="3">
-        <v>4700</v>
-      </c>
       <c r="H24" s="3">
+        <v>4900</v>
+      </c>
+      <c r="I24" s="3">
         <v>-500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-2100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-3100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-1500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>2500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-2100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>5800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>3000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>7500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-5100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>7600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-2700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>7500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-1100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>2200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-200</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>10900</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-500</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>2700</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>200</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>8800</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2632,234 +2680,243 @@
       <c r="AM25" s="3">
         <v>0</v>
       </c>
+      <c r="AN25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="E26" s="3">
         <v>1300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-15300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-3500</v>
       </c>
-      <c r="G26" s="3">
-        <v>-28500</v>
-      </c>
       <c r="H26" s="3">
+        <v>-28200</v>
+      </c>
+      <c r="I26" s="3">
         <v>-2000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-7900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>6400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-10500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-2000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-3900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>7500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-6200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-1300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>17300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>2800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>8900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>21800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>5900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-15200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>24200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-7600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>20500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-3100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>6500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-700</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>18100</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-700</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>4400</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>400</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>14000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="E27" s="3">
         <v>1300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-15300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-3500</v>
       </c>
-      <c r="G27" s="3">
-        <v>-28500</v>
-      </c>
       <c r="H27" s="3">
+        <v>-28200</v>
+      </c>
+      <c r="I27" s="3">
         <v>-2000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-7900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>6400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-10500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-2000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-3900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>7400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-6200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-1300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>17400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>2800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>9000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>21800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>5900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-15100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>24400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-7600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>20600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-3200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>6400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-700</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>18000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-800</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>4300</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>400</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>14000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2971,8 +3028,11 @@
       <c r="AM28" s="3">
         <v>0</v>
       </c>
+      <c r="AN28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3048,8 +3108,8 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
+      <c r="AB29" s="3">
+        <v>0</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
@@ -3066,12 +3126,12 @@
       <c r="AG29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AH29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI29" s="3">
         <v>1500</v>
       </c>
-      <c r="AI29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ29" s="3" t="s">
         <v>8</v>
       </c>
@@ -3084,8 +3144,11 @@
       <c r="AM29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AN29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3197,8 +3260,11 @@
       <c r="AM30" s="3">
         <v>0</v>
       </c>
+      <c r="AN30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3310,112 +3376,115 @@
       <c r="AM31" s="3">
         <v>0</v>
       </c>
+      <c r="AN31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
         <v>-100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-200</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
         <v>0</v>
       </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>100</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>600</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M32" s="3">
         <v>100</v>
       </c>
       <c r="N32" s="3">
+        <v>100</v>
+      </c>
+      <c r="O32" s="3">
         <v>200</v>
-      </c>
-      <c r="O32" s="3">
-        <v>-100</v>
       </c>
       <c r="P32" s="3">
         <v>-100</v>
       </c>
       <c r="Q32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>-200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-100</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W32" s="3">
         <v>-100</v>
       </c>
       <c r="X32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Y32" s="3">
         <v>300</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>-100</v>
       </c>
       <c r="Z32" s="3">
         <v>-100</v>
       </c>
       <c r="AA32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AB32" s="3">
         <v>0</v>
       </c>
       <c r="AC32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="3">
         <v>-200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-300</v>
       </c>
-      <c r="AE32" s="3">
-        <v>0</v>
-      </c>
       <c r="AF32" s="3">
         <v>0</v>
       </c>
       <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH32" s="3">
         <v>-200</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-300</v>
-      </c>
-      <c r="AI32" s="3">
-        <v>-100</v>
       </c>
       <c r="AJ32" s="3">
         <v>-100</v>
       </c>
       <c r="AK32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AL32" s="3">
         <v>0</v>
@@ -3423,121 +3492,127 @@
       <c r="AM32" s="3">
         <v>0</v>
       </c>
+      <c r="AN32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="E33" s="3">
         <v>1300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-15300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-3500</v>
       </c>
-      <c r="G33" s="3">
-        <v>-28500</v>
-      </c>
       <c r="H33" s="3">
+        <v>-28200</v>
+      </c>
+      <c r="I33" s="3">
         <v>-2000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-7900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>6400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-10500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-2000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-3900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>7400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-6200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-1300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>17400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>2800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>9000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>21800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>5900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-15100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>24400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-7600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>20600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-3200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>6400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-700</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>19500</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-800</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>4300</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>400</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>14000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3649,239 +3724,248 @@
       <c r="AM34" s="3">
         <v>0</v>
       </c>
+      <c r="AN34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="E35" s="3">
         <v>1300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-15300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-3500</v>
       </c>
-      <c r="G35" s="3">
-        <v>-28500</v>
-      </c>
       <c r="H35" s="3">
+        <v>-28200</v>
+      </c>
+      <c r="I35" s="3">
         <v>-2000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-7900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>6400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-10500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-2000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-3900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>7400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-6200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-1300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>17400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>2800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>9000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>21800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>5900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-15100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>24400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-7600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>20600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-3200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>6400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-700</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>19500</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-800</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>4300</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>400</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>14000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45963</v>
+      </c>
+      <c r="E38" s="2">
         <v>45872</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45781</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45690</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45592</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45501</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45410</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45319</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45228</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45137</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45046</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44955</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44864</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44773</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44682</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44591</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44500</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44409</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44318</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44227</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44136</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44045</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43954</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43863</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43772</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43681</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43590</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43499</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43401</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43310</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43219</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43128</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43037</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42946</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42855</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42764</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42673</v>
       </c>
     </row>
-    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3921,8 +4005,9 @@
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
+      <c r="AN39" s="3"/>
     </row>
-    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3962,121 +4047,125 @@
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
+      <c r="AN40" s="3"/>
     </row>
-    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E41" s="3">
         <v>5700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>8600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>9300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>9800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>6800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>32200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>8200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>11100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>9200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>45500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>9400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>15400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>40400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>77100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>20400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>18900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>26100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>46600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>12800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>19000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>8900</v>
-      </c>
-      <c r="Z41" s="3">
-        <v>2200</v>
       </c>
       <c r="AA41" s="3">
         <v>2200</v>
       </c>
       <c r="AB41" s="3">
+        <v>2200</v>
+      </c>
+      <c r="AC41" s="3">
         <v>3500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>2500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>2400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1200</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>2900</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1400</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>13600</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>24000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4188,540 +4277,555 @@
       <c r="AM42" s="3">
         <v>0</v>
       </c>
+      <c r="AN42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E43" s="3">
         <v>10900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>6000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>6300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>6700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>10700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>12800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>9400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>7900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>7800</v>
-      </c>
-      <c r="M43" s="3">
-        <v>8400</v>
       </c>
       <c r="N43" s="3">
         <v>8400</v>
       </c>
       <c r="O43" s="3">
+        <v>8400</v>
+      </c>
+      <c r="P43" s="3">
         <v>10200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>7600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>6900</v>
-      </c>
-      <c r="R43" s="3">
-        <v>7700</v>
       </c>
       <c r="S43" s="3">
         <v>7700</v>
       </c>
       <c r="T43" s="3">
+        <v>7700</v>
+      </c>
+      <c r="U43" s="3">
         <v>4900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>4600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>5300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>7000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>7600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>5400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>3400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>8200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>7100</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>8700</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>4600</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>3200</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>400</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>600</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>300</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>1700</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>500</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>1100</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>400</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>192200</v>
+      </c>
+      <c r="E44" s="3">
         <v>148100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>176100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>166500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>231400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>168700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>136400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>125800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>174000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>157100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>145000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>154900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>204700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>164500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>152200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>122700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>165100</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>134900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>144200</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>149100</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>213400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>167600</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>175000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>147800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>183100</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>114800</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>104300</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>97700</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>131400</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>102400</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>98000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>89500</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>129500</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>84700</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>75700</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>70400</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>96700</v>
       </c>
     </row>
-    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E45" s="3">
         <v>4700</v>
-      </c>
-      <c r="E45" s="3">
-        <v>3700</v>
       </c>
       <c r="F45" s="3">
         <v>3700</v>
       </c>
       <c r="G45" s="3">
+        <v>3700</v>
+      </c>
+      <c r="H45" s="3">
         <v>4600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>15700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>15100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>14600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>15100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>13400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>11200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>9700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>8700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>9700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>7600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>7700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>8800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>10700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>12000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>12200</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>15100</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>13100</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>11500</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>9800</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>9100</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>13300</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>9500</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>5400</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>6400</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>8300</v>
       </c>
     </row>
-    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>228700</v>
+      </c>
+      <c r="E46" s="3">
         <v>185900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>211100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>191600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>264300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>206900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>171400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>181000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>203500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>191800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>176500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>221700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>240000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>202500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>214100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>222500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>206600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>169800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>184600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>209700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>242900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>201800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>197000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>162200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>204300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>137500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>126100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>118200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>150200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>116600</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>109600</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>101800</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>145400</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>96100</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>95900</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>101200</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>108200</v>
       </c>
     </row>
-    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E47" s="3">
         <v>4800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>4900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>4500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>4800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>4900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>4800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>5000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>4900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>5300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>5400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>5500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>5300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>5800</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>6100</v>
-      </c>
-      <c r="R47" s="3">
-        <v>6600</v>
       </c>
       <c r="S47" s="3">
         <v>6600</v>
       </c>
       <c r="T47" s="3">
+        <v>6600</v>
+      </c>
+      <c r="U47" s="3">
         <v>6700</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>6300</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>6100</v>
-      </c>
-      <c r="W47" s="3">
-        <v>6000</v>
       </c>
       <c r="X47" s="3">
         <v>6000</v>
       </c>
       <c r="Y47" s="3">
+        <v>6000</v>
+      </c>
+      <c r="Z47" s="3">
         <v>5700</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>6400</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>6500</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>6200</v>
-      </c>
-      <c r="AC47" s="3">
-        <v>6300</v>
       </c>
       <c r="AD47" s="3">
         <v>6300</v>
@@ -4741,8 +4845,8 @@
       <c r="AI47" s="3">
         <v>6300</v>
       </c>
-      <c r="AJ47" s="3" t="s">
-        <v>8</v>
+      <c r="AJ47" s="3">
+        <v>6300</v>
       </c>
       <c r="AK47" s="3" t="s">
         <v>8</v>
@@ -4753,171 +4857,177 @@
       <c r="AM47" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AN47" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>223800</v>
+      </c>
+      <c r="E48" s="3">
         <v>231900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>238500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>247200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>252500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>263600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>282400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>294500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>304100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>297800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>297700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>291500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>295900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>278300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>276100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>281100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>289600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>281300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>287200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>295200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>304600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>296600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>301100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>304200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>303800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>284400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>282200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>334200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>165900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>144800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>129200</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>109700</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>98200</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>75700</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>62500</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>52400</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>45300</v>
       </c>
     </row>
-    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>9300</v>
+      </c>
+      <c r="E49" s="3">
         <v>9800</v>
-      </c>
-      <c r="E49" s="3">
-        <v>7900</v>
       </c>
       <c r="F49" s="3">
         <v>7900</v>
       </c>
       <c r="G49" s="3">
+        <v>7900</v>
+      </c>
+      <c r="H49" s="3">
         <v>10100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>7600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>8200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>7500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>8300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>6200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>6900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>7000</v>
-      </c>
-      <c r="O49" s="3">
-        <v>900</v>
       </c>
       <c r="P49" s="3">
         <v>900</v>
       </c>
       <c r="Q49" s="3">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="R49" s="3">
         <v>600</v>
       </c>
       <c r="S49" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="T49" s="3">
         <v>700</v>
@@ -4938,22 +5048,22 @@
         <v>700</v>
       </c>
       <c r="Z49" s="3">
+        <v>700</v>
+      </c>
+      <c r="AA49" s="3">
         <v>1700</v>
-      </c>
-      <c r="AA49" s="3">
-        <v>700</v>
       </c>
       <c r="AB49" s="3">
         <v>700</v>
       </c>
       <c r="AC49" s="3">
+        <v>700</v>
+      </c>
+      <c r="AD49" s="3">
         <v>400</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>700</v>
-      </c>
-      <c r="AE49" s="3">
-        <v>400</v>
       </c>
       <c r="AF49" s="3">
         <v>400</v>
@@ -4979,8 +5089,11 @@
       <c r="AM49" s="3">
         <v>400</v>
       </c>
+      <c r="AN49" s="3">
+        <v>400</v>
+      </c>
     </row>
-    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5092,8 +5205,11 @@
       <c r="AM50" s="3">
         <v>0</v>
       </c>
+      <c r="AN50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5205,37 +5321,40 @@
       <c r="AM51" s="3">
         <v>0</v>
       </c>
+      <c r="AN51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="E52" s="3">
         <v>1400</v>
       </c>
       <c r="F52" s="3">
+        <v>1400</v>
+      </c>
+      <c r="G52" s="3">
         <v>1200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1300</v>
-      </c>
-      <c r="H52" s="3">
-        <v>1400</v>
       </c>
       <c r="I52" s="3">
         <v>1400</v>
       </c>
       <c r="J52" s="3">
+        <v>1400</v>
+      </c>
+      <c r="K52" s="3">
         <v>1500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1600</v>
-      </c>
-      <c r="L52" s="3">
-        <v>1700</v>
       </c>
       <c r="M52" s="3">
         <v>1700</v>
@@ -5244,82 +5363,85 @@
         <v>1700</v>
       </c>
       <c r="O52" s="3">
+        <v>1700</v>
+      </c>
+      <c r="P52" s="3">
         <v>5600</v>
-      </c>
-      <c r="P52" s="3">
-        <v>5900</v>
       </c>
       <c r="Q52" s="3">
         <v>5900</v>
       </c>
       <c r="R52" s="3">
-        <v>4700</v>
+        <v>5900</v>
       </c>
       <c r="S52" s="3">
         <v>4700</v>
       </c>
       <c r="T52" s="3">
+        <v>4700</v>
+      </c>
+      <c r="U52" s="3">
         <v>4600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>3400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>3300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>2900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>5300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>3900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>3000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1700</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>2300</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>3500</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>4800</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>2700</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>9400</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>1200</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>1900</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5431,121 +5553,127 @@
       <c r="AM53" s="3">
         <v>0</v>
       </c>
+      <c r="AN53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>468000</v>
+      </c>
+      <c r="E54" s="3">
         <v>433800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>463700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>452400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>533100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>488600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>471400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>491200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>526000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>503100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>488400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>527500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>547700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>493300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>502800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>515600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>508200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>463200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>482200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>514900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>554700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>506200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>505600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>474100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>518100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>434100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>418900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>295300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>324500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>270400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>249000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>223100</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>252900</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>181700</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>160000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>156000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>155600</v>
       </c>
     </row>
-    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5585,8 +5713,9 @@
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
+      <c r="AN55" s="3"/>
     </row>
-    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5626,165 +5755,169 @@
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
+      <c r="AN56" s="3"/>
     </row>
-    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>80200</v>
+      </c>
+      <c r="E57" s="3">
         <v>43600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>45900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>73900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>104500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>77600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>37400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>51100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>53500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>59300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>36100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>56500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>77800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>53600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>54500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>45400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>59200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>37700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>40100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>33600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>57100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>40100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>34400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>33100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>55400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>36300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>26700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>25400</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>34200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>19500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>14600</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>17300</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>30100</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>17800</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>10700</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>9300</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>19300</v>
       </c>
     </row>
-    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>64600</v>
+      </c>
+      <c r="E58" s="3">
         <v>52200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>83400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>19000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>62900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>19400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>31700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>20400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>55900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>19800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>19400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>19200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>13600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>3500</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>3400</v>
       </c>
       <c r="R58" s="3">
         <v>3400</v>
@@ -5793,406 +5926,418 @@
         <v>3400</v>
       </c>
       <c r="T58" s="3">
+        <v>3400</v>
+      </c>
+      <c r="U58" s="3">
         <v>3300</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>20800</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>5800</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>5700</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>4800</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>2200</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>3200</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>2100</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1600</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>800</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>200</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>600</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>21800</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>100</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>3000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>2400</v>
-      </c>
-      <c r="AK58" s="3">
-        <v>700</v>
       </c>
       <c r="AL58" s="3">
         <v>700</v>
       </c>
       <c r="AM58" s="3">
+        <v>700</v>
+      </c>
+      <c r="AN58" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>24400</v>
+      </c>
+      <c r="E59" s="3">
         <v>25100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>20700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>28400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>22900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>23900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>19400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>26300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>21400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>20400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>22000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>31000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>49900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>43000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>50200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>67200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>54200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>44700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>49800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>56300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>43500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>39200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>46000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>54500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>38000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>33500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>35200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>26700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>30700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>22800</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>33200</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>32900</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>25700</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>17500</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>25300</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>25000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>17400</v>
       </c>
     </row>
-    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>177700</v>
+      </c>
+      <c r="E60" s="3">
         <v>129100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>157000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>128600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>203600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>127000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>95500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>105600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>141200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>107200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>87900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>118300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>141300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>100100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>108200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>116000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>116700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>85700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>110700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>95700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>106300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>84100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>82600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>79800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>95500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>71400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>62700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>52600</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>65200</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>42800</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>69600</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>50300</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>58800</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>37800</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>36700</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>35100</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>38800</v>
       </c>
     </row>
-    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>131700</v>
+      </c>
+      <c r="E61" s="3">
         <v>136800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>140500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>144100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>144200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>148900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>160600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>165800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>170900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>172400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>176400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>180700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>64300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>65100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>66000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>66900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>67700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>68600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>69400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>116300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>160700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>141400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>149800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>103500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>156500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>99200</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>77500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>67900</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>111200</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>76900</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>35600</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>28000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>70000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>20200</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>4800</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>3400</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -6229,71 +6374,71 @@
       <c r="N62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O62" s="3">
+      <c r="O62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P62" s="3">
         <v>123500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>103700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>107200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>110000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>118500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>107000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>110100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>112500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>119000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>113200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>112400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>123100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>113100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>110200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>127900</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>14700</v>
-      </c>
-      <c r="AE62" s="3">
-        <v>5500</v>
       </c>
       <c r="AF62" s="3">
         <v>5500</v>
       </c>
       <c r="AG62" s="3">
+        <v>5500</v>
+      </c>
+      <c r="AH62" s="3">
         <v>5400</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>5500</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>4800</v>
-      </c>
-      <c r="AJ62" s="3">
-        <v>3700</v>
       </c>
       <c r="AK62" s="3">
         <v>3700</v>
@@ -6302,10 +6447,13 @@
         <v>3700</v>
       </c>
       <c r="AM62" s="3">
+        <v>3700</v>
+      </c>
+      <c r="AN62" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6417,8 +6565,11 @@
       <c r="AM63" s="3">
         <v>0</v>
       </c>
+      <c r="AN63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6530,8 +6681,11 @@
       <c r="AM64" s="3">
         <v>0</v>
       </c>
+      <c r="AN64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6643,121 +6797,127 @@
       <c r="AM65" s="3">
         <v>0</v>
       </c>
+      <c r="AN65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>310300</v>
+      </c>
+      <c r="E66" s="3">
         <v>266700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>298800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>272800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>348000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>275900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>256100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>271500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>312100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>279700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>264300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>300300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>325800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>265700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>278200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>289700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>300400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>258800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>287800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>321500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>383700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>336500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>342600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>295800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>364600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>280400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>267800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>135000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>185300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>128500</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>113900</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>87000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>136800</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>65300</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>48100</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>44800</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>58700</v>
       </c>
     </row>
-    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6797,8 +6957,9 @@
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
+      <c r="AN67" s="3"/>
     </row>
-    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6910,8 +7071,11 @@
       <c r="AM68" s="3">
         <v>0</v>
       </c>
+      <c r="AN68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7023,8 +7187,11 @@
       <c r="AM69" s="3">
         <v>0</v>
       </c>
+      <c r="AN69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7136,8 +7303,11 @@
       <c r="AM70" s="3">
         <v>0</v>
       </c>
+      <c r="AN70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7249,121 +7419,127 @@
       <c r="AM71" s="3">
         <v>0</v>
       </c>
+      <c r="AN71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>53600</v>
+      </c>
+      <c r="E72" s="3">
         <v>63700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>62400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>77700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>83700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>112200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>115900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>121400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>116800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>127300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>129300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>133200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>125700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>131900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>129600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>130900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>113500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>110700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>101700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>101200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>79300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>78400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>72500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>87600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>63200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>63000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>61100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>70600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>50000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>53100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>46700</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>48100</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>28600</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>29400</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>25100</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>24700</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>10700</v>
       </c>
     </row>
-    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7475,8 +7651,11 @@
       <c r="AM73" s="3">
         <v>0</v>
       </c>
+      <c r="AN73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7588,8 +7767,11 @@
       <c r="AM74" s="3">
         <v>0</v>
       </c>
+      <c r="AN74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7701,121 +7883,127 @@
       <c r="AM75" s="3">
         <v>0</v>
       </c>
+      <c r="AN75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>160600</v>
+      </c>
+      <c r="E76" s="3">
         <v>170000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>167900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>182700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>188100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>215700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>218400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>222800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>217100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>226700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>227300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>230400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>221900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>227600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>224600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>225900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>207800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>204400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>194400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>193500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>171100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>169700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>163100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>178300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>153500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>153700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>151100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>160300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>139200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>141900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>135100</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>136100</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>116100</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>116400</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>111900</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>111200</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>96900</v>
       </c>
     </row>
-    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7927,239 +8115,248 @@
       <c r="AM77" s="3">
         <v>0</v>
       </c>
+      <c r="AN77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45963</v>
+      </c>
+      <c r="E80" s="2">
         <v>45872</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45781</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45690</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45592</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45501</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45410</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45319</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45228</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45137</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45046</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44955</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44864</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44773</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44682</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44591</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44500</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44409</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44318</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44227</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44136</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44045</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43954</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43863</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43772</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43681</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43590</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43499</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43401</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43310</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43219</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43128</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43037</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42946</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42855</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42764</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42673</v>
       </c>
     </row>
-    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="E81" s="3">
         <v>1300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-15300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-3500</v>
       </c>
-      <c r="G81" s="3">
-        <v>-28500</v>
-      </c>
       <c r="H81" s="3">
+        <v>-28200</v>
+      </c>
+      <c r="I81" s="3">
         <v>-2000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-7900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>6400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-10500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-2000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-3900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>7400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-6200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-1300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>17400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>2800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>9000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>21800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>5900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-15100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>24400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-7600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>20600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-3200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>6400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-700</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>19500</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-800</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>4300</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>400</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>14000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8199,121 +8396,125 @@
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
+      <c r="AN82" s="3"/>
     </row>
-    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>8400</v>
+      </c>
+      <c r="E83" s="3">
         <v>8000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>8300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>8500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>8600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>7500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>7400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>7700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>7600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>7900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>7500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>7200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>7600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>7900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>7500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>7400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>7300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>7200</v>
-      </c>
-      <c r="U83" s="3">
-        <v>7300</v>
       </c>
       <c r="V83" s="3">
         <v>7300</v>
       </c>
       <c r="W83" s="3">
+        <v>7300</v>
+      </c>
+      <c r="X83" s="3">
         <v>7900</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>6600</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>6700</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>6100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>6500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>5000</v>
-      </c>
-      <c r="AC83" s="3">
-        <v>4400</v>
       </c>
       <c r="AD83" s="3">
         <v>4400</v>
       </c>
       <c r="AE83" s="3">
+        <v>4400</v>
+      </c>
+      <c r="AF83" s="3">
         <v>3100</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>2800</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>2300</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>2200</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>1800</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>1700</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>1600</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>1500</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8425,8 +8626,11 @@
       <c r="AM84" s="3">
         <v>0</v>
       </c>
+      <c r="AN84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8538,8 +8742,11 @@
       <c r="AM85" s="3">
         <v>0</v>
       </c>
+      <c r="AN85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8651,8 +8858,11 @@
       <c r="AM86" s="3">
         <v>0</v>
       </c>
+      <c r="AN86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8764,8 +8974,11 @@
       <c r="AM87" s="3">
         <v>0</v>
       </c>
+      <c r="AN87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8877,121 +9090,127 @@
       <c r="AM88" s="3">
         <v>0</v>
       </c>
+      <c r="AN88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-6700</v>
+      </c>
+      <c r="E89" s="3">
         <v>32000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-56500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>41200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-41100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>16600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-33700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>69700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-29800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>12700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-14000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>49600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-9900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-9400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-31700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>59200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>6200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>14100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>12400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>79400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-15800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>20700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-33500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>56000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-39600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>5100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-13100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>54600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-10900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-1600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-11000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>64800</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-22800</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-8600</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-3500</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>47000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>-27900</v>
       </c>
     </row>
-    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9031,121 +9250,125 @@
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
+      <c r="AN90" s="3"/>
     </row>
-    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-9100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-8500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-10100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-21400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-5400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-14900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-3900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-4100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-3000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-2000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-2200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-4800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-4100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-3500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-7100</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-5800</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-8000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-7200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-19100</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-12800</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-14000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-9000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-17400</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-11700</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-8300</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-7600</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-6500</v>
       </c>
     </row>
-    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9257,8 +9480,11 @@
       <c r="AM92" s="3">
         <v>0</v>
       </c>
+      <c r="AN92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9370,8 +9596,11 @@
       <c r="AM93" s="3">
         <v>0</v>
       </c>
+      <c r="AN93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -9379,112 +9608,115 @@
         <v>-2200</v>
       </c>
       <c r="E94" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="F94" s="3">
         <v>-1300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-8900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-8400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-10000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-21300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-5400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-14900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-3800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-4100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-2900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-2000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-2300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-5000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-4100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-6100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-7800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-7000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-9800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-7400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-19000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-13400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-14000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-11900</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-17300</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-18900</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-7700</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-7900</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-7200</v>
       </c>
     </row>
-    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9524,8 +9756,9 @@
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
+      <c r="AN95" s="3"/>
     </row>
-    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9562,8 +9795,8 @@
       <c r="N96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -9637,8 +9870,11 @@
       <c r="AM96" s="3">
         <v>0</v>
       </c>
+      <c r="AN96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9750,8 +9986,11 @@
       <c r="AM97" s="3">
         <v>0</v>
       </c>
+      <c r="AN97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9863,8 +10102,11 @@
       <c r="AM98" s="3">
         <v>0</v>
       </c>
+      <c r="AN98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9976,121 +10218,127 @@
       <c r="AM99" s="3">
         <v>0</v>
       </c>
+      <c r="AN99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>11300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-32700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>63000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-44700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>43200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-12000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>9800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-36800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>35200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-10700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>9300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1100</v>
-      </c>
-      <c r="R100" s="3">
-        <v>-700</v>
       </c>
       <c r="S100" s="3">
         <v>-700</v>
       </c>
       <c r="T100" s="3">
+        <v>-700</v>
+      </c>
+      <c r="U100" s="3">
         <v>-18300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-31600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-44300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>11800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-5800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>44700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-51500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>45200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>5500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>22400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-47300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>29500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>14400</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>22000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-51800</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>39300</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>16400</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>800</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-15300</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>11900</v>
       </c>
     </row>
-    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10127,8 +10375,8 @@
       <c r="N101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -10202,117 +10450,123 @@
       <c r="AM101" s="3">
         <v>0</v>
       </c>
+      <c r="AN101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-2800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>5200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-6000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>3000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-25400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>24000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-3000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-36300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>36100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-6000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-25000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-36700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>57300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-7100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-21200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>34400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-6400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>9900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>7100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-1700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-2200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>3600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-3000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>1200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-800</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-11100</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-10500</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>23900</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-23100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DLTH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DLTH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="92">
   <si>
     <t>DLTH</t>
   </si>
@@ -656,520 +656,533 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="40" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46054</v>
+      </c>
+      <c r="E7" s="2">
         <v>45963</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45872</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45781</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45690</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45592</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45501</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45410</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45319</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45228</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45137</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45046</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44955</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44864</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44773</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44682</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44591</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44500</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44409</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44318</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44227</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44136</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44045</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43954</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43863</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43772</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43681</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43590</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43499</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43401</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43310</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43219</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43128</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43037</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42946</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42855</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42764</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42673</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>215900</v>
+      </c>
+      <c r="E8" s="3">
         <v>114900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>131700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>102700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>241300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>127100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>141600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>116700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>245600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>138200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>139100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>123800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>241800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>147100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>141500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>122900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>270800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>145300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>149100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>133400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>256000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>135500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>137400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>109900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>259600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>119800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>122000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>114200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>250500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>106700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>110700</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>100200</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>217800</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>83700</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>86200</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>83700</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>174700</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>67000</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>101500</v>
+      </c>
+      <c r="E9" s="3">
         <v>53000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>59700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>49300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>134800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>60600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>67600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>55100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>127200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>68800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>67600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>58100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>117900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>70200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>65900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>55800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>125100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>61600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>67700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>66900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>120300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>64500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>64900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>57600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>122600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>54400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>57200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>53300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>119300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>45700</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>48400</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>44300</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>101800</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>36300</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>37300</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>35000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>77900</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>28300</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>114400</v>
+      </c>
+      <c r="E10" s="3">
         <v>61800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>72000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>53400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>106500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>66400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>74000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>61600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>118400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>69400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>71500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>65700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>123800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>76900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>75600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>67100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>145700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>83700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>81400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>66500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>135700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>71000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>72500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>52300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>137000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>65400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>64800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>60900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>131200</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>61000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>62300</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>55900</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>116000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>47400</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>48900</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>48700</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>96800</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>38700</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1210,8 +1223,9 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1326,8 +1340,11 @@
       <c r="AN12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1442,32 +1459,35 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E14" s="3">
+      <c r="D14" s="3">
+        <v>400</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3">
         <v>900</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
+      <c r="G14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>6200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1600</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1483,8 +1503,8 @@
       <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1495,8 +1515,8 @@
       <c r="S14" s="3">
         <v>0</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>8</v>
+      <c r="T14" s="3">
+        <v>0</v>
       </c>
       <c r="U14" s="3" t="s">
         <v>8</v>
@@ -1513,12 +1533,12 @@
       <c r="Y14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="Z14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA14" s="3">
         <v>1600</v>
       </c>
-      <c r="AA14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1534,8 +1554,8 @@
       <c r="AF14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
+      <c r="AG14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AH14" s="3">
         <v>0</v>
@@ -1558,8 +1578,11 @@
       <c r="AN14" s="3">
         <v>0</v>
       </c>
+      <c r="AO14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1579,10 +1602,10 @@
         <v>1000</v>
       </c>
       <c r="I15" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J15" s="3">
         <v>1100</v>
-      </c>
-      <c r="J15" s="3">
-        <v>1200</v>
       </c>
       <c r="K15" s="3">
         <v>1200</v>
@@ -1600,7 +1623,7 @@
         <v>1200</v>
       </c>
       <c r="P15" s="3">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="Q15" s="3">
         <v>800</v>
@@ -1627,26 +1650,26 @@
         <v>800</v>
       </c>
       <c r="Y15" s="3">
+        <v>800</v>
+      </c>
+      <c r="Z15" s="3">
         <v>900</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>700</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>200</v>
-      </c>
-      <c r="AB15" s="3">
-        <v>500</v>
       </c>
       <c r="AC15" s="3">
         <v>500</v>
       </c>
       <c r="AD15" s="3">
+        <v>500</v>
+      </c>
+      <c r="AE15" s="3">
         <v>100</v>
       </c>
-      <c r="AE15" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF15" s="3" t="s">
         <v>8</v>
       </c>
@@ -1656,8 +1679,8 @@
       <c r="AH15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI15" s="3">
-        <v>0</v>
+      <c r="AI15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AJ15" s="3">
         <v>0</v>
@@ -1674,8 +1697,11 @@
       <c r="AN15" s="3">
         <v>0</v>
       </c>
+      <c r="AO15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1713,240 +1739,247 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>206900</v>
+      </c>
+      <c r="E17" s="3">
         <v>123700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>128500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>115100</v>
       </c>
-      <c r="G17" s="3">
-        <v>242700</v>
-      </c>
       <c r="H17" s="3">
+        <v>245500</v>
+      </c>
+      <c r="I17" s="3">
         <v>143000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>141600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>125700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>236800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>150600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>140500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>128300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>231100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>154500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>137600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>123800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>246500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>140400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>136000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>131500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>225400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>132700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>127600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>128900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>226500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>118400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>118200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>123900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>220400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>109300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>100800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>100500</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>188300</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>84300</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>78800</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>82900</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>151800</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>66200</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-8800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>3300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-12400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-15900</v>
+      </c>
+      <c r="J18" s="3">
+        <v>0</v>
+      </c>
+      <c r="K18" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="L18" s="3">
+        <v>8900</v>
+      </c>
+      <c r="M18" s="3">
+        <v>-12400</v>
+      </c>
+      <c r="N18" s="3">
         <v>-1400</v>
       </c>
-      <c r="H18" s="3">
-        <v>-15900</v>
-      </c>
-      <c r="I18" s="3">
-        <v>0</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-9000</v>
-      </c>
-      <c r="K18" s="3">
-        <v>8900</v>
-      </c>
-      <c r="L18" s="3">
-        <v>-12400</v>
-      </c>
-      <c r="M18" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-4500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>10700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-7400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>3900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>24300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>4900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>13100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>30600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>2800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>9800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-19000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>33100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>3800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-9700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>30100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-2600</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>9900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>29500</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-600</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>7400</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>800</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>22900</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1987,115 +2020,116 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>200</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3">
         <v>0</v>
       </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>-100</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>-600</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="N20" s="3">
         <v>-100</v>
       </c>
       <c r="O20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P20" s="3">
         <v>-200</v>
-      </c>
-      <c r="P20" s="3">
-        <v>100</v>
       </c>
       <c r="Q20" s="3">
         <v>100</v>
       </c>
       <c r="R20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>100</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X20" s="3">
         <v>100</v>
       </c>
       <c r="Y20" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-300</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>100</v>
       </c>
       <c r="AA20" s="3">
         <v>100</v>
       </c>
       <c r="AB20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC20" s="3">
         <v>0</v>
       </c>
       <c r="AD20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="3">
         <v>200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>300</v>
       </c>
-      <c r="AF20" s="3">
-        <v>0</v>
-      </c>
       <c r="AG20" s="3">
         <v>0</v>
       </c>
       <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI20" s="3">
         <v>200</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>300</v>
-      </c>
-      <c r="AJ20" s="3">
-        <v>100</v>
       </c>
       <c r="AK20" s="3">
         <v>100</v>
       </c>
       <c r="AL20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AM20" s="3">
         <v>0</v>
@@ -2103,156 +2137,162 @@
       <c r="AN20" s="3">
         <v>0</v>
       </c>
+      <c r="AO20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>10600</v>
+      </c>
+      <c r="E21" s="3">
         <v>-7800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>4200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-11500</v>
       </c>
-      <c r="G21" s="3">
-        <v>-400</v>
-      </c>
       <c r="H21" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="I21" s="3">
         <v>-14900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-7800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>10600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-11200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-3200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>12000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>11800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>6600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>31900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>11900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>20400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>9200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>38000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>10900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>16100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-12200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>39300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>7900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>8700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-5100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>34700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>12700</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>2200</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>32000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1300</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>9200</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>2400</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>24400</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E22" s="3">
         <v>1200</v>
-      </c>
-      <c r="E22" s="3">
-        <v>1500</v>
       </c>
       <c r="F22" s="3">
         <v>1500</v>
       </c>
       <c r="G22" s="3">
-        <v>1300</v>
+        <v>1500</v>
       </c>
       <c r="H22" s="3">
         <v>1300</v>
       </c>
       <c r="I22" s="3">
-        <v>1000</v>
+        <v>1300</v>
       </c>
       <c r="J22" s="3">
         <v>1000</v>
       </c>
       <c r="K22" s="3">
+        <v>1000</v>
+      </c>
+      <c r="L22" s="3">
         <v>1100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1200</v>
-      </c>
-      <c r="M22" s="3">
-        <v>900</v>
       </c>
       <c r="N22" s="3">
         <v>900</v>
@@ -2261,314 +2301,323 @@
         <v>900</v>
       </c>
       <c r="P22" s="3">
+        <v>900</v>
+      </c>
+      <c r="Q22" s="3">
         <v>1000</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>900</v>
       </c>
       <c r="R22" s="3">
         <v>900</v>
       </c>
       <c r="S22" s="3">
+        <v>900</v>
+      </c>
+      <c r="T22" s="3">
         <v>1300</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>900</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>1200</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>1300</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>1500</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>1600</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>1800</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>1400</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>1300</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>1500</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>1200</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>800</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>2300</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>1600</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>1200</v>
-      </c>
-      <c r="AH22" s="3">
-        <v>800</v>
       </c>
       <c r="AI22" s="3">
         <v>800</v>
       </c>
       <c r="AJ22" s="3">
+        <v>800</v>
+      </c>
+      <c r="AK22" s="3">
         <v>700</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>400</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>200</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>100</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-10100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-14000</v>
       </c>
-      <c r="G23" s="3">
-        <v>-2700</v>
-      </c>
       <c r="H23" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="I23" s="3">
         <v>-23300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-2400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-9900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>8300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-13600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-2200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-5300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>9900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-8300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>3100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-1800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>23200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>3700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>12000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>29200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>7800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-20300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>31800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>2500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-10300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>28000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-4100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>8700</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>29000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-1200</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>7100</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>600</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>22900</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E24" s="3">
+      <c r="D24" s="3">
+        <v>400</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" s="3">
         <v>-400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1300</v>
       </c>
-      <c r="G24" s="3">
-        <v>800</v>
-      </c>
       <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
         <v>4900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-2100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-3100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-1500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>5800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>3000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>7500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-5100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>7600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-2700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>7500</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-1100</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>2200</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-200</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>10900</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-500</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>2700</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>200</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>8800</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2683,240 +2732,249 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-10100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-15300</v>
       </c>
-      <c r="G26" s="3">
-        <v>-3500</v>
-      </c>
       <c r="H26" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="I26" s="3">
         <v>-28200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-2000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-7900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>6400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-10500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-2000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-3900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>7500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-6200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>2300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-1300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>17300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>2800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>8900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>21800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>5900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-15200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>24200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-7600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>20500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-3100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>6500</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-700</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>18100</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-700</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>4400</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>400</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>14000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-10100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-15300</v>
       </c>
-      <c r="G27" s="3">
-        <v>-3500</v>
-      </c>
       <c r="H27" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="I27" s="3">
         <v>-28200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-2000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-7900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>6400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-10500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-2000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-3900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>7400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-6200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>2400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-1300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>17400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>2800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>9000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>21800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>5900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-15100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>24400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-7600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>20600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-3200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>6400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-700</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>18000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-800</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>4300</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>400</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>14000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3031,8 +3089,11 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3111,8 +3172,8 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
+      <c r="AC29" s="3">
+        <v>0</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
@@ -3129,12 +3190,12 @@
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AI29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ29" s="3">
         <v>1500</v>
       </c>
-      <c r="AJ29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK29" s="3" t="s">
         <v>8</v>
       </c>
@@ -3147,8 +3208,11 @@
       <c r="AN29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3263,8 +3327,11 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3379,115 +3446,118 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>-100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-200</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
         <v>0</v>
       </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>100</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>600</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N32" s="3">
         <v>100</v>
       </c>
       <c r="O32" s="3">
+        <v>100</v>
+      </c>
+      <c r="P32" s="3">
         <v>200</v>
-      </c>
-      <c r="P32" s="3">
-        <v>-100</v>
       </c>
       <c r="Q32" s="3">
         <v>-100</v>
       </c>
       <c r="R32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>-200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-100</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="X32" s="3">
         <v>-100</v>
       </c>
       <c r="Y32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Z32" s="3">
         <v>300</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>-100</v>
       </c>
       <c r="AA32" s="3">
         <v>-100</v>
       </c>
       <c r="AB32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AC32" s="3">
         <v>0</v>
       </c>
       <c r="AD32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="3">
         <v>-200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-300</v>
       </c>
-      <c r="AF32" s="3">
-        <v>0</v>
-      </c>
       <c r="AG32" s="3">
         <v>0</v>
       </c>
       <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI32" s="3">
         <v>-200</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-300</v>
-      </c>
-      <c r="AJ32" s="3">
-        <v>-100</v>
       </c>
       <c r="AK32" s="3">
         <v>-100</v>
       </c>
       <c r="AL32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AM32" s="3">
         <v>0</v>
@@ -3495,124 +3565,130 @@
       <c r="AN32" s="3">
         <v>0</v>
       </c>
+      <c r="AO32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-10100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-15300</v>
       </c>
-      <c r="G33" s="3">
-        <v>-3500</v>
-      </c>
       <c r="H33" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="I33" s="3">
         <v>-28200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-2000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-7900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>6400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-10500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-2000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-3900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>7400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-6200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>2400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-1300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>17400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>2800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>9000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>21800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>5900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-15100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>24400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-7600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>20600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-3200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>6400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-700</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>19500</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-800</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>4300</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>400</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>14000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3727,245 +3803,254 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-10100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-15300</v>
       </c>
-      <c r="G35" s="3">
-        <v>-3500</v>
-      </c>
       <c r="H35" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="I35" s="3">
         <v>-28200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-2000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-7900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>6400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-10500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-2000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-3900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>7400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-6200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>2400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-1300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>17400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>2800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>9000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>21800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>5900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-15100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>24400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-7600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>20600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-3200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>6400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-700</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>19500</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-800</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>4300</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>400</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>14000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46054</v>
+      </c>
+      <c r="E38" s="2">
         <v>45963</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45872</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45781</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45690</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45592</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45501</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45410</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45319</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45228</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45137</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45046</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44955</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44864</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44773</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44682</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44591</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44500</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44409</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44318</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44227</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44136</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44045</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43954</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43863</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43772</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43681</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43590</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43499</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43401</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43310</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43219</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43128</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43037</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42946</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42855</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42764</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42673</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4006,8 +4091,9 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4048,124 +4134,128 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>16300</v>
+      </c>
+      <c r="E41" s="3">
         <v>8200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>5700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>8600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>9300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>9800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>32200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>8200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>11100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>9200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>45500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>9400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>15400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>40400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>77100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>20400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>18900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>26100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>46600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>12800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>19000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>8900</v>
-      </c>
-      <c r="AA41" s="3">
-        <v>2200</v>
       </c>
       <c r="AB41" s="3">
         <v>2200</v>
       </c>
       <c r="AC41" s="3">
+        <v>2200</v>
+      </c>
+      <c r="AD41" s="3">
         <v>3500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>2500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>2400</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1200</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>2900</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>1400</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>13600</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>24000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4280,555 +4370,570 @@
       <c r="AN42" s="3">
         <v>0</v>
       </c>
+      <c r="AO42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E43" s="3">
         <v>7100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>10900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>6000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>6300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>6700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>10700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>12800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>9400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>7900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>7800</v>
-      </c>
-      <c r="N43" s="3">
-        <v>8400</v>
       </c>
       <c r="O43" s="3">
         <v>8400</v>
       </c>
       <c r="P43" s="3">
+        <v>8400</v>
+      </c>
+      <c r="Q43" s="3">
         <v>10200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>7600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>6900</v>
-      </c>
-      <c r="S43" s="3">
-        <v>7700</v>
       </c>
       <c r="T43" s="3">
         <v>7700</v>
       </c>
       <c r="U43" s="3">
+        <v>7700</v>
+      </c>
+      <c r="V43" s="3">
         <v>4900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>4600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>5300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>7000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>7600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>5400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>3400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>8200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>7100</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>8700</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>4600</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>3200</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>400</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>600</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>300</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>1700</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>500</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>1100</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>400</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>131300</v>
+      </c>
+      <c r="E44" s="3">
         <v>192200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>148100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>176100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>166500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>231400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>168700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>136400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>125800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>174000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>157100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>145000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>154900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>204700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>164500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>152200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>122700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>165100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>134900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>144200</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>149100</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>213400</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>167600</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>175000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>147800</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>183100</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>114800</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>104300</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>97700</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>131400</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>102400</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>98000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>89500</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>129500</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>84700</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>75700</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>70400</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>96700</v>
       </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E45" s="3">
         <v>4500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>4700</v>
-      </c>
-      <c r="F45" s="3">
-        <v>3700</v>
       </c>
       <c r="G45" s="3">
         <v>3700</v>
       </c>
       <c r="H45" s="3">
+        <v>3700</v>
+      </c>
+      <c r="I45" s="3">
         <v>4600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>15700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>15100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>14600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>15100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>13400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>11200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>9700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>8700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>9700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>7600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>7700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>8800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>10700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>12000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>12200</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>15100</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>13100</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>11500</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>9800</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>9100</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>13300</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>9500</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>5400</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>6400</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>8300</v>
       </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>172100</v>
+      </c>
+      <c r="E46" s="3">
         <v>228700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>185900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>211100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>191600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>264300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>206900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>171400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>181000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>203500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>191800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>176500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>221700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>240000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>202500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>214100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>222500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>206600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>169800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>184600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>209700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>242900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>201800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>197000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>162200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>204300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>137500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>126100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>118200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>150200</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>116600</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>109600</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>101800</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>145400</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>96100</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>95900</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>101200</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>108200</v>
       </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E47" s="3">
         <v>4900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>4800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>4900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>4500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>4800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>4900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>4800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>5000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>4900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>5300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>5400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>5500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>5300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>5800</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>6100</v>
-      </c>
-      <c r="S47" s="3">
-        <v>6600</v>
       </c>
       <c r="T47" s="3">
         <v>6600</v>
       </c>
       <c r="U47" s="3">
+        <v>6600</v>
+      </c>
+      <c r="V47" s="3">
         <v>6700</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>6300</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>6100</v>
-      </c>
-      <c r="X47" s="3">
-        <v>6000</v>
       </c>
       <c r="Y47" s="3">
         <v>6000</v>
       </c>
       <c r="Z47" s="3">
+        <v>6000</v>
+      </c>
+      <c r="AA47" s="3">
         <v>5700</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>6400</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>6500</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>6200</v>
-      </c>
-      <c r="AD47" s="3">
-        <v>6300</v>
       </c>
       <c r="AE47" s="3">
         <v>6300</v>
@@ -4848,8 +4953,8 @@
       <c r="AJ47" s="3">
         <v>6300</v>
       </c>
-      <c r="AK47" s="3" t="s">
-        <v>8</v>
+      <c r="AK47" s="3">
+        <v>6300</v>
       </c>
       <c r="AL47" s="3" t="s">
         <v>8</v>
@@ -4860,177 +4965,183 @@
       <c r="AN47" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO47" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>215800</v>
+      </c>
+      <c r="E48" s="3">
         <v>223800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>231900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>238500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>247200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>252500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>263600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>282400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>294500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>304100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>297800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>297700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>291500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>295900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>278300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>276100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>281100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>289600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>281300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>287200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>295200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>304600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>296600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>301100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>304200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>303800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>284400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>282200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>334200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>165900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>144800</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>129200</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>109700</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>98200</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>75700</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>62500</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>52400</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>45300</v>
       </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E49" s="3">
         <v>9300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>9800</v>
-      </c>
-      <c r="F49" s="3">
-        <v>7900</v>
       </c>
       <c r="G49" s="3">
         <v>7900</v>
       </c>
       <c r="H49" s="3">
+        <v>7900</v>
+      </c>
+      <c r="I49" s="3">
         <v>10100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>7600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>8200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>7500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>8300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>6200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>6900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>7000</v>
-      </c>
-      <c r="P49" s="3">
-        <v>900</v>
       </c>
       <c r="Q49" s="3">
         <v>900</v>
       </c>
       <c r="R49" s="3">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="S49" s="3">
         <v>600</v>
       </c>
       <c r="T49" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="U49" s="3">
         <v>700</v>
@@ -5051,22 +5162,22 @@
         <v>700</v>
       </c>
       <c r="AA49" s="3">
+        <v>700</v>
+      </c>
+      <c r="AB49" s="3">
         <v>1700</v>
-      </c>
-      <c r="AB49" s="3">
-        <v>700</v>
       </c>
       <c r="AC49" s="3">
         <v>700</v>
       </c>
       <c r="AD49" s="3">
+        <v>700</v>
+      </c>
+      <c r="AE49" s="3">
         <v>400</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>700</v>
-      </c>
-      <c r="AF49" s="3">
-        <v>400</v>
       </c>
       <c r="AG49" s="3">
         <v>400</v>
@@ -5092,8 +5203,11 @@
       <c r="AN49" s="3">
         <v>400</v>
       </c>
+      <c r="AO49" s="3">
+        <v>400</v>
+      </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5208,8 +5322,11 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5324,8 +5441,11 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -5333,31 +5453,31 @@
         <v>1300</v>
       </c>
       <c r="E52" s="3">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="F52" s="3">
         <v>1400</v>
       </c>
       <c r="G52" s="3">
+        <v>1400</v>
+      </c>
+      <c r="H52" s="3">
         <v>1200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1300</v>
-      </c>
-      <c r="I52" s="3">
-        <v>1400</v>
       </c>
       <c r="J52" s="3">
         <v>1400</v>
       </c>
       <c r="K52" s="3">
+        <v>1400</v>
+      </c>
+      <c r="L52" s="3">
         <v>1500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1600</v>
-      </c>
-      <c r="M52" s="3">
-        <v>1700</v>
       </c>
       <c r="N52" s="3">
         <v>1700</v>
@@ -5366,82 +5486,85 @@
         <v>1700</v>
       </c>
       <c r="P52" s="3">
+        <v>1700</v>
+      </c>
+      <c r="Q52" s="3">
         <v>5600</v>
-      </c>
-      <c r="Q52" s="3">
-        <v>5900</v>
       </c>
       <c r="R52" s="3">
         <v>5900</v>
       </c>
       <c r="S52" s="3">
-        <v>4700</v>
+        <v>5900</v>
       </c>
       <c r="T52" s="3">
         <v>4700</v>
       </c>
       <c r="U52" s="3">
+        <v>4700</v>
+      </c>
+      <c r="V52" s="3">
         <v>4600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>3400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>3300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>2900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>5300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>3900</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>3000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1700</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>2300</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>3500</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>4800</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>2700</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>9400</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>1200</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>1900</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5556,124 +5679,130 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>402600</v>
+      </c>
+      <c r="E54" s="3">
         <v>468000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>433800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>463700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>452400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>533100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>488600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>471400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>491200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>526000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>503100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>488400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>527500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>547700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>493300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>502800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>515600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>508200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>463200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>482200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>514900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>554700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>506200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>505600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>474100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>518100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>434100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>418900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>295300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>324500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>270400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>249000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>223100</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>252900</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>181700</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>160000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>156000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>155600</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5714,8 +5843,9 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5756,171 +5886,175 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>48200</v>
+      </c>
+      <c r="E57" s="3">
         <v>80200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>43600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>45900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>73900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>104500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>77600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>37400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>51100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>53500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>59300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>36100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>56500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>77800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>53600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>54500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>45400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>59200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>37700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>40100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>33600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>57100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>40100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>34400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>33100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>55400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>36300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>26700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>25400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>34200</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>19500</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>14600</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>17300</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>30100</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>17800</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>10700</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>9300</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>19300</v>
       </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>20200</v>
+      </c>
+      <c r="E58" s="3">
         <v>64600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>52200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>83400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>19000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>62900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>19400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>31700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>20400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>55900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>19800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>19400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>19200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>13600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>3500</v>
-      </c>
-      <c r="R58" s="3">
-        <v>3400</v>
       </c>
       <c r="S58" s="3">
         <v>3400</v>
@@ -5929,415 +6063,427 @@
         <v>3400</v>
       </c>
       <c r="U58" s="3">
+        <v>3400</v>
+      </c>
+      <c r="V58" s="3">
         <v>3300</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>20800</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>5800</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>5700</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>4800</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>2200</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>3200</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>2100</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1600</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>800</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>200</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>600</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>21800</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>100</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>3000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>2400</v>
-      </c>
-      <c r="AL58" s="3">
-        <v>700</v>
       </c>
       <c r="AM58" s="3">
         <v>700</v>
       </c>
       <c r="AN58" s="3">
+        <v>700</v>
+      </c>
+      <c r="AO58" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>22900</v>
+      </c>
+      <c r="E59" s="3">
         <v>24400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>25100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>20700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>28400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>22900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>23900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>19400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>26300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>21400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>20400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>22000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>31000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>49900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>43000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>50200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>67200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>54200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>44700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>49800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>56300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>43500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>39200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>46000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>54500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>38000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>33500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>35200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>26700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>30700</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>22800</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>33200</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>32900</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>25700</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>17500</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>25300</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>25000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>17400</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>108200</v>
+      </c>
+      <c r="E60" s="3">
         <v>177700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>129100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>157000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>128600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>203600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>127000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>95500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>105600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>141200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>107200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>87900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>118300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>141300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>100100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>108200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>116000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>116700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>85700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>110700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>95700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>106300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>84100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>82600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>79800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>95500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>71400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>62700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>52600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>65200</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>42800</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>69600</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>50300</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>58800</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>37800</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>36700</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>35100</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>38800</v>
       </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>127300</v>
+      </c>
+      <c r="E61" s="3">
         <v>131700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>136800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>140500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>144100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>144200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>148900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>160600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>165800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>170900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>172400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>176400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>180700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>64300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>65100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>66000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>66900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>67700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>68600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>69400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>116300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>160700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>141400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>149800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>103500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>156500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>99200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>77500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>67900</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>111200</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>76900</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>35600</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>28000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>70000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>20200</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>4800</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>3400</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -6377,71 +6523,71 @@
       <c r="O62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P62" s="3">
+      <c r="P62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q62" s="3">
         <v>123500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>103700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>107200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>110000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>118500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>107000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>110100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>112500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>119000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>113200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>112400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>123100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>113100</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>110200</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>127900</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>14700</v>
-      </c>
-      <c r="AF62" s="3">
-        <v>5500</v>
       </c>
       <c r="AG62" s="3">
         <v>5500</v>
       </c>
       <c r="AH62" s="3">
+        <v>5500</v>
+      </c>
+      <c r="AI62" s="3">
         <v>5400</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>5500</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>4800</v>
-      </c>
-      <c r="AK62" s="3">
-        <v>3700</v>
       </c>
       <c r="AL62" s="3">
         <v>3700</v>
@@ -6450,10 +6596,13 @@
         <v>3700</v>
       </c>
       <c r="AN62" s="3">
+        <v>3700</v>
+      </c>
+      <c r="AO62" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6568,8 +6717,11 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6684,8 +6836,11 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6800,124 +6955,130 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>236500</v>
+      </c>
+      <c r="E66" s="3">
         <v>310300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>266700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>298800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>272800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>348000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>275900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>256100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>271500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>312100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>279700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>264300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>300300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>325800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>265700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>278200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>289700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>300400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>258800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>287800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>321500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>383700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>336500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>342600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>295800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>364600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>280400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>267800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>135000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>185300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>128500</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>113900</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>87000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>136800</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>65300</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>48100</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>44800</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>58700</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6958,8 +7119,9 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7074,8 +7236,11 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7190,8 +7355,11 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7306,8 +7474,11 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7422,124 +7593,130 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>61300</v>
+      </c>
+      <c r="E72" s="3">
         <v>53600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>63700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>62400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>77700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>83700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>112200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>115900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>121400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>116800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>127300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>129300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>133200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>125700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>131900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>129600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>130900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>113500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>110700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>101700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>101200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>79300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>78400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>72500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>87600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>63200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>63000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>61100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>70600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>50000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>53100</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>46700</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>48100</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>28600</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>29400</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>25100</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>24700</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>10700</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7654,8 +7831,11 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7770,8 +7950,11 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7886,124 +8069,130 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>169000</v>
+      </c>
+      <c r="E76" s="3">
         <v>160600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>170000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>167900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>182700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>188100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>215700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>218400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>222800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>217100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>226700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>227300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>230400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>221900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>227600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>224600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>225900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>207800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>204400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>194400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>193500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>171100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>169700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>163100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>178300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>153500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>153700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>151100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>160300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>139200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>141900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>135100</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>136100</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>116100</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>116400</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>111900</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>111200</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>96900</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8118,245 +8307,254 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46054</v>
+      </c>
+      <c r="E80" s="2">
         <v>45963</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45872</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45781</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45690</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45592</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45501</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45410</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45319</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45228</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45137</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45046</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44955</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44864</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44773</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44682</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44591</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44500</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44409</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44318</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44227</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44136</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44045</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43954</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43863</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43772</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43681</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43590</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43499</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43401</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43310</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43219</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43128</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43037</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42946</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42855</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42764</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42673</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-10100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-15300</v>
       </c>
-      <c r="G81" s="3">
-        <v>-3500</v>
-      </c>
       <c r="H81" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="I81" s="3">
         <v>-28200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-2000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-7900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>6400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-10500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-2000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-3900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>7400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-6200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>2400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-1300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>17400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>2800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>9000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>21800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>5900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-15100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>24400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-7600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>20600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-3200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>6400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-700</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>19500</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-800</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>4300</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>400</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>14000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8397,124 +8595,128 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E83" s="3">
         <v>8400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>8000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>8300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>8500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>8600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>7500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>7400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>7700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>7600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>7900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>7500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>7200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>7600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>7900</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>7500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>7400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>7300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>7200</v>
-      </c>
-      <c r="V83" s="3">
-        <v>7300</v>
       </c>
       <c r="W83" s="3">
         <v>7300</v>
       </c>
       <c r="X83" s="3">
+        <v>7300</v>
+      </c>
+      <c r="Y83" s="3">
         <v>7900</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>6600</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>6700</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>6100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>6500</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>5000</v>
-      </c>
-      <c r="AD83" s="3">
-        <v>4400</v>
       </c>
       <c r="AE83" s="3">
         <v>4400</v>
       </c>
       <c r="AF83" s="3">
+        <v>4400</v>
+      </c>
+      <c r="AG83" s="3">
         <v>3100</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>2800</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>2300</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>2200</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>1800</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>1700</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>1600</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>1500</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8629,8 +8831,11 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8745,8 +8950,11 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8861,8 +9069,11 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8977,8 +9188,11 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9093,124 +9307,130 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>55300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-6700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>32000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-56500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>41200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-41100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>16600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-33700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>69700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-29800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>12700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-14000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>49600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-9900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-9400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-31700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>59200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>6200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>14100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>12400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>79400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-15800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>20700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-33500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>56000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-39600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>5100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-13100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>54600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-10900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-1600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-11000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>64800</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-22800</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-8600</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>-3500</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>47000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>-27900</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9251,124 +9471,128 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-9100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-8500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-10100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-21400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-5400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-14900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-3900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-4100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-3000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-2000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-2200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-4800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-4100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-3500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-7100</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-5800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-8000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-7200</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-19100</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-12800</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-14000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-9000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-17400</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-11700</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-8300</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-7600</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-6500</v>
       </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9483,8 +9707,11 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9599,124 +9826,130 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-2200</v>
+        <v>-1700</v>
       </c>
       <c r="E94" s="3">
         <v>-2200</v>
       </c>
       <c r="F94" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="G94" s="3">
         <v>-1300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-8900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-8400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-10000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-21300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-5400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-14900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-3800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-4100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-2900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-2000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-2300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-5000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-4100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-6100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-7800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-7000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-9800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-7400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-19000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-13400</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-14000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-11900</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-17300</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-18900</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-7700</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-7900</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-7200</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9757,8 +9990,9 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9798,8 +10032,8 @@
       <c r="O96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -9873,8 +10107,11 @@
       <c r="AN96" s="3">
         <v>0</v>
       </c>
+      <c r="AO96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9989,8 +10226,11 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10105,8 +10345,11 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10221,124 +10464,130 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-45400</v>
+      </c>
+      <c r="E100" s="3">
         <v>11300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-32700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>63000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-44700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>43200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-12000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>9800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-36800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>35200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-10700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>9300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1100</v>
-      </c>
-      <c r="S100" s="3">
-        <v>-700</v>
       </c>
       <c r="T100" s="3">
         <v>-700</v>
       </c>
       <c r="U100" s="3">
+        <v>-700</v>
+      </c>
+      <c r="V100" s="3">
         <v>-18300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-31600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-44300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>11800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-5800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>44700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-51500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>45200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>5500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>22400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-47300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>29500</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>14400</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>22000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-51800</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>39300</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>16400</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>800</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-15300</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>11900</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10378,8 +10627,8 @@
       <c r="O101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -10453,120 +10702,126 @@
       <c r="AN101" s="3">
         <v>0</v>
       </c>
+      <c r="AO101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E102" s="3">
         <v>2400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-2800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>5200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-6000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>3000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-25400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>24000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-3000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-36300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>36100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-6000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-25000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-36700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>57300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-7100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-21200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>34400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-6400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>9900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>7100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-1700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-2200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>3600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-400</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-500</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-3000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>1200</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-800</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-11100</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-10500</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>23900</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-23100</v>
       </c>
     </row>
